--- a/PREMIO.xlsx
+++ b/PREMIO.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alan Souto\Desktop\Premio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alan Souto\Desktop\Premio\PREMIO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44F97F02-D289-4057-B3E5-AF5979EEE839}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C265299-27BD-4EB3-8275-79A8E7DA6947}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{EBBE1F25-C943-4A3A-8B11-92CFB5DB310C}"/>
   </bookViews>
@@ -1382,7 +1382,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="115">
+  <cellXfs count="114">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1651,7 +1651,6 @@
     <xf numFmtId="0" fontId="22" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="22" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1685,6 +1684,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="15" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1714,9 +1716,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2126,7 +2125,7 @@
       <c r="Q1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="R1" s="94" t="s">
+      <c r="R1" s="93" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2198,7 +2197,7 @@
       <c r="E3" s="37">
         <v>4.8</v>
       </c>
-      <c r="F3" s="95">
+      <c r="F3" s="94">
         <v>5</v>
       </c>
       <c r="G3" s="20"/>
@@ -2216,19 +2215,19 @@
       </c>
       <c r="L3" s="51"/>
       <c r="M3" s="51"/>
-      <c r="N3" s="96">
+      <c r="N3" s="95">
         <v>24</v>
       </c>
-      <c r="O3" s="96">
+      <c r="O3" s="95">
         <v>24</v>
       </c>
-      <c r="P3" s="95">
+      <c r="P3" s="94">
         <v>4.99</v>
       </c>
       <c r="Q3" s="48">
         <v>594</v>
       </c>
-      <c r="R3" s="97" t="s">
+      <c r="R3" s="96" t="s">
         <v>196</v>
       </c>
     </row>
@@ -2248,7 +2247,7 @@
       <c r="E4" s="37">
         <v>3.96</v>
       </c>
-      <c r="F4" s="95">
+      <c r="F4" s="94">
         <v>3</v>
       </c>
       <c r="G4" s="20"/>
@@ -2266,13 +2265,13 @@
       </c>
       <c r="L4" s="51"/>
       <c r="M4" s="51"/>
-      <c r="N4" s="96">
+      <c r="N4" s="95">
         <v>24</v>
       </c>
-      <c r="O4" s="96">
+      <c r="O4" s="95">
         <v>22</v>
       </c>
-      <c r="P4" s="95">
+      <c r="P4" s="94">
         <v>4.5</v>
       </c>
       <c r="Q4" s="48">
@@ -2298,7 +2297,7 @@
       <c r="E5" s="37">
         <v>2.8</v>
       </c>
-      <c r="F5" s="95">
+      <c r="F5" s="94">
         <v>3</v>
       </c>
       <c r="G5" s="20"/>
@@ -2316,13 +2315,13 @@
       </c>
       <c r="L5" s="51"/>
       <c r="M5" s="51"/>
-      <c r="N5" s="96">
+      <c r="N5" s="95">
         <v>24</v>
       </c>
-      <c r="O5" s="96">
+      <c r="O5" s="95">
         <v>25</v>
       </c>
-      <c r="P5" s="95">
+      <c r="P5" s="94">
         <v>2.79</v>
       </c>
       <c r="Q5" s="48">
@@ -2363,10 +2362,10 @@
       <c r="L6" s="51"/>
       <c r="M6" s="51"/>
       <c r="N6" s="51"/>
-      <c r="O6" s="96">
+      <c r="O6" s="95">
         <v>21</v>
       </c>
-      <c r="P6" s="95">
+      <c r="P6" s="94">
         <v>0.1</v>
       </c>
       <c r="Q6" s="41" t="s">
@@ -2392,7 +2391,7 @@
       <c r="E7" s="37">
         <v>4.3600000000000003</v>
       </c>
-      <c r="F7" s="95">
+      <c r="F7" s="94">
         <v>8</v>
       </c>
       <c r="G7" s="37">
@@ -2412,19 +2411,19 @@
       </c>
       <c r="L7" s="51"/>
       <c r="M7" s="51"/>
-      <c r="N7" s="96">
+      <c r="N7" s="95">
         <v>23</v>
       </c>
-      <c r="O7" s="96">
+      <c r="O7" s="95">
         <v>23</v>
       </c>
-      <c r="P7" s="95">
+      <c r="P7" s="94">
         <v>4.58</v>
       </c>
       <c r="Q7" s="48">
         <v>353.44</v>
       </c>
-      <c r="R7" s="98" t="s">
+      <c r="R7" s="97" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2444,7 +2443,7 @@
       <c r="E8" s="37">
         <v>3.68</v>
       </c>
-      <c r="F8" s="95">
+      <c r="F8" s="94">
         <v>7</v>
       </c>
       <c r="G8" s="20"/>
@@ -2462,13 +2461,13 @@
       </c>
       <c r="L8" s="51"/>
       <c r="M8" s="51"/>
-      <c r="N8" s="96">
+      <c r="N8" s="95">
         <v>23</v>
       </c>
-      <c r="O8" s="96">
+      <c r="O8" s="95">
         <v>22</v>
       </c>
-      <c r="P8" s="95">
+      <c r="P8" s="94">
         <v>4.03</v>
       </c>
       <c r="Q8" s="48">
@@ -2511,10 +2510,10 @@
       <c r="L9" s="51"/>
       <c r="M9" s="51"/>
       <c r="N9" s="51"/>
-      <c r="O9" s="96">
+      <c r="O9" s="95">
         <v>23</v>
       </c>
-      <c r="P9" s="95">
+      <c r="P9" s="94">
         <v>3</v>
       </c>
       <c r="Q9" s="41" t="s">
@@ -2540,7 +2539,7 @@
       <c r="E10" s="37">
         <v>4</v>
       </c>
-      <c r="F10" s="95">
+      <c r="F10" s="94">
         <v>3</v>
       </c>
       <c r="G10" s="37">
@@ -2560,19 +2559,19 @@
       </c>
       <c r="L10" s="51"/>
       <c r="M10" s="51"/>
-      <c r="N10" s="96">
+      <c r="N10" s="95">
         <v>23</v>
       </c>
-      <c r="O10" s="96">
+      <c r="O10" s="95">
         <v>23</v>
       </c>
-      <c r="P10" s="95">
+      <c r="P10" s="94">
         <v>4.3499999999999996</v>
       </c>
       <c r="Q10" s="48">
         <v>678</v>
       </c>
-      <c r="R10" s="98" t="s">
+      <c r="R10" s="97" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2592,7 +2591,7 @@
       <c r="E11" s="37">
         <v>3.48</v>
       </c>
-      <c r="F11" s="95">
+      <c r="F11" s="94">
         <v>8</v>
       </c>
       <c r="G11" s="20"/>
@@ -2610,19 +2609,19 @@
       </c>
       <c r="L11" s="51"/>
       <c r="M11" s="51"/>
-      <c r="N11" s="96">
+      <c r="N11" s="95">
         <v>23</v>
       </c>
-      <c r="O11" s="96">
+      <c r="O11" s="95">
         <v>21</v>
       </c>
-      <c r="P11" s="95">
+      <c r="P11" s="94">
         <v>3.93</v>
       </c>
       <c r="Q11" s="48">
         <v>0</v>
       </c>
-      <c r="R11" s="99" t="s">
+      <c r="R11" s="98" t="s">
         <v>12</v>
       </c>
     </row>
@@ -2661,16 +2660,16 @@
       <c r="L12" s="51"/>
       <c r="M12" s="51"/>
       <c r="N12" s="51"/>
-      <c r="O12" s="96">
+      <c r="O12" s="95">
         <v>24</v>
       </c>
-      <c r="P12" s="95">
+      <c r="P12" s="94">
         <v>0.71</v>
       </c>
       <c r="Q12" s="48">
         <v>51</v>
       </c>
-      <c r="R12" s="98" t="s">
+      <c r="R12" s="97" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2690,7 +2689,7 @@
       <c r="E13" s="37">
         <v>4.5199999999999996</v>
       </c>
-      <c r="F13" s="95">
+      <c r="F13" s="94">
         <v>1</v>
       </c>
       <c r="G13" s="20"/>
@@ -2709,10 +2708,10 @@
       <c r="L13" s="51"/>
       <c r="M13" s="51"/>
       <c r="N13" s="51"/>
-      <c r="O13" s="96">
+      <c r="O13" s="95">
         <v>24</v>
       </c>
-      <c r="P13" s="95">
+      <c r="P13" s="94">
         <v>4.71</v>
       </c>
       <c r="Q13" s="41" t="s">
@@ -2738,7 +2737,7 @@
       <c r="E14" s="37">
         <v>3.4</v>
       </c>
-      <c r="F14" s="95">
+      <c r="F14" s="94">
         <v>5</v>
       </c>
       <c r="G14" s="20"/>
@@ -2756,19 +2755,19 @@
       </c>
       <c r="L14" s="51"/>
       <c r="M14" s="51"/>
-      <c r="N14" s="96">
+      <c r="N14" s="95">
         <v>24</v>
       </c>
-      <c r="O14" s="96">
+      <c r="O14" s="95">
         <v>23</v>
       </c>
-      <c r="P14" s="95">
+      <c r="P14" s="94">
         <v>3.63</v>
       </c>
       <c r="Q14" s="48">
         <v>0</v>
       </c>
-      <c r="R14" s="99" t="s">
+      <c r="R14" s="98" t="s">
         <v>12</v>
       </c>
     </row>
@@ -2788,7 +2787,7 @@
       <c r="E15" s="37">
         <v>3.96</v>
       </c>
-      <c r="F15" s="95">
+      <c r="F15" s="94">
         <v>6</v>
       </c>
       <c r="G15" s="37">
@@ -2808,19 +2807,19 @@
       </c>
       <c r="L15" s="51"/>
       <c r="M15" s="51"/>
-      <c r="N15" s="96">
+      <c r="N15" s="95">
         <v>24</v>
       </c>
-      <c r="O15" s="96">
+      <c r="O15" s="95">
         <v>23</v>
       </c>
-      <c r="P15" s="95">
+      <c r="P15" s="94">
         <v>4.22</v>
       </c>
       <c r="Q15" s="48">
         <v>665.84</v>
       </c>
-      <c r="R15" s="98" t="s">
+      <c r="R15" s="97" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2840,7 +2839,7 @@
       <c r="E16" s="37">
         <v>3.32</v>
       </c>
-      <c r="F16" s="95">
+      <c r="F16" s="94">
         <v>7</v>
       </c>
       <c r="G16" s="20"/>
@@ -2858,19 +2857,19 @@
       </c>
       <c r="L16" s="51"/>
       <c r="M16" s="51"/>
-      <c r="N16" s="96">
+      <c r="N16" s="95">
         <v>24</v>
       </c>
-      <c r="O16" s="96">
+      <c r="O16" s="95">
         <v>22</v>
       </c>
-      <c r="P16" s="95">
+      <c r="P16" s="94">
         <v>3.61</v>
       </c>
       <c r="Q16" s="48">
         <v>609.28</v>
       </c>
-      <c r="R16" s="98" t="s">
+      <c r="R16" s="97" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2890,7 +2889,7 @@
       <c r="E17" s="37">
         <v>0.72</v>
       </c>
-      <c r="F17" s="95">
+      <c r="F17" s="94">
         <v>4</v>
       </c>
       <c r="G17" s="20"/>
@@ -2908,19 +2907,19 @@
       </c>
       <c r="L17" s="51"/>
       <c r="M17" s="51"/>
-      <c r="N17" s="96">
+      <c r="N17" s="95">
         <v>23</v>
       </c>
-      <c r="O17" s="96">
+      <c r="O17" s="95">
         <v>25</v>
       </c>
-      <c r="P17" s="95">
+      <c r="P17" s="94">
         <v>0.59</v>
       </c>
       <c r="Q17" s="48">
         <v>0</v>
       </c>
-      <c r="R17" s="99" t="s">
+      <c r="R17" s="98" t="s">
         <v>12</v>
       </c>
     </row>
@@ -2940,7 +2939,7 @@
       <c r="E18" s="37">
         <v>2.6</v>
       </c>
-      <c r="F18" s="95">
+      <c r="F18" s="94">
         <v>6</v>
       </c>
       <c r="G18" s="20"/>
@@ -2958,19 +2957,19 @@
       </c>
       <c r="L18" s="51"/>
       <c r="M18" s="51"/>
-      <c r="N18" s="96">
+      <c r="N18" s="95">
         <v>23</v>
       </c>
-      <c r="O18" s="96">
+      <c r="O18" s="95">
         <v>18</v>
       </c>
-      <c r="P18" s="95">
+      <c r="P18" s="94">
         <v>3.42</v>
       </c>
       <c r="Q18" s="48">
         <v>0</v>
       </c>
-      <c r="R18" s="99" t="s">
+      <c r="R18" s="98" t="s">
         <v>12</v>
       </c>
     </row>
@@ -2990,7 +2989,7 @@
       <c r="E19" s="37">
         <v>4.12</v>
       </c>
-      <c r="F19" s="95">
+      <c r="F19" s="94">
         <v>10</v>
       </c>
       <c r="G19" s="20"/>
@@ -3008,19 +3007,19 @@
       </c>
       <c r="L19" s="51"/>
       <c r="M19" s="51"/>
-      <c r="N19" s="96">
+      <c r="N19" s="95">
         <v>24</v>
       </c>
-      <c r="O19" s="96">
+      <c r="O19" s="95">
         <v>22</v>
       </c>
-      <c r="P19" s="95">
+      <c r="P19" s="94">
         <v>4.41</v>
       </c>
       <c r="Q19" s="48">
         <v>680.48</v>
       </c>
-      <c r="R19" s="98" t="s">
+      <c r="R19" s="97" t="s">
         <v>10</v>
       </c>
     </row>
@@ -3040,7 +3039,7 @@
       <c r="E20" s="37">
         <v>3.2</v>
       </c>
-      <c r="F20" s="95">
+      <c r="F20" s="94">
         <v>6</v>
       </c>
       <c r="G20" s="37">
@@ -3060,19 +3059,19 @@
       </c>
       <c r="L20" s="51"/>
       <c r="M20" s="51"/>
-      <c r="N20" s="96">
+      <c r="N20" s="95">
         <v>24</v>
       </c>
-      <c r="O20" s="96">
+      <c r="O20" s="95">
         <v>22</v>
       </c>
-      <c r="P20" s="95">
+      <c r="P20" s="94">
         <v>3.51</v>
       </c>
       <c r="Q20" s="48">
         <v>231.6</v>
       </c>
-      <c r="R20" s="98" t="s">
+      <c r="R20" s="97" t="s">
         <v>10</v>
       </c>
     </row>
@@ -3092,7 +3091,7 @@
       <c r="E21" s="37">
         <v>3</v>
       </c>
-      <c r="F21" s="95">
+      <c r="F21" s="94">
         <v>1</v>
       </c>
       <c r="G21" s="20"/>
@@ -3111,16 +3110,16 @@
       <c r="L21" s="51"/>
       <c r="M21" s="51"/>
       <c r="N21" s="51"/>
-      <c r="O21" s="96">
+      <c r="O21" s="95">
         <v>24</v>
       </c>
-      <c r="P21" s="95">
+      <c r="P21" s="94">
         <v>3.13</v>
       </c>
       <c r="Q21" s="48">
         <v>0</v>
       </c>
-      <c r="R21" s="99" t="s">
+      <c r="R21" s="98" t="s">
         <v>12</v>
       </c>
     </row>
@@ -3140,7 +3139,7 @@
       <c r="E22" s="37">
         <v>4.08</v>
       </c>
-      <c r="F22" s="95">
+      <c r="F22" s="94">
         <v>8</v>
       </c>
       <c r="G22" s="20"/>
@@ -3158,19 +3157,19 @@
       </c>
       <c r="L22" s="51"/>
       <c r="M22" s="51"/>
-      <c r="N22" s="96">
+      <c r="N22" s="95">
         <v>23</v>
       </c>
-      <c r="O22" s="96">
+      <c r="O22" s="95">
         <v>23</v>
       </c>
-      <c r="P22" s="95">
+      <c r="P22" s="94">
         <v>4.26</v>
       </c>
       <c r="Q22" s="48">
         <v>324.32</v>
       </c>
-      <c r="R22" s="98" t="s">
+      <c r="R22" s="97" t="s">
         <v>10</v>
       </c>
     </row>
@@ -3190,7 +3189,7 @@
       <c r="E23" s="37">
         <v>2</v>
       </c>
-      <c r="F23" s="95">
+      <c r="F23" s="94">
         <v>4</v>
       </c>
       <c r="G23" s="20"/>
@@ -3209,16 +3208,16 @@
       <c r="L23" s="51"/>
       <c r="M23" s="51"/>
       <c r="N23" s="51"/>
-      <c r="O23" s="96">
+      <c r="O23" s="95">
         <v>23</v>
       </c>
-      <c r="P23" s="95">
+      <c r="P23" s="94">
         <v>2.09</v>
       </c>
       <c r="Q23" s="48">
         <v>0</v>
       </c>
-      <c r="R23" s="99" t="s">
+      <c r="R23" s="98" t="s">
         <v>12</v>
       </c>
     </row>
@@ -3238,7 +3237,7 @@
       <c r="E24" s="37">
         <v>1.28</v>
       </c>
-      <c r="F24" s="95">
+      <c r="F24" s="94">
         <v>1</v>
       </c>
       <c r="G24" s="20"/>
@@ -3257,16 +3256,16 @@
       <c r="L24" s="51"/>
       <c r="M24" s="51"/>
       <c r="N24" s="51"/>
-      <c r="O24" s="96">
+      <c r="O24" s="95">
         <v>23</v>
       </c>
-      <c r="P24" s="95">
+      <c r="P24" s="94">
         <v>1.39</v>
       </c>
       <c r="Q24" s="48">
         <v>270.3</v>
       </c>
-      <c r="R24" s="98" t="s">
+      <c r="R24" s="97" t="s">
         <v>10</v>
       </c>
     </row>
@@ -3286,7 +3285,7 @@
       <c r="E25" s="37">
         <v>4.2</v>
       </c>
-      <c r="F25" s="95">
+      <c r="F25" s="94">
         <v>4</v>
       </c>
       <c r="G25" s="20"/>
@@ -3304,19 +3303,19 @@
       </c>
       <c r="L25" s="51"/>
       <c r="M25" s="51"/>
-      <c r="N25" s="96">
+      <c r="N25" s="95">
         <v>23</v>
       </c>
-      <c r="O25" s="96">
+      <c r="O25" s="95">
         <v>22</v>
       </c>
-      <c r="P25" s="95">
+      <c r="P25" s="94">
         <v>4.7699999999999996</v>
       </c>
       <c r="Q25" s="48">
         <v>285</v>
       </c>
-      <c r="R25" s="97" t="s">
+      <c r="R25" s="96" t="s">
         <v>196</v>
       </c>
     </row>
@@ -3336,7 +3335,7 @@
       <c r="E26" s="37">
         <v>3.72</v>
       </c>
-      <c r="F26" s="95">
+      <c r="F26" s="94">
         <v>5</v>
       </c>
       <c r="G26" s="20"/>
@@ -3354,19 +3353,19 @@
       </c>
       <c r="L26" s="51"/>
       <c r="M26" s="51"/>
-      <c r="N26" s="96">
+      <c r="N26" s="95">
         <v>23</v>
       </c>
-      <c r="O26" s="96">
+      <c r="O26" s="95">
         <v>22</v>
       </c>
-      <c r="P26" s="95">
+      <c r="P26" s="94">
         <v>4.17</v>
       </c>
       <c r="Q26" s="48">
         <v>314.88</v>
       </c>
-      <c r="R26" s="98" t="s">
+      <c r="R26" s="97" t="s">
         <v>10</v>
       </c>
     </row>
@@ -3386,7 +3385,7 @@
       <c r="E27" s="37">
         <v>2.8</v>
       </c>
-      <c r="F27" s="95">
+      <c r="F27" s="94">
         <v>4</v>
       </c>
       <c r="G27" s="20"/>
@@ -3404,19 +3403,19 @@
       </c>
       <c r="L27" s="51"/>
       <c r="M27" s="51"/>
-      <c r="N27" s="96">
+      <c r="N27" s="95">
         <v>23</v>
       </c>
-      <c r="O27" s="96">
+      <c r="O27" s="95">
         <v>21</v>
       </c>
-      <c r="P27" s="95">
+      <c r="P27" s="94">
         <v>3.28</v>
       </c>
       <c r="Q27" s="48">
         <v>0</v>
       </c>
-      <c r="R27" s="99" t="s">
+      <c r="R27" s="98" t="s">
         <v>12</v>
       </c>
     </row>
@@ -3436,7 +3435,7 @@
       <c r="E28" s="37">
         <v>2.4</v>
       </c>
-      <c r="F28" s="95">
+      <c r="F28" s="94">
         <v>1</v>
       </c>
       <c r="G28" s="20"/>
@@ -3454,19 +3453,19 @@
       </c>
       <c r="L28" s="51"/>
       <c r="M28" s="51"/>
-      <c r="N28" s="96">
+      <c r="N28" s="95">
         <v>23</v>
       </c>
-      <c r="O28" s="96">
+      <c r="O28" s="95">
         <v>23</v>
       </c>
-      <c r="P28" s="95">
+      <c r="P28" s="94">
         <v>2.61</v>
       </c>
       <c r="Q28" s="48">
         <v>180</v>
       </c>
-      <c r="R28" s="98" t="s">
+      <c r="R28" s="97" t="s">
         <v>10</v>
       </c>
     </row>
@@ -3486,7 +3485,7 @@
       <c r="E29" s="37">
         <v>1.76</v>
       </c>
-      <c r="F29" s="95">
+      <c r="F29" s="94">
         <v>2</v>
       </c>
       <c r="G29" s="20"/>
@@ -3504,13 +3503,13 @@
       </c>
       <c r="L29" s="51"/>
       <c r="M29" s="51"/>
-      <c r="N29" s="96">
+      <c r="N29" s="95">
         <v>16</v>
       </c>
-      <c r="O29" s="96">
+      <c r="O29" s="95">
         <v>11</v>
       </c>
-      <c r="P29" s="95">
+      <c r="P29" s="94">
         <v>3.98</v>
       </c>
       <c r="Q29" s="48">
@@ -3536,7 +3535,7 @@
       <c r="E30" s="37">
         <v>3.8</v>
       </c>
-      <c r="F30" s="95">
+      <c r="F30" s="94">
         <v>2</v>
       </c>
       <c r="G30" s="37">
@@ -3556,19 +3555,19 @@
       </c>
       <c r="L30" s="51"/>
       <c r="M30" s="51"/>
-      <c r="N30" s="96">
+      <c r="N30" s="95">
         <v>24</v>
       </c>
-      <c r="O30" s="96">
+      <c r="O30" s="95">
         <v>23</v>
       </c>
-      <c r="P30" s="95">
+      <c r="P30" s="94">
         <v>4.13</v>
       </c>
       <c r="Q30" s="48">
         <v>312</v>
       </c>
-      <c r="R30" s="98" t="s">
+      <c r="R30" s="97" t="s">
         <v>10</v>
       </c>
     </row>
@@ -3588,7 +3587,7 @@
       <c r="E31" s="37">
         <v>4.76</v>
       </c>
-      <c r="F31" s="95">
+      <c r="F31" s="94">
         <v>9</v>
       </c>
       <c r="G31" s="20"/>
@@ -3606,19 +3605,19 @@
       </c>
       <c r="L31" s="51"/>
       <c r="M31" s="51"/>
-      <c r="N31" s="96">
+      <c r="N31" s="95">
         <v>24</v>
       </c>
-      <c r="O31" s="96">
+      <c r="O31" s="95">
         <v>22</v>
       </c>
-      <c r="P31" s="95">
+      <c r="P31" s="94">
         <v>5.22</v>
       </c>
       <c r="Q31" s="48">
         <v>628.55999999999995</v>
       </c>
-      <c r="R31" s="98" t="s">
+      <c r="R31" s="97" t="s">
         <v>10</v>
       </c>
     </row>
@@ -3638,7 +3637,7 @@
       <c r="E32" s="37">
         <v>1.24</v>
       </c>
-      <c r="F32" s="95">
+      <c r="F32" s="94">
         <v>1</v>
       </c>
       <c r="G32" s="20"/>
@@ -3656,19 +3655,19 @@
       </c>
       <c r="L32" s="51"/>
       <c r="M32" s="51"/>
-      <c r="N32" s="96">
+      <c r="N32" s="95">
         <v>6</v>
       </c>
-      <c r="O32" s="96">
+      <c r="O32" s="95">
         <v>6</v>
       </c>
-      <c r="P32" s="95">
+      <c r="P32" s="94">
         <v>5.17</v>
       </c>
       <c r="Q32" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="R32" s="98" t="s">
+      <c r="R32" s="97" t="s">
         <v>10</v>
       </c>
     </row>
@@ -3688,7 +3687,7 @@
       <c r="E33" s="37">
         <v>3.32</v>
       </c>
-      <c r="F33" s="95">
+      <c r="F33" s="94">
         <v>3</v>
       </c>
       <c r="G33" s="37">
@@ -3708,19 +3707,19 @@
       </c>
       <c r="L33" s="51"/>
       <c r="M33" s="51"/>
-      <c r="N33" s="96">
+      <c r="N33" s="95">
         <v>23</v>
       </c>
-      <c r="O33" s="96">
+      <c r="O33" s="95">
         <v>16</v>
       </c>
-      <c r="P33" s="95">
+      <c r="P33" s="94">
         <v>5.19</v>
       </c>
       <c r="Q33" s="48">
         <v>618</v>
       </c>
-      <c r="R33" s="98" t="s">
+      <c r="R33" s="97" t="s">
         <v>10</v>
       </c>
     </row>
@@ -3740,7 +3739,7 @@
       <c r="E34" s="37">
         <v>3.16</v>
       </c>
-      <c r="F34" s="95">
+      <c r="F34" s="94">
         <v>8</v>
       </c>
       <c r="G34" s="20"/>
@@ -3758,19 +3757,19 @@
       </c>
       <c r="L34" s="51"/>
       <c r="M34" s="51"/>
-      <c r="N34" s="96">
+      <c r="N34" s="95">
         <v>24</v>
       </c>
-      <c r="O34" s="96">
+      <c r="O34" s="95">
         <v>18</v>
       </c>
-      <c r="P34" s="95">
+      <c r="P34" s="94">
         <v>4.12</v>
       </c>
       <c r="Q34" s="48">
         <v>0</v>
       </c>
-      <c r="R34" s="99" t="s">
+      <c r="R34" s="98" t="s">
         <v>12</v>
       </c>
     </row>
@@ -3790,7 +3789,7 @@
       <c r="E35" s="37">
         <v>2.68</v>
       </c>
-      <c r="F35" s="95">
+      <c r="F35" s="94">
         <v>7</v>
       </c>
       <c r="G35" s="37">
@@ -3810,19 +3809,19 @@
       </c>
       <c r="L35" s="51"/>
       <c r="M35" s="51"/>
-      <c r="N35" s="96">
+      <c r="N35" s="95">
         <v>23</v>
       </c>
-      <c r="O35" s="96">
+      <c r="O35" s="95">
         <v>21</v>
       </c>
-      <c r="P35" s="95">
+      <c r="P35" s="94">
         <v>2.98</v>
       </c>
       <c r="Q35" s="48">
         <v>0</v>
       </c>
-      <c r="R35" s="99" t="s">
+      <c r="R35" s="98" t="s">
         <v>12</v>
       </c>
     </row>
@@ -3842,7 +3841,7 @@
       <c r="E36" s="37">
         <v>3.12</v>
       </c>
-      <c r="F36" s="95">
+      <c r="F36" s="94">
         <v>5</v>
       </c>
       <c r="G36" s="20"/>
@@ -3860,19 +3859,19 @@
       </c>
       <c r="L36" s="51"/>
       <c r="M36" s="51"/>
-      <c r="N36" s="96">
+      <c r="N36" s="95">
         <v>23</v>
       </c>
-      <c r="O36" s="96">
+      <c r="O36" s="95">
         <v>22</v>
       </c>
-      <c r="P36" s="95">
+      <c r="P36" s="94">
         <v>3.46</v>
       </c>
       <c r="Q36" s="48">
         <v>228.36</v>
       </c>
-      <c r="R36" s="98" t="s">
+      <c r="R36" s="97" t="s">
         <v>10</v>
       </c>
     </row>
@@ -3892,7 +3891,7 @@
       <c r="E37" s="37">
         <v>3.72</v>
       </c>
-      <c r="F37" s="95">
+      <c r="F37" s="94">
         <v>4</v>
       </c>
       <c r="G37" s="20"/>
@@ -3910,19 +3909,19 @@
       </c>
       <c r="L37" s="51"/>
       <c r="M37" s="51"/>
-      <c r="N37" s="96">
+      <c r="N37" s="95">
         <v>23</v>
       </c>
-      <c r="O37" s="96">
+      <c r="O37" s="95">
         <v>20</v>
       </c>
-      <c r="P37" s="95">
+      <c r="P37" s="94">
         <v>4.6399999999999997</v>
       </c>
       <c r="Q37" s="48">
         <v>0</v>
       </c>
-      <c r="R37" s="99" t="s">
+      <c r="R37" s="98" t="s">
         <v>12</v>
       </c>
     </row>
@@ -3942,7 +3941,7 @@
       <c r="E38" s="37">
         <v>6.72</v>
       </c>
-      <c r="F38" s="95">
+      <c r="F38" s="94">
         <v>3</v>
       </c>
       <c r="G38" s="37">
@@ -3962,13 +3961,13 @@
       </c>
       <c r="L38" s="51"/>
       <c r="M38" s="51"/>
-      <c r="N38" s="96">
+      <c r="N38" s="95">
         <v>24</v>
       </c>
-      <c r="O38" s="96">
+      <c r="O38" s="95">
         <v>24</v>
       </c>
-      <c r="P38" s="95">
+      <c r="P38" s="94">
         <v>7</v>
       </c>
       <c r="Q38" s="48">
@@ -3994,7 +3993,7 @@
       <c r="E39" s="37">
         <v>4.92</v>
       </c>
-      <c r="F39" s="95">
+      <c r="F39" s="94">
         <v>1</v>
       </c>
       <c r="G39" s="37">
@@ -4014,19 +4013,19 @@
       </c>
       <c r="L39" s="51"/>
       <c r="M39" s="51"/>
-      <c r="N39" s="96">
+      <c r="N39" s="95">
         <v>23</v>
       </c>
-      <c r="O39" s="96">
+      <c r="O39" s="95">
         <v>24</v>
       </c>
-      <c r="P39" s="95">
+      <c r="P39" s="94">
         <v>5.13</v>
       </c>
       <c r="Q39" s="48">
         <v>990</v>
       </c>
-      <c r="R39" s="98" t="s">
+      <c r="R39" s="97" t="s">
         <v>10</v>
       </c>
     </row>
@@ -4046,7 +4045,7 @@
       <c r="E40" s="37">
         <v>5.08</v>
       </c>
-      <c r="F40" s="95">
+      <c r="F40" s="94">
         <v>2</v>
       </c>
       <c r="G40" s="20"/>
@@ -4064,13 +4063,13 @@
       </c>
       <c r="L40" s="51"/>
       <c r="M40" s="51"/>
-      <c r="N40" s="96">
+      <c r="N40" s="95">
         <v>21</v>
       </c>
-      <c r="O40" s="96">
+      <c r="O40" s="95">
         <v>17</v>
       </c>
-      <c r="P40" s="95">
+      <c r="P40" s="94">
         <v>7.47</v>
       </c>
       <c r="Q40" s="48">
@@ -4112,19 +4111,19 @@
       </c>
       <c r="L41" s="51"/>
       <c r="M41" s="51"/>
-      <c r="N41" s="96">
+      <c r="N41" s="95">
         <v>1</v>
       </c>
-      <c r="O41" s="96">
+      <c r="O41" s="95">
         <v>1</v>
       </c>
-      <c r="P41" s="95">
+      <c r="P41" s="94">
         <v>3</v>
       </c>
       <c r="Q41" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="R41" s="98" t="s">
+      <c r="R41" s="97" t="s">
         <v>10</v>
       </c>
     </row>
@@ -4144,7 +4143,7 @@
       <c r="E42" s="37">
         <v>4.84</v>
       </c>
-      <c r="F42" s="95">
+      <c r="F42" s="94">
         <v>6</v>
       </c>
       <c r="G42" s="37">
@@ -4164,19 +4163,19 @@
       </c>
       <c r="L42" s="51"/>
       <c r="M42" s="51"/>
-      <c r="N42" s="96">
+      <c r="N42" s="95">
         <v>23</v>
       </c>
-      <c r="O42" s="96">
+      <c r="O42" s="95">
         <v>23</v>
       </c>
-      <c r="P42" s="95">
+      <c r="P42" s="94">
         <v>5.21</v>
       </c>
       <c r="Q42" s="48">
         <v>319.36</v>
       </c>
-      <c r="R42" s="98" t="s">
+      <c r="R42" s="97" t="s">
         <v>10</v>
       </c>
     </row>
@@ -4196,7 +4195,7 @@
       <c r="E43" s="37">
         <v>4.96</v>
       </c>
-      <c r="F43" s="95">
+      <c r="F43" s="94">
         <v>3</v>
       </c>
       <c r="G43" s="37">
@@ -4216,19 +4215,19 @@
       </c>
       <c r="L43" s="51"/>
       <c r="M43" s="51"/>
-      <c r="N43" s="96">
+      <c r="N43" s="95">
         <v>24</v>
       </c>
-      <c r="O43" s="96">
+      <c r="O43" s="95">
         <v>22</v>
       </c>
-      <c r="P43" s="95">
+      <c r="P43" s="94">
         <v>5.64</v>
       </c>
       <c r="Q43" s="48">
         <v>1224</v>
       </c>
-      <c r="R43" s="98" t="s">
+      <c r="R43" s="97" t="s">
         <v>10</v>
       </c>
     </row>
@@ -4248,7 +4247,7 @@
       <c r="E44" s="37">
         <v>0.28000000000000003</v>
       </c>
-      <c r="F44" s="95">
+      <c r="F44" s="94">
         <v>1</v>
       </c>
       <c r="G44" s="20"/>
@@ -4266,13 +4265,13 @@
       </c>
       <c r="L44" s="51"/>
       <c r="M44" s="51"/>
-      <c r="N44" s="96">
+      <c r="N44" s="95">
         <v>24</v>
       </c>
-      <c r="O44" s="96">
+      <c r="O44" s="95">
         <v>18</v>
       </c>
-      <c r="P44" s="95">
+      <c r="P44" s="94">
         <v>0.35</v>
       </c>
       <c r="Q44" s="48">
@@ -4298,7 +4297,7 @@
       <c r="E45" s="37">
         <v>4.2</v>
       </c>
-      <c r="F45" s="95">
+      <c r="F45" s="94">
         <v>3</v>
       </c>
       <c r="G45" s="20"/>
@@ -4316,19 +4315,19 @@
       </c>
       <c r="L45" s="51"/>
       <c r="M45" s="51"/>
-      <c r="N45" s="96">
+      <c r="N45" s="95">
         <v>23</v>
       </c>
-      <c r="O45" s="96">
+      <c r="O45" s="95">
         <v>20</v>
       </c>
-      <c r="P45" s="95">
+      <c r="P45" s="94">
         <v>5.25</v>
       </c>
       <c r="Q45" s="48">
         <v>320</v>
       </c>
-      <c r="R45" s="98" t="s">
+      <c r="R45" s="97" t="s">
         <v>10</v>
       </c>
     </row>
@@ -4362,19 +4361,19 @@
       </c>
       <c r="L46" s="51"/>
       <c r="M46" s="51"/>
-      <c r="N46" s="96">
+      <c r="N46" s="95">
         <v>24</v>
       </c>
-      <c r="O46" s="96">
+      <c r="O46" s="95">
         <v>26</v>
       </c>
-      <c r="P46" s="95">
+      <c r="P46" s="94">
         <v>0.12</v>
       </c>
       <c r="Q46" s="48">
         <v>0</v>
       </c>
-      <c r="R46" s="99" t="s">
+      <c r="R46" s="98" t="s">
         <v>12</v>
       </c>
     </row>
@@ -4394,7 +4393,7 @@
       <c r="E47" s="37">
         <v>6.24</v>
       </c>
-      <c r="F47" s="95">
+      <c r="F47" s="94">
         <v>5</v>
       </c>
       <c r="G47" s="20"/>
@@ -4412,19 +4411,19 @@
       </c>
       <c r="L47" s="51"/>
       <c r="M47" s="51"/>
-      <c r="N47" s="96">
+      <c r="N47" s="95">
         <v>23</v>
       </c>
-      <c r="O47" s="96">
+      <c r="O47" s="95">
         <v>22</v>
       </c>
-      <c r="P47" s="95">
+      <c r="P47" s="94">
         <v>7.09</v>
       </c>
       <c r="Q47" s="48">
         <v>916</v>
       </c>
-      <c r="R47" s="98" t="s">
+      <c r="R47" s="97" t="s">
         <v>10</v>
       </c>
     </row>
@@ -4459,10 +4458,10 @@
       <c r="L48" s="51"/>
       <c r="M48" s="51"/>
       <c r="N48" s="51"/>
-      <c r="O48" s="96">
+      <c r="O48" s="95">
         <v>22</v>
       </c>
-      <c r="P48" s="95">
+      <c r="P48" s="94">
         <v>0.27</v>
       </c>
       <c r="Q48" s="41" t="s">
@@ -4488,7 +4487,7 @@
       <c r="E49" s="37">
         <v>3.8</v>
       </c>
-      <c r="F49" s="95">
+      <c r="F49" s="94">
         <v>1</v>
       </c>
       <c r="G49" s="20"/>
@@ -4507,10 +4506,10 @@
       <c r="L49" s="51"/>
       <c r="M49" s="51"/>
       <c r="N49" s="51"/>
-      <c r="O49" s="96">
+      <c r="O49" s="95">
         <v>25</v>
       </c>
-      <c r="P49" s="95">
+      <c r="P49" s="94">
         <v>3.8</v>
       </c>
       <c r="Q49" s="41" t="s">
@@ -4536,7 +4535,7 @@
       <c r="E50" s="37">
         <v>3.4</v>
       </c>
-      <c r="F50" s="95">
+      <c r="F50" s="94">
         <v>5</v>
       </c>
       <c r="G50" s="20"/>
@@ -4554,19 +4553,19 @@
       </c>
       <c r="L50" s="51"/>
       <c r="M50" s="51"/>
-      <c r="N50" s="96">
+      <c r="N50" s="95">
         <v>23</v>
       </c>
-      <c r="O50" s="96">
+      <c r="O50" s="95">
         <v>22</v>
       </c>
-      <c r="P50" s="95">
+      <c r="P50" s="94">
         <v>3.79</v>
       </c>
       <c r="Q50" s="48">
         <v>250.2</v>
       </c>
-      <c r="R50" s="98" t="s">
+      <c r="R50" s="97" t="s">
         <v>10</v>
       </c>
     </row>
@@ -4586,7 +4585,7 @@
       <c r="E51" s="37">
         <v>2.56</v>
       </c>
-      <c r="F51" s="95">
+      <c r="F51" s="94">
         <v>3</v>
       </c>
       <c r="G51" s="20"/>
@@ -4604,13 +4603,13 @@
       </c>
       <c r="L51" s="51"/>
       <c r="M51" s="51"/>
-      <c r="N51" s="96">
+      <c r="N51" s="95">
         <v>21</v>
       </c>
-      <c r="O51" s="96">
+      <c r="O51" s="95">
         <v>20</v>
       </c>
-      <c r="P51" s="95">
+      <c r="P51" s="94">
         <v>3.18</v>
       </c>
       <c r="Q51" s="48">
@@ -4652,13 +4651,13 @@
       </c>
       <c r="L52" s="51"/>
       <c r="M52" s="51"/>
-      <c r="N52" s="96">
+      <c r="N52" s="95">
         <v>23</v>
       </c>
-      <c r="O52" s="96">
+      <c r="O52" s="95">
         <v>9</v>
       </c>
-      <c r="P52" s="95">
+      <c r="P52" s="94">
         <v>1.89</v>
       </c>
       <c r="Q52" s="48">
@@ -4684,7 +4683,7 @@
       <c r="E53" s="37">
         <v>4.28</v>
       </c>
-      <c r="F53" s="95">
+      <c r="F53" s="94">
         <v>5</v>
       </c>
       <c r="G53" s="20"/>
@@ -4703,10 +4702,10 @@
       <c r="L53" s="51"/>
       <c r="M53" s="51"/>
       <c r="N53" s="51"/>
-      <c r="O53" s="96">
+      <c r="O53" s="95">
         <v>25</v>
       </c>
-      <c r="P53" s="95">
+      <c r="P53" s="94">
         <v>4.25</v>
       </c>
       <c r="Q53" s="49" t="s">
@@ -4732,7 +4731,7 @@
       <c r="E54" s="37">
         <v>3.88</v>
       </c>
-      <c r="F54" s="95">
+      <c r="F54" s="94">
         <v>5</v>
       </c>
       <c r="G54" s="20"/>
@@ -4750,19 +4749,19 @@
       </c>
       <c r="L54" s="51"/>
       <c r="M54" s="51"/>
-      <c r="N54" s="96">
+      <c r="N54" s="95">
         <v>24</v>
       </c>
-      <c r="O54" s="96">
+      <c r="O54" s="95">
         <v>23</v>
       </c>
-      <c r="P54" s="95">
+      <c r="P54" s="94">
         <v>4.17</v>
       </c>
       <c r="Q54" s="48">
         <v>590.79999999999995</v>
       </c>
-      <c r="R54" s="97" t="s">
+      <c r="R54" s="96" t="s">
         <v>196</v>
       </c>
     </row>
@@ -4782,7 +4781,7 @@
       <c r="E55" s="37">
         <v>2.96</v>
       </c>
-      <c r="F55" s="95">
+      <c r="F55" s="94">
         <v>2</v>
       </c>
       <c r="G55" s="20"/>
@@ -4800,19 +4799,19 @@
       </c>
       <c r="L55" s="51"/>
       <c r="M55" s="51"/>
-      <c r="N55" s="96">
+      <c r="N55" s="95">
         <v>23</v>
       </c>
-      <c r="O55" s="96">
+      <c r="O55" s="95">
         <v>22</v>
       </c>
-      <c r="P55" s="95">
+      <c r="P55" s="94">
         <v>3.36</v>
       </c>
       <c r="Q55" s="48">
         <v>0</v>
       </c>
-      <c r="R55" s="99" t="s">
+      <c r="R55" s="98" t="s">
         <v>12</v>
       </c>
     </row>
@@ -4832,7 +4831,7 @@
       <c r="E56" s="37">
         <v>3.8</v>
       </c>
-      <c r="F56" s="95">
+      <c r="F56" s="94">
         <v>1</v>
       </c>
       <c r="G56" s="20"/>
@@ -4850,19 +4849,19 @@
       </c>
       <c r="L56" s="51"/>
       <c r="M56" s="51"/>
-      <c r="N56" s="96">
+      <c r="N56" s="95">
         <v>24</v>
       </c>
-      <c r="O56" s="96">
+      <c r="O56" s="95">
         <v>21</v>
       </c>
-      <c r="P56" s="95">
+      <c r="P56" s="94">
         <v>4.5199999999999996</v>
       </c>
       <c r="Q56" s="48">
         <v>0</v>
       </c>
-      <c r="R56" s="99" t="s">
+      <c r="R56" s="98" t="s">
         <v>12</v>
       </c>
     </row>
@@ -4882,7 +4881,7 @@
       <c r="E57" s="37">
         <v>2.68</v>
       </c>
-      <c r="F57" s="95">
+      <c r="F57" s="94">
         <v>4</v>
       </c>
       <c r="G57" s="20"/>
@@ -4900,19 +4899,19 @@
       </c>
       <c r="L57" s="51"/>
       <c r="M57" s="51"/>
-      <c r="N57" s="96">
+      <c r="N57" s="95">
         <v>23</v>
       </c>
-      <c r="O57" s="96">
+      <c r="O57" s="95">
         <v>19</v>
       </c>
-      <c r="P57" s="95">
+      <c r="P57" s="94">
         <v>3.46</v>
       </c>
       <c r="Q57" s="48">
         <v>197.04</v>
       </c>
-      <c r="R57" s="98" t="s">
+      <c r="R57" s="97" t="s">
         <v>10</v>
       </c>
     </row>
@@ -4948,19 +4947,19 @@
       </c>
       <c r="L58" s="51"/>
       <c r="M58" s="51"/>
-      <c r="N58" s="96">
+      <c r="N58" s="95">
         <v>23</v>
       </c>
-      <c r="O58" s="96">
+      <c r="O58" s="95">
         <v>19</v>
       </c>
-      <c r="P58" s="95">
+      <c r="P58" s="94">
         <v>3.16</v>
       </c>
       <c r="Q58" s="48">
         <v>0</v>
       </c>
-      <c r="R58" s="99" t="s">
+      <c r="R58" s="98" t="s">
         <v>12</v>
       </c>
     </row>
@@ -4999,16 +4998,16 @@
       <c r="L59" s="52"/>
       <c r="M59" s="52"/>
       <c r="N59" s="51"/>
-      <c r="O59" s="96">
+      <c r="O59" s="95">
         <v>23</v>
       </c>
-      <c r="P59" s="95">
+      <c r="P59" s="94">
         <v>1.35</v>
       </c>
       <c r="Q59" s="48">
         <v>93</v>
       </c>
-      <c r="R59" s="98" t="s">
+      <c r="R59" s="97" t="s">
         <v>10</v>
       </c>
     </row>
@@ -5028,7 +5027,7 @@
       <c r="E60" s="37">
         <v>5.12</v>
       </c>
-      <c r="F60" s="95">
+      <c r="F60" s="94">
         <v>9</v>
       </c>
       <c r="G60" s="20"/>
@@ -5046,19 +5045,19 @@
       </c>
       <c r="L60" s="52"/>
       <c r="M60" s="52"/>
-      <c r="N60" s="96">
+      <c r="N60" s="95">
         <v>24</v>
       </c>
-      <c r="O60" s="96">
+      <c r="O60" s="95">
         <v>22</v>
       </c>
-      <c r="P60" s="95">
+      <c r="P60" s="94">
         <v>5.64</v>
       </c>
       <c r="Q60" s="48">
         <v>684.72</v>
       </c>
-      <c r="R60" s="98" t="s">
+      <c r="R60" s="97" t="s">
         <v>10</v>
       </c>
     </row>
@@ -5078,7 +5077,7 @@
       <c r="E61" s="37">
         <v>3.88</v>
       </c>
-      <c r="F61" s="95">
+      <c r="F61" s="94">
         <v>2</v>
       </c>
       <c r="G61" s="20"/>
@@ -5096,19 +5095,19 @@
       </c>
       <c r="L61" s="52"/>
       <c r="M61" s="52"/>
-      <c r="N61" s="96">
+      <c r="N61" s="95">
         <v>24</v>
       </c>
-      <c r="O61" s="96">
+      <c r="O61" s="95">
         <v>21</v>
       </c>
-      <c r="P61" s="95">
+      <c r="P61" s="94">
         <v>4.62</v>
       </c>
       <c r="Q61" s="48">
         <v>0</v>
       </c>
-      <c r="R61" s="99" t="s">
+      <c r="R61" s="98" t="s">
         <v>12</v>
       </c>
     </row>
@@ -5128,7 +5127,7 @@
       <c r="E62" s="37">
         <v>3.92</v>
       </c>
-      <c r="F62" s="95">
+      <c r="F62" s="94">
         <v>4</v>
       </c>
       <c r="G62" s="20"/>
@@ -5146,19 +5145,19 @@
       </c>
       <c r="L62" s="52"/>
       <c r="M62" s="52"/>
-      <c r="N62" s="96">
+      <c r="N62" s="95">
         <v>24</v>
       </c>
-      <c r="O62" s="96">
+      <c r="O62" s="95">
         <v>21</v>
       </c>
-      <c r="P62" s="95">
+      <c r="P62" s="94">
         <v>4.66</v>
       </c>
       <c r="Q62" s="48">
         <v>0</v>
       </c>
-      <c r="R62" s="99" t="s">
+      <c r="R62" s="98" t="s">
         <v>12</v>
       </c>
     </row>
@@ -5178,7 +5177,7 @@
       <c r="E63" s="37">
         <v>4.12</v>
       </c>
-      <c r="F63" s="95">
+      <c r="F63" s="94">
         <v>5</v>
       </c>
       <c r="G63" s="20"/>
@@ -5196,19 +5195,19 @@
       </c>
       <c r="L63" s="52"/>
       <c r="M63" s="52"/>
-      <c r="N63" s="96">
+      <c r="N63" s="95">
         <v>23</v>
       </c>
-      <c r="O63" s="96">
+      <c r="O63" s="95">
         <v>22</v>
       </c>
-      <c r="P63" s="95">
+      <c r="P63" s="94">
         <v>4.6399999999999997</v>
       </c>
       <c r="Q63" s="48">
         <v>0</v>
       </c>
-      <c r="R63" s="99" t="s">
+      <c r="R63" s="98" t="s">
         <v>12</v>
       </c>
     </row>
@@ -5228,7 +5227,7 @@
       <c r="E64" s="37">
         <v>4.4400000000000004</v>
       </c>
-      <c r="F64" s="95">
+      <c r="F64" s="94">
         <v>4</v>
       </c>
       <c r="G64" s="20"/>
@@ -5246,19 +5245,19 @@
       </c>
       <c r="L64" s="52"/>
       <c r="M64" s="52"/>
-      <c r="N64" s="96">
+      <c r="N64" s="95">
         <v>24</v>
       </c>
-      <c r="O64" s="96">
+      <c r="O64" s="95">
         <v>24</v>
       </c>
-      <c r="P64" s="95">
+      <c r="P64" s="94">
         <v>4.63</v>
       </c>
       <c r="Q64" s="48">
         <v>360</v>
       </c>
-      <c r="R64" s="98" t="s">
+      <c r="R64" s="97" t="s">
         <v>10</v>
       </c>
     </row>
@@ -5278,7 +5277,7 @@
       <c r="E65" s="37">
         <v>3.28</v>
       </c>
-      <c r="F65" s="95">
+      <c r="F65" s="94">
         <v>1</v>
       </c>
       <c r="G65" s="37">
@@ -5298,19 +5297,19 @@
       </c>
       <c r="L65" s="52"/>
       <c r="M65" s="52"/>
-      <c r="N65" s="96">
+      <c r="N65" s="95">
         <v>23</v>
       </c>
-      <c r="O65" s="96">
+      <c r="O65" s="95">
         <v>23</v>
       </c>
-      <c r="P65" s="95">
+      <c r="P65" s="94">
         <v>3.57</v>
       </c>
       <c r="Q65" s="48">
         <v>0</v>
       </c>
-      <c r="R65" s="99" t="s">
+      <c r="R65" s="98" t="s">
         <v>12</v>
       </c>
     </row>
@@ -5330,7 +5329,7 @@
       <c r="E66" s="37">
         <v>2.96</v>
       </c>
-      <c r="F66" s="95">
+      <c r="F66" s="94">
         <v>5</v>
       </c>
       <c r="G66" s="20"/>
@@ -5348,19 +5347,19 @@
       </c>
       <c r="L66" s="52"/>
       <c r="M66" s="52"/>
-      <c r="N66" s="96">
+      <c r="N66" s="95">
         <v>24</v>
       </c>
-      <c r="O66" s="96">
+      <c r="O66" s="95">
         <v>21</v>
       </c>
-      <c r="P66" s="95">
+      <c r="P66" s="94">
         <v>3.43</v>
       </c>
       <c r="Q66" s="48">
         <v>0</v>
       </c>
-      <c r="R66" s="99" t="s">
+      <c r="R66" s="98" t="s">
         <v>12</v>
       </c>
     </row>
@@ -5380,7 +5379,7 @@
       <c r="E67" s="37">
         <v>4.84</v>
       </c>
-      <c r="F67" s="95">
+      <c r="F67" s="94">
         <v>5</v>
       </c>
       <c r="G67" s="20"/>
@@ -5398,19 +5397,19 @@
       </c>
       <c r="L67" s="52"/>
       <c r="M67" s="52"/>
-      <c r="N67" s="96">
+      <c r="N67" s="95">
         <v>24</v>
       </c>
-      <c r="O67" s="96">
+      <c r="O67" s="95">
         <v>22</v>
       </c>
-      <c r="P67" s="95">
+      <c r="P67" s="94">
         <v>5.49</v>
       </c>
       <c r="Q67" s="48">
         <v>343.36</v>
       </c>
-      <c r="R67" s="98" t="s">
+      <c r="R67" s="97" t="s">
         <v>10</v>
       </c>
     </row>
@@ -5445,10 +5444,10 @@
       <c r="L68" s="52"/>
       <c r="M68" s="52"/>
       <c r="N68" s="51"/>
-      <c r="O68" s="96">
+      <c r="O68" s="95">
         <v>20</v>
       </c>
-      <c r="P68" s="95">
+      <c r="P68" s="94">
         <v>0.1</v>
       </c>
       <c r="Q68" s="41" t="s">
@@ -5491,10 +5490,10 @@
       <c r="L69" s="52"/>
       <c r="M69" s="52"/>
       <c r="N69" s="51"/>
-      <c r="O69" s="96">
+      <c r="O69" s="95">
         <v>26</v>
       </c>
-      <c r="P69" s="95">
+      <c r="P69" s="94">
         <v>2.69</v>
       </c>
       <c r="Q69" s="41" t="s">
@@ -5520,7 +5519,7 @@
       <c r="E70" s="37">
         <v>2.84</v>
       </c>
-      <c r="F70" s="95">
+      <c r="F70" s="94">
         <v>2</v>
       </c>
       <c r="G70" s="20"/>
@@ -5538,19 +5537,19 @@
       </c>
       <c r="L70" s="52"/>
       <c r="M70" s="52"/>
-      <c r="N70" s="96">
+      <c r="N70" s="95">
         <v>23</v>
       </c>
-      <c r="O70" s="96">
+      <c r="O70" s="95">
         <v>21</v>
       </c>
-      <c r="P70" s="95">
+      <c r="P70" s="94">
         <v>3.38</v>
       </c>
       <c r="Q70" s="48">
         <v>0</v>
       </c>
-      <c r="R70" s="99" t="s">
+      <c r="R70" s="98" t="s">
         <v>12</v>
       </c>
     </row>
@@ -5570,7 +5569,7 @@
       <c r="E71" s="37">
         <v>4.6399999999999997</v>
       </c>
-      <c r="F71" s="95">
+      <c r="F71" s="94">
         <v>6</v>
       </c>
       <c r="G71" s="37">
@@ -5590,19 +5589,19 @@
       </c>
       <c r="L71" s="52"/>
       <c r="M71" s="52"/>
-      <c r="N71" s="96">
+      <c r="N71" s="95">
         <v>24</v>
       </c>
-      <c r="O71" s="96">
+      <c r="O71" s="95">
         <v>23</v>
       </c>
-      <c r="P71" s="95">
+      <c r="P71" s="94">
         <v>4.9800000000000004</v>
       </c>
       <c r="Q71" s="48">
         <v>966.84</v>
       </c>
-      <c r="R71" s="98" t="s">
+      <c r="R71" s="97" t="s">
         <v>10</v>
       </c>
     </row>
@@ -5622,7 +5621,7 @@
       <c r="E72" s="37">
         <v>3.6</v>
       </c>
-      <c r="F72" s="95">
+      <c r="F72" s="94">
         <v>6</v>
       </c>
       <c r="G72" s="20"/>
@@ -5640,19 +5639,19 @@
       </c>
       <c r="L72" s="52"/>
       <c r="M72" s="52"/>
-      <c r="N72" s="96">
+      <c r="N72" s="95">
         <v>24</v>
       </c>
-      <c r="O72" s="96">
+      <c r="O72" s="95">
         <v>23</v>
       </c>
-      <c r="P72" s="95">
+      <c r="P72" s="94">
         <v>3.81</v>
       </c>
       <c r="Q72" s="48">
         <v>0</v>
       </c>
-      <c r="R72" s="99" t="s">
+      <c r="R72" s="98" t="s">
         <v>12</v>
       </c>
     </row>
@@ -5672,7 +5671,7 @@
       <c r="E73" s="37">
         <v>4.12</v>
       </c>
-      <c r="F73" s="95">
+      <c r="F73" s="94">
         <v>1</v>
       </c>
       <c r="G73" s="20"/>
@@ -5691,10 +5690,10 @@
       <c r="L73" s="52"/>
       <c r="M73" s="52"/>
       <c r="N73" s="51"/>
-      <c r="O73" s="96">
+      <c r="O73" s="95">
         <v>23</v>
       </c>
-      <c r="P73" s="95">
+      <c r="P73" s="94">
         <v>4.4800000000000004</v>
       </c>
       <c r="Q73" s="41" t="s">
@@ -5737,10 +5736,10 @@
       <c r="L74" s="52"/>
       <c r="M74" s="52"/>
       <c r="N74" s="51"/>
-      <c r="O74" s="96">
+      <c r="O74" s="95">
         <v>23</v>
       </c>
-      <c r="P74" s="95">
+      <c r="P74" s="94">
         <v>3</v>
       </c>
       <c r="Q74" s="41" t="s">
@@ -5785,16 +5784,16 @@
       <c r="L75" s="52"/>
       <c r="M75" s="52"/>
       <c r="N75" s="51"/>
-      <c r="O75" s="96">
+      <c r="O75" s="95">
         <v>24</v>
       </c>
-      <c r="P75" s="95">
+      <c r="P75" s="94">
         <v>1.63</v>
       </c>
       <c r="Q75" s="48">
         <v>117</v>
       </c>
-      <c r="R75" s="98" t="s">
+      <c r="R75" s="97" t="s">
         <v>10</v>
       </c>
     </row>
@@ -5814,7 +5813,7 @@
       <c r="E76" s="37">
         <v>1.28</v>
       </c>
-      <c r="F76" s="95">
+      <c r="F76" s="94">
         <v>1</v>
       </c>
       <c r="G76" s="20"/>
@@ -5832,19 +5831,19 @@
       </c>
       <c r="L76" s="52"/>
       <c r="M76" s="52"/>
-      <c r="N76" s="96">
+      <c r="N76" s="95">
         <v>8</v>
       </c>
-      <c r="O76" s="96">
+      <c r="O76" s="95">
         <v>7</v>
       </c>
-      <c r="P76" s="95">
+      <c r="P76" s="94">
         <v>4.57</v>
       </c>
       <c r="Q76" s="48">
         <v>0</v>
       </c>
-      <c r="R76" s="99" t="s">
+      <c r="R76" s="98" t="s">
         <v>12</v>
       </c>
     </row>
@@ -5864,7 +5863,7 @@
       <c r="E77" s="37">
         <v>3.56</v>
       </c>
-      <c r="F77" s="95">
+      <c r="F77" s="94">
         <v>1</v>
       </c>
       <c r="G77" s="20"/>
@@ -5883,16 +5882,16 @@
       <c r="L77" s="52"/>
       <c r="M77" s="52"/>
       <c r="N77" s="51"/>
-      <c r="O77" s="96">
+      <c r="O77" s="95">
         <v>21</v>
       </c>
-      <c r="P77" s="95">
+      <c r="P77" s="94">
         <v>4.24</v>
       </c>
       <c r="Q77" s="48">
         <v>138.94</v>
       </c>
-      <c r="R77" s="98" t="s">
+      <c r="R77" s="97" t="s">
         <v>10</v>
       </c>
     </row>
@@ -5912,7 +5911,7 @@
       <c r="E78" s="37">
         <v>3.76</v>
       </c>
-      <c r="F78" s="95">
+      <c r="F78" s="94">
         <v>4</v>
       </c>
       <c r="G78" s="37">
@@ -5932,19 +5931,19 @@
       </c>
       <c r="L78" s="52"/>
       <c r="M78" s="52"/>
-      <c r="N78" s="96">
+      <c r="N78" s="95">
         <v>24</v>
       </c>
-      <c r="O78" s="96">
+      <c r="O78" s="95">
         <v>21</v>
       </c>
-      <c r="P78" s="95">
+      <c r="P78" s="94">
         <v>4.46</v>
       </c>
       <c r="Q78" s="48">
         <v>339.04</v>
       </c>
-      <c r="R78" s="98" t="s">
+      <c r="R78" s="97" t="s">
         <v>10</v>
       </c>
     </row>
@@ -5964,7 +5963,7 @@
       <c r="E79" s="37">
         <v>4.28</v>
       </c>
-      <c r="F79" s="95">
+      <c r="F79" s="94">
         <v>1</v>
       </c>
       <c r="G79" s="20"/>
@@ -5982,13 +5981,13 @@
       </c>
       <c r="L79" s="52"/>
       <c r="M79" s="52"/>
-      <c r="N79" s="96">
+      <c r="N79" s="95">
         <v>23</v>
       </c>
-      <c r="O79" s="96">
+      <c r="O79" s="95">
         <v>22</v>
       </c>
-      <c r="P79" s="95">
+      <c r="P79" s="94">
         <v>4.8600000000000003</v>
       </c>
       <c r="Q79" s="48">
@@ -6014,7 +6013,7 @@
       <c r="E80" s="37">
         <v>3.6</v>
       </c>
-      <c r="F80" s="95">
+      <c r="F80" s="94">
         <v>2</v>
       </c>
       <c r="G80" s="20"/>
@@ -6032,19 +6031,19 @@
       </c>
       <c r="L80" s="52"/>
       <c r="M80" s="52"/>
-      <c r="N80" s="96">
+      <c r="N80" s="95">
         <v>24</v>
       </c>
-      <c r="O80" s="96">
+      <c r="O80" s="95">
         <v>24</v>
       </c>
-      <c r="P80" s="95">
+      <c r="P80" s="94">
         <v>3.75</v>
       </c>
       <c r="Q80" s="48">
         <v>270</v>
       </c>
-      <c r="R80" s="98" t="s">
+      <c r="R80" s="97" t="s">
         <v>10</v>
       </c>
     </row>
@@ -6064,7 +6063,7 @@
       <c r="E81" s="37">
         <v>3.76</v>
       </c>
-      <c r="F81" s="95">
+      <c r="F81" s="94">
         <v>4</v>
       </c>
       <c r="G81" s="37">
@@ -6084,19 +6083,19 @@
       </c>
       <c r="L81" s="52"/>
       <c r="M81" s="52"/>
-      <c r="N81" s="96">
+      <c r="N81" s="95">
         <v>23</v>
       </c>
-      <c r="O81" s="96">
+      <c r="O81" s="95">
         <v>22</v>
       </c>
-      <c r="P81" s="95">
+      <c r="P81" s="94">
         <v>4.26</v>
       </c>
       <c r="Q81" s="48">
         <v>0</v>
       </c>
-      <c r="R81" s="99" t="s">
+      <c r="R81" s="98" t="s">
         <v>12</v>
       </c>
     </row>
@@ -6116,7 +6115,7 @@
       <c r="E82" s="37">
         <v>2.72</v>
       </c>
-      <c r="F82" s="95">
+      <c r="F82" s="94">
         <v>6</v>
       </c>
       <c r="G82" s="20"/>
@@ -6134,41 +6133,41 @@
       </c>
       <c r="L82" s="52"/>
       <c r="M82" s="52"/>
-      <c r="N82" s="96">
+      <c r="N82" s="95">
         <v>24</v>
       </c>
-      <c r="O82" s="96">
+      <c r="O82" s="95">
         <v>21</v>
       </c>
-      <c r="P82" s="95">
+      <c r="P82" s="94">
         <v>3.08</v>
       </c>
       <c r="Q82" s="48">
         <v>0</v>
       </c>
-      <c r="R82" s="99" t="s">
+      <c r="R82" s="98" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="83" spans="1:18" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A83" s="21"/>
       <c r="B83" s="20"/>
-      <c r="C83" s="103"/>
-      <c r="D83" s="103"/>
-      <c r="E83" s="103"/>
-      <c r="F83" s="103"/>
-      <c r="G83" s="103"/>
-      <c r="H83" s="103"/>
-      <c r="I83" s="103"/>
-      <c r="J83" s="103"/>
-      <c r="K83" s="103"/>
+      <c r="C83" s="102"/>
+      <c r="D83" s="102"/>
+      <c r="E83" s="102"/>
+      <c r="F83" s="102"/>
+      <c r="G83" s="102"/>
+      <c r="H83" s="102"/>
+      <c r="I83" s="102"/>
+      <c r="J83" s="102"/>
+      <c r="K83" s="102"/>
       <c r="L83" s="30"/>
       <c r="M83" s="30"/>
       <c r="N83" s="30"/>
       <c r="O83" s="30"/>
       <c r="P83" s="30"/>
       <c r="Q83" s="30"/>
-      <c r="R83" s="103"/>
+      <c r="R83" s="102"/>
     </row>
     <row r="84" spans="1:18" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A84" s="22"/>
@@ -6180,15 +6179,15 @@
       <c r="G84" s="38"/>
       <c r="H84" s="38"/>
       <c r="I84" s="38"/>
-      <c r="J84" s="103"/>
-      <c r="K84" s="103"/>
+      <c r="J84" s="102"/>
+      <c r="K84" s="102"/>
       <c r="L84" s="30"/>
       <c r="M84" s="30"/>
       <c r="N84" s="30"/>
       <c r="O84" s="30"/>
       <c r="P84" s="30"/>
       <c r="Q84" s="30"/>
-      <c r="R84" s="103"/>
+      <c r="R84" s="102"/>
     </row>
     <row r="85" spans="1:18" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A85" s="104" t="s">
@@ -6218,15 +6217,15 @@
       <c r="I85" s="40" t="s">
         <v>96</v>
       </c>
-      <c r="J85" s="103"/>
-      <c r="K85" s="103"/>
+      <c r="J85" s="102"/>
+      <c r="K85" s="102"/>
       <c r="L85" s="30"/>
       <c r="M85" s="30"/>
       <c r="N85" s="30"/>
       <c r="O85" s="30"/>
       <c r="P85" s="30"/>
       <c r="Q85" s="30"/>
-      <c r="R85" s="103"/>
+      <c r="R85" s="102"/>
     </row>
     <row r="86" spans="1:18" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A86" s="105"/>
@@ -6250,8 +6249,8 @@
       <c r="I86" s="42">
         <v>101.71</v>
       </c>
-      <c r="J86" s="103"/>
-      <c r="K86" s="103"/>
+      <c r="J86" s="102"/>
+      <c r="K86" s="102"/>
       <c r="L86" s="30"/>
       <c r="M86" s="30"/>
       <c r="N86" s="30"/>
@@ -6280,8 +6279,8 @@
       <c r="I87" s="42">
         <v>199.75</v>
       </c>
-      <c r="J87" s="103"/>
-      <c r="K87" s="103"/>
+      <c r="J87" s="102"/>
+      <c r="K87" s="102"/>
       <c r="L87" s="30"/>
       <c r="M87" s="30"/>
       <c r="N87" s="30"/>
@@ -6310,8 +6309,8 @@
       <c r="I88" s="42">
         <v>51</v>
       </c>
-      <c r="J88" s="103"/>
-      <c r="K88" s="103"/>
+      <c r="J88" s="102"/>
+      <c r="K88" s="102"/>
       <c r="L88" s="30"/>
       <c r="M88" s="30"/>
       <c r="N88" s="30"/>
@@ -6340,8 +6339,8 @@
       <c r="I89" s="42">
         <v>203.4</v>
       </c>
-      <c r="J89" s="103"/>
-      <c r="K89" s="103"/>
+      <c r="J89" s="102"/>
+      <c r="K89" s="102"/>
       <c r="L89" s="30"/>
       <c r="M89" s="30"/>
       <c r="N89" s="30"/>
@@ -6370,8 +6369,8 @@
       <c r="I90" s="42">
         <v>284.39999999999998</v>
       </c>
-      <c r="J90" s="103"/>
-      <c r="K90" s="103"/>
+      <c r="J90" s="102"/>
+      <c r="K90" s="102"/>
       <c r="L90" s="30"/>
       <c r="M90" s="30"/>
       <c r="N90" s="30"/>
@@ -6400,8 +6399,8 @@
       <c r="I91" s="42">
         <v>367.2</v>
       </c>
-      <c r="J91" s="103"/>
-      <c r="K91" s="103"/>
+      <c r="J91" s="102"/>
+      <c r="K91" s="102"/>
       <c r="L91" s="30"/>
       <c r="M91" s="30"/>
       <c r="N91" s="30"/>
@@ -6426,8 +6425,8 @@
       <c r="I92" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="J92" s="103"/>
-      <c r="K92" s="103"/>
+      <c r="J92" s="102"/>
+      <c r="K92" s="102"/>
       <c r="L92" s="30"/>
       <c r="M92" s="30"/>
       <c r="N92" s="30"/>
@@ -6471,7 +6470,7 @@
       <c r="B94" s="24" t="s">
         <v>197</v>
       </c>
-      <c r="C94" s="100" t="s">
+      <c r="C94" s="99" t="s">
         <v>39</v>
       </c>
       <c r="D94" s="20"/>
@@ -6489,7 +6488,7 @@
       <c r="J94" s="43"/>
       <c r="K94" s="43"/>
       <c r="L94" s="25"/>
-      <c r="M94" s="103"/>
+      <c r="M94" s="102"/>
       <c r="N94" s="25"/>
       <c r="O94" s="25"/>
       <c r="P94" s="25"/>
@@ -6506,8 +6505,8 @@
       <c r="G95" s="20"/>
       <c r="H95" s="20"/>
       <c r="I95" s="20"/>
-      <c r="J95" s="103"/>
-      <c r="K95" s="103"/>
+      <c r="J95" s="102"/>
+      <c r="K95" s="102"/>
       <c r="L95" s="30"/>
       <c r="M95" s="30"/>
       <c r="N95" s="30"/>
@@ -6526,7 +6525,7 @@
       </c>
       <c r="D96" s="20"/>
       <c r="E96" s="20"/>
-      <c r="F96" s="101">
+      <c r="F96" s="100">
         <v>2</v>
       </c>
       <c r="G96" s="41">
@@ -6538,8 +6537,8 @@
       <c r="I96" s="42">
         <v>182.78</v>
       </c>
-      <c r="J96" s="103"/>
-      <c r="K96" s="103"/>
+      <c r="J96" s="102"/>
+      <c r="K96" s="102"/>
       <c r="L96" s="30"/>
       <c r="M96" s="30"/>
       <c r="N96" s="30"/>
@@ -6568,8 +6567,8 @@
       <c r="I97" s="42">
         <v>290.05</v>
       </c>
-      <c r="J97" s="103"/>
-      <c r="K97" s="103"/>
+      <c r="J97" s="102"/>
+      <c r="K97" s="102"/>
       <c r="L97" s="30"/>
       <c r="M97" s="30"/>
       <c r="N97" s="30"/>
@@ -6598,8 +6597,8 @@
       <c r="I98" s="41">
         <v>83.1</v>
       </c>
-      <c r="J98" s="103"/>
-      <c r="K98" s="103"/>
+      <c r="J98" s="102"/>
+      <c r="K98" s="102"/>
       <c r="L98" s="30"/>
       <c r="M98" s="30"/>
       <c r="N98" s="30"/>
@@ -6610,7 +6609,7 @@
     </row>
     <row r="99" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="25"/>
-      <c r="B99" s="103"/>
+      <c r="B99" s="102"/>
       <c r="C99" s="25"/>
       <c r="D99" s="43"/>
       <c r="E99" s="43"/>
@@ -6650,8 +6649,8 @@
       <c r="I100" s="45" t="s">
         <v>96</v>
       </c>
-      <c r="J100" s="103"/>
-      <c r="K100" s="103"/>
+      <c r="J100" s="102"/>
+      <c r="K100" s="102"/>
       <c r="L100" s="30"/>
       <c r="M100" s="30"/>
       <c r="N100" s="30"/>
@@ -6682,10 +6681,10 @@
       <c r="I101" s="42">
         <v>260</v>
       </c>
-      <c r="J101" s="102" t="s">
+      <c r="J101" s="101" t="s">
         <v>198</v>
       </c>
-      <c r="K101" s="103"/>
+      <c r="K101" s="102"/>
       <c r="L101" s="30"/>
       <c r="M101" s="30"/>
       <c r="N101" s="30"/>
@@ -6714,8 +6713,8 @@
       <c r="I102" s="42">
         <v>260</v>
       </c>
-      <c r="J102" s="103"/>
-      <c r="K102" s="103"/>
+      <c r="J102" s="102"/>
+      <c r="K102" s="102"/>
       <c r="L102" s="30"/>
       <c r="M102" s="30"/>
       <c r="N102" s="30"/>
@@ -6744,8 +6743,8 @@
       <c r="I103" s="42">
         <v>280</v>
       </c>
-      <c r="J103" s="103"/>
-      <c r="K103" s="103"/>
+      <c r="J103" s="102"/>
+      <c r="K103" s="102"/>
       <c r="L103" s="30"/>
       <c r="M103" s="30"/>
       <c r="N103" s="30"/>
@@ -6776,8 +6775,8 @@
       <c r="I104" s="42">
         <v>260</v>
       </c>
-      <c r="J104" s="103"/>
-      <c r="K104" s="103"/>
+      <c r="J104" s="102"/>
+      <c r="K104" s="102"/>
       <c r="L104" s="30"/>
       <c r="M104" s="30"/>
       <c r="N104" s="30"/>
@@ -6806,8 +6805,8 @@
       <c r="I105" s="42">
         <v>250</v>
       </c>
-      <c r="J105" s="103"/>
-      <c r="K105" s="103"/>
+      <c r="J105" s="102"/>
+      <c r="K105" s="102"/>
       <c r="L105" s="30"/>
       <c r="M105" s="30"/>
       <c r="N105" s="30"/>
@@ -6836,8 +6835,8 @@
       <c r="I106" s="42">
         <v>140</v>
       </c>
-      <c r="J106" s="103"/>
-      <c r="K106" s="103"/>
+      <c r="J106" s="102"/>
+      <c r="K106" s="102"/>
       <c r="L106" s="30"/>
       <c r="M106" s="30"/>
       <c r="N106" s="30"/>
@@ -6866,8 +6865,8 @@
       <c r="I107" s="42">
         <v>170</v>
       </c>
-      <c r="J107" s="103"/>
-      <c r="K107" s="103"/>
+      <c r="J107" s="102"/>
+      <c r="K107" s="102"/>
       <c r="L107" s="30"/>
       <c r="M107" s="30"/>
       <c r="N107" s="30"/>
@@ -6896,8 +6895,8 @@
       <c r="I108" s="42">
         <v>140</v>
       </c>
-      <c r="J108" s="103"/>
-      <c r="K108" s="103"/>
+      <c r="J108" s="102"/>
+      <c r="K108" s="102"/>
       <c r="L108" s="30"/>
       <c r="M108" s="30"/>
       <c r="N108" s="30"/>
@@ -6926,8 +6925,8 @@
       <c r="I109" s="42">
         <v>140</v>
       </c>
-      <c r="J109" s="103"/>
-      <c r="K109" s="103"/>
+      <c r="J109" s="102"/>
+      <c r="K109" s="102"/>
       <c r="L109" s="30"/>
       <c r="M109" s="30"/>
       <c r="N109" s="30"/>
@@ -6956,8 +6955,8 @@
       <c r="I110" s="42">
         <v>140</v>
       </c>
-      <c r="J110" s="103"/>
-      <c r="K110" s="103"/>
+      <c r="J110" s="102"/>
+      <c r="K110" s="102"/>
       <c r="L110" s="30"/>
       <c r="M110" s="30"/>
       <c r="N110" s="30"/>
@@ -6986,8 +6985,8 @@
       <c r="I111" s="42">
         <v>140</v>
       </c>
-      <c r="J111" s="103"/>
-      <c r="K111" s="103"/>
+      <c r="J111" s="102"/>
+      <c r="K111" s="102"/>
       <c r="L111" s="30"/>
       <c r="M111" s="30"/>
       <c r="N111" s="30"/>
@@ -7016,10 +7015,10 @@
       <c r="I112" s="42">
         <v>100</v>
       </c>
-      <c r="J112" s="102" t="s">
+      <c r="J112" s="101" t="s">
         <v>199</v>
       </c>
-      <c r="K112" s="103"/>
+      <c r="K112" s="102"/>
       <c r="L112" s="30"/>
       <c r="M112" s="30"/>
       <c r="N112" s="30"/>
@@ -7048,8 +7047,8 @@
       <c r="I113" s="42">
         <v>140</v>
       </c>
-      <c r="J113" s="103"/>
-      <c r="K113" s="103"/>
+      <c r="J113" s="102"/>
+      <c r="K113" s="102"/>
       <c r="L113" s="30"/>
       <c r="M113" s="30"/>
       <c r="N113" s="30"/>
@@ -7078,8 +7077,8 @@
       <c r="I114" s="42">
         <v>140</v>
       </c>
-      <c r="J114" s="103"/>
-      <c r="K114" s="103"/>
+      <c r="J114" s="102"/>
+      <c r="K114" s="102"/>
       <c r="L114" s="30"/>
       <c r="M114" s="30"/>
       <c r="N114" s="30"/>
@@ -7090,16 +7089,16 @@
     </row>
     <row r="115" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="108"/>
-      <c r="B115" s="103"/>
-      <c r="C115" s="103"/>
-      <c r="D115" s="103"/>
-      <c r="E115" s="103"/>
-      <c r="F115" s="103"/>
-      <c r="G115" s="103"/>
-      <c r="H115" s="103"/>
-      <c r="I115" s="103"/>
-      <c r="J115" s="103"/>
-      <c r="K115" s="103"/>
+      <c r="B115" s="102"/>
+      <c r="C115" s="102"/>
+      <c r="D115" s="102"/>
+      <c r="E115" s="102"/>
+      <c r="F115" s="102"/>
+      <c r="G115" s="102"/>
+      <c r="H115" s="102"/>
+      <c r="I115" s="102"/>
+      <c r="J115" s="102"/>
+      <c r="K115" s="102"/>
       <c r="L115" s="30"/>
       <c r="M115" s="30"/>
       <c r="N115" s="30"/>
@@ -7110,16 +7109,16 @@
     </row>
     <row r="116" spans="1:18" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A116" s="109"/>
-      <c r="B116" s="103"/>
-      <c r="C116" s="103"/>
-      <c r="D116" s="103"/>
-      <c r="E116" s="103"/>
-      <c r="F116" s="103"/>
-      <c r="G116" s="103"/>
-      <c r="H116" s="103"/>
-      <c r="I116" s="103"/>
-      <c r="J116" s="103"/>
-      <c r="K116" s="103"/>
+      <c r="B116" s="102"/>
+      <c r="C116" s="102"/>
+      <c r="D116" s="102"/>
+      <c r="E116" s="102"/>
+      <c r="F116" s="102"/>
+      <c r="G116" s="102"/>
+      <c r="H116" s="102"/>
+      <c r="I116" s="102"/>
+      <c r="J116" s="102"/>
+      <c r="K116" s="102"/>
       <c r="L116" s="30"/>
       <c r="M116" s="30"/>
       <c r="N116" s="30"/>
@@ -7130,16 +7129,16 @@
     </row>
     <row r="117" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="30"/>
-      <c r="B117" s="103"/>
-      <c r="C117" s="103"/>
-      <c r="D117" s="103"/>
-      <c r="E117" s="103"/>
-      <c r="F117" s="103"/>
-      <c r="G117" s="103"/>
-      <c r="H117" s="103"/>
-      <c r="I117" s="103"/>
-      <c r="J117" s="103"/>
-      <c r="K117" s="103"/>
+      <c r="B117" s="102"/>
+      <c r="C117" s="102"/>
+      <c r="D117" s="102"/>
+      <c r="E117" s="102"/>
+      <c r="F117" s="102"/>
+      <c r="G117" s="102"/>
+      <c r="H117" s="102"/>
+      <c r="I117" s="102"/>
+      <c r="J117" s="102"/>
+      <c r="K117" s="102"/>
       <c r="L117" s="30"/>
       <c r="M117" s="30"/>
       <c r="N117" s="30"/>
@@ -7152,14 +7151,14 @@
       <c r="A118" s="30"/>
       <c r="B118" s="30"/>
       <c r="C118" s="30"/>
-      <c r="D118" s="103"/>
-      <c r="E118" s="103"/>
-      <c r="F118" s="103"/>
-      <c r="G118" s="103"/>
-      <c r="H118" s="103"/>
-      <c r="I118" s="103"/>
-      <c r="J118" s="103"/>
-      <c r="K118" s="103"/>
+      <c r="D118" s="102"/>
+      <c r="E118" s="102"/>
+      <c r="F118" s="102"/>
+      <c r="G118" s="102"/>
+      <c r="H118" s="102"/>
+      <c r="I118" s="102"/>
+      <c r="J118" s="102"/>
+      <c r="K118" s="102"/>
       <c r="L118" s="30"/>
       <c r="M118" s="30"/>
       <c r="N118" s="30"/>
@@ -7172,14 +7171,14 @@
       <c r="A119" s="30"/>
       <c r="B119" s="31"/>
       <c r="C119" s="31"/>
-      <c r="D119" s="103"/>
-      <c r="E119" s="103"/>
-      <c r="F119" s="103"/>
-      <c r="G119" s="103"/>
-      <c r="H119" s="103"/>
-      <c r="I119" s="103"/>
-      <c r="J119" s="103"/>
-      <c r="K119" s="103"/>
+      <c r="D119" s="102"/>
+      <c r="E119" s="102"/>
+      <c r="F119" s="102"/>
+      <c r="G119" s="102"/>
+      <c r="H119" s="102"/>
+      <c r="I119" s="102"/>
+      <c r="J119" s="102"/>
+      <c r="K119" s="102"/>
       <c r="L119" s="30"/>
       <c r="M119" s="30"/>
       <c r="N119" s="30"/>
@@ -7196,14 +7195,14 @@
       <c r="C120" s="33" t="s">
         <v>139</v>
       </c>
-      <c r="D120" s="103"/>
+      <c r="D120" s="102"/>
       <c r="E120" s="110"/>
       <c r="F120" s="110"/>
-      <c r="G120" s="103"/>
-      <c r="H120" s="103"/>
-      <c r="I120" s="103"/>
-      <c r="J120" s="103"/>
-      <c r="K120" s="103"/>
+      <c r="G120" s="102"/>
+      <c r="H120" s="102"/>
+      <c r="I120" s="102"/>
+      <c r="J120" s="102"/>
+      <c r="K120" s="102"/>
       <c r="L120" s="30"/>
       <c r="M120" s="30"/>
       <c r="N120" s="30"/>
@@ -7220,14 +7219,14 @@
       <c r="C121" s="54" t="s">
         <v>140</v>
       </c>
-      <c r="D121" s="103"/>
+      <c r="D121" s="102"/>
       <c r="E121" s="43"/>
       <c r="F121" s="43"/>
-      <c r="G121" s="103"/>
-      <c r="H121" s="103"/>
-      <c r="I121" s="103"/>
-      <c r="J121" s="103"/>
-      <c r="K121" s="103"/>
+      <c r="G121" s="102"/>
+      <c r="H121" s="102"/>
+      <c r="I121" s="102"/>
+      <c r="J121" s="102"/>
+      <c r="K121" s="102"/>
       <c r="L121" s="30"/>
       <c r="M121" s="30"/>
       <c r="N121" s="30"/>
@@ -7244,14 +7243,14 @@
       <c r="C122" s="54" t="s">
         <v>141</v>
       </c>
-      <c r="D122" s="103"/>
+      <c r="D122" s="102"/>
       <c r="E122" s="43"/>
       <c r="F122" s="43"/>
-      <c r="G122" s="103"/>
-      <c r="H122" s="103"/>
-      <c r="I122" s="103"/>
-      <c r="J122" s="103"/>
-      <c r="K122" s="103"/>
+      <c r="G122" s="102"/>
+      <c r="H122" s="102"/>
+      <c r="I122" s="102"/>
+      <c r="J122" s="102"/>
+      <c r="K122" s="102"/>
       <c r="L122" s="30"/>
       <c r="M122" s="30"/>
       <c r="N122" s="30"/>
@@ -7268,14 +7267,14 @@
       <c r="C123" s="54" t="s">
         <v>142</v>
       </c>
-      <c r="D123" s="103"/>
+      <c r="D123" s="102"/>
       <c r="E123" s="43"/>
       <c r="F123" s="43"/>
-      <c r="G123" s="103"/>
-      <c r="H123" s="103"/>
-      <c r="I123" s="103"/>
-      <c r="J123" s="103"/>
-      <c r="K123" s="103"/>
+      <c r="G123" s="102"/>
+      <c r="H123" s="102"/>
+      <c r="I123" s="102"/>
+      <c r="J123" s="102"/>
+      <c r="K123" s="102"/>
       <c r="L123" s="30"/>
       <c r="M123" s="30"/>
       <c r="N123" s="30"/>
@@ -7292,14 +7291,14 @@
       <c r="C124" s="54" t="s">
         <v>140</v>
       </c>
-      <c r="D124" s="103"/>
+      <c r="D124" s="102"/>
       <c r="E124" s="43"/>
       <c r="F124" s="43"/>
-      <c r="G124" s="103"/>
-      <c r="H124" s="103"/>
-      <c r="I124" s="103"/>
-      <c r="J124" s="103"/>
-      <c r="K124" s="103"/>
+      <c r="G124" s="102"/>
+      <c r="H124" s="102"/>
+      <c r="I124" s="102"/>
+      <c r="J124" s="102"/>
+      <c r="K124" s="102"/>
       <c r="L124" s="30"/>
       <c r="M124" s="30"/>
       <c r="N124" s="30"/>
@@ -7316,14 +7315,14 @@
       <c r="C125" s="54" t="s">
         <v>140</v>
       </c>
-      <c r="D125" s="103"/>
+      <c r="D125" s="102"/>
       <c r="E125" s="43"/>
       <c r="F125" s="43"/>
-      <c r="G125" s="103"/>
-      <c r="H125" s="103"/>
-      <c r="I125" s="103"/>
-      <c r="J125" s="103"/>
-      <c r="K125" s="103"/>
+      <c r="G125" s="102"/>
+      <c r="H125" s="102"/>
+      <c r="I125" s="102"/>
+      <c r="J125" s="102"/>
+      <c r="K125" s="102"/>
       <c r="L125" s="30"/>
       <c r="M125" s="30"/>
       <c r="N125" s="30"/>
@@ -7340,14 +7339,14 @@
       <c r="C126" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="D126" s="103"/>
+      <c r="D126" s="102"/>
       <c r="E126" s="43"/>
       <c r="F126" s="43"/>
-      <c r="G126" s="103"/>
-      <c r="H126" s="103"/>
-      <c r="I126" s="103"/>
-      <c r="J126" s="103"/>
-      <c r="K126" s="103"/>
+      <c r="G126" s="102"/>
+      <c r="H126" s="102"/>
+      <c r="I126" s="102"/>
+      <c r="J126" s="102"/>
+      <c r="K126" s="102"/>
       <c r="L126" s="30"/>
       <c r="M126" s="30"/>
       <c r="N126" s="30"/>
@@ -7364,14 +7363,14 @@
       <c r="C127" s="54" t="s">
         <v>141</v>
       </c>
-      <c r="D127" s="103"/>
+      <c r="D127" s="102"/>
       <c r="E127" s="43"/>
       <c r="F127" s="43"/>
-      <c r="G127" s="103"/>
-      <c r="H127" s="103"/>
-      <c r="I127" s="103"/>
-      <c r="J127" s="103"/>
-      <c r="K127" s="103"/>
+      <c r="G127" s="102"/>
+      <c r="H127" s="102"/>
+      <c r="I127" s="102"/>
+      <c r="J127" s="102"/>
+      <c r="K127" s="102"/>
       <c r="L127" s="30"/>
       <c r="M127" s="30"/>
       <c r="N127" s="30"/>
@@ -7388,14 +7387,14 @@
       <c r="C128" s="54" t="s">
         <v>140</v>
       </c>
-      <c r="D128" s="103"/>
+      <c r="D128" s="102"/>
       <c r="E128" s="43"/>
       <c r="F128" s="43"/>
-      <c r="G128" s="103"/>
-      <c r="H128" s="103"/>
-      <c r="I128" s="103"/>
-      <c r="J128" s="103"/>
-      <c r="K128" s="103"/>
+      <c r="G128" s="102"/>
+      <c r="H128" s="102"/>
+      <c r="I128" s="102"/>
+      <c r="J128" s="102"/>
+      <c r="K128" s="102"/>
       <c r="L128" s="30"/>
       <c r="M128" s="30"/>
       <c r="N128" s="30"/>
@@ -7412,14 +7411,14 @@
       <c r="C129" s="54" t="s">
         <v>142</v>
       </c>
-      <c r="D129" s="103"/>
+      <c r="D129" s="102"/>
       <c r="E129" s="43"/>
       <c r="F129" s="43"/>
-      <c r="G129" s="103"/>
-      <c r="H129" s="103"/>
-      <c r="I129" s="103"/>
-      <c r="J129" s="103"/>
-      <c r="K129" s="103"/>
+      <c r="G129" s="102"/>
+      <c r="H129" s="102"/>
+      <c r="I129" s="102"/>
+      <c r="J129" s="102"/>
+      <c r="K129" s="102"/>
       <c r="L129" s="30"/>
       <c r="M129" s="30"/>
       <c r="N129" s="30"/>
@@ -7436,14 +7435,14 @@
       <c r="C130" s="54" t="s">
         <v>142</v>
       </c>
-      <c r="D130" s="103"/>
+      <c r="D130" s="102"/>
       <c r="E130" s="43"/>
       <c r="F130" s="43"/>
-      <c r="G130" s="103"/>
-      <c r="H130" s="103"/>
-      <c r="I130" s="103"/>
-      <c r="J130" s="103"/>
-      <c r="K130" s="103"/>
+      <c r="G130" s="102"/>
+      <c r="H130" s="102"/>
+      <c r="I130" s="102"/>
+      <c r="J130" s="102"/>
+      <c r="K130" s="102"/>
       <c r="L130" s="30"/>
       <c r="M130" s="30"/>
       <c r="N130" s="30"/>
@@ -7460,14 +7459,14 @@
       <c r="C131" s="54" t="s">
         <v>140</v>
       </c>
-      <c r="D131" s="103"/>
+      <c r="D131" s="102"/>
       <c r="E131" s="43"/>
       <c r="F131" s="43"/>
-      <c r="G131" s="103"/>
-      <c r="H131" s="103"/>
-      <c r="I131" s="103"/>
-      <c r="J131" s="103"/>
-      <c r="K131" s="103"/>
+      <c r="G131" s="102"/>
+      <c r="H131" s="102"/>
+      <c r="I131" s="102"/>
+      <c r="J131" s="102"/>
+      <c r="K131" s="102"/>
       <c r="L131" s="30"/>
       <c r="M131" s="30"/>
       <c r="N131" s="30"/>
@@ -7484,14 +7483,14 @@
       <c r="C132" s="54" t="s">
         <v>142</v>
       </c>
-      <c r="D132" s="103"/>
+      <c r="D132" s="102"/>
       <c r="E132" s="43"/>
       <c r="F132" s="43"/>
-      <c r="G132" s="103"/>
-      <c r="H132" s="103"/>
-      <c r="I132" s="103"/>
-      <c r="J132" s="103"/>
-      <c r="K132" s="103"/>
+      <c r="G132" s="102"/>
+      <c r="H132" s="102"/>
+      <c r="I132" s="102"/>
+      <c r="J132" s="102"/>
+      <c r="K132" s="102"/>
       <c r="L132" s="30"/>
       <c r="M132" s="30"/>
       <c r="N132" s="30"/>
@@ -7508,14 +7507,14 @@
       <c r="C133" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="D133" s="103"/>
+      <c r="D133" s="102"/>
       <c r="E133" s="43"/>
       <c r="F133" s="43"/>
-      <c r="G133" s="103"/>
-      <c r="H133" s="103"/>
-      <c r="I133" s="103"/>
-      <c r="J133" s="103"/>
-      <c r="K133" s="103"/>
+      <c r="G133" s="102"/>
+      <c r="H133" s="102"/>
+      <c r="I133" s="102"/>
+      <c r="J133" s="102"/>
+      <c r="K133" s="102"/>
       <c r="L133" s="30"/>
       <c r="M133" s="30"/>
       <c r="N133" s="30"/>
@@ -7532,14 +7531,14 @@
       <c r="C134" s="54" t="s">
         <v>140</v>
       </c>
-      <c r="D134" s="103"/>
+      <c r="D134" s="102"/>
       <c r="E134" s="43"/>
       <c r="F134" s="43"/>
-      <c r="G134" s="103"/>
-      <c r="H134" s="103"/>
-      <c r="I134" s="103"/>
-      <c r="J134" s="103"/>
-      <c r="K134" s="103"/>
+      <c r="G134" s="102"/>
+      <c r="H134" s="102"/>
+      <c r="I134" s="102"/>
+      <c r="J134" s="102"/>
+      <c r="K134" s="102"/>
       <c r="L134" s="30"/>
       <c r="M134" s="30"/>
       <c r="N134" s="30"/>
@@ -7556,14 +7555,14 @@
       <c r="C135" s="54" t="s">
         <v>140</v>
       </c>
-      <c r="D135" s="103"/>
+      <c r="D135" s="102"/>
       <c r="E135" s="43"/>
       <c r="F135" s="43"/>
-      <c r="G135" s="103"/>
-      <c r="H135" s="103"/>
-      <c r="I135" s="103"/>
-      <c r="J135" s="103"/>
-      <c r="K135" s="103"/>
+      <c r="G135" s="102"/>
+      <c r="H135" s="102"/>
+      <c r="I135" s="102"/>
+      <c r="J135" s="102"/>
+      <c r="K135" s="102"/>
       <c r="L135" s="30"/>
       <c r="M135" s="30"/>
       <c r="N135" s="30"/>
@@ -7580,14 +7579,14 @@
       <c r="C136" s="54" t="s">
         <v>140</v>
       </c>
-      <c r="D136" s="103"/>
+      <c r="D136" s="102"/>
       <c r="E136" s="43"/>
       <c r="F136" s="43"/>
-      <c r="G136" s="103"/>
-      <c r="H136" s="103"/>
-      <c r="I136" s="103"/>
-      <c r="J136" s="103"/>
-      <c r="K136" s="103"/>
+      <c r="G136" s="102"/>
+      <c r="H136" s="102"/>
+      <c r="I136" s="102"/>
+      <c r="J136" s="102"/>
+      <c r="K136" s="102"/>
       <c r="L136" s="30"/>
       <c r="M136" s="30"/>
       <c r="N136" s="30"/>
@@ -7604,14 +7603,14 @@
       <c r="C137" s="54" t="s">
         <v>143</v>
       </c>
-      <c r="D137" s="103"/>
+      <c r="D137" s="102"/>
       <c r="E137" s="43"/>
       <c r="F137" s="43"/>
-      <c r="G137" s="103"/>
-      <c r="H137" s="103"/>
-      <c r="I137" s="103"/>
-      <c r="J137" s="103"/>
-      <c r="K137" s="103"/>
+      <c r="G137" s="102"/>
+      <c r="H137" s="102"/>
+      <c r="I137" s="102"/>
+      <c r="J137" s="102"/>
+      <c r="K137" s="102"/>
       <c r="L137" s="30"/>
       <c r="M137" s="30"/>
       <c r="N137" s="30"/>
@@ -7628,14 +7627,14 @@
       <c r="C138" s="54" t="s">
         <v>140</v>
       </c>
-      <c r="D138" s="103"/>
+      <c r="D138" s="102"/>
       <c r="E138" s="43"/>
       <c r="F138" s="43"/>
-      <c r="G138" s="103"/>
-      <c r="H138" s="103"/>
-      <c r="I138" s="103"/>
-      <c r="J138" s="103"/>
-      <c r="K138" s="103"/>
+      <c r="G138" s="102"/>
+      <c r="H138" s="102"/>
+      <c r="I138" s="102"/>
+      <c r="J138" s="102"/>
+      <c r="K138" s="102"/>
       <c r="L138" s="30"/>
       <c r="M138" s="30"/>
       <c r="N138" s="30"/>
@@ -7652,14 +7651,14 @@
       <c r="C139" s="54" t="s">
         <v>141</v>
       </c>
-      <c r="D139" s="103"/>
+      <c r="D139" s="102"/>
       <c r="E139" s="43"/>
       <c r="F139" s="43"/>
-      <c r="G139" s="103"/>
-      <c r="H139" s="103"/>
-      <c r="I139" s="103"/>
-      <c r="J139" s="103"/>
-      <c r="K139" s="103"/>
+      <c r="G139" s="102"/>
+      <c r="H139" s="102"/>
+      <c r="I139" s="102"/>
+      <c r="J139" s="102"/>
+      <c r="K139" s="102"/>
       <c r="L139" s="30"/>
       <c r="M139" s="30"/>
       <c r="N139" s="30"/>
@@ -7676,14 +7675,14 @@
       <c r="C140" s="54" t="s">
         <v>140</v>
       </c>
-      <c r="D140" s="103"/>
+      <c r="D140" s="102"/>
       <c r="E140" s="43"/>
       <c r="F140" s="43"/>
-      <c r="G140" s="103"/>
-      <c r="H140" s="103"/>
-      <c r="I140" s="103"/>
-      <c r="J140" s="103"/>
-      <c r="K140" s="103"/>
+      <c r="G140" s="102"/>
+      <c r="H140" s="102"/>
+      <c r="I140" s="102"/>
+      <c r="J140" s="102"/>
+      <c r="K140" s="102"/>
       <c r="L140" s="30"/>
       <c r="M140" s="30"/>
       <c r="N140" s="30"/>
@@ -7700,14 +7699,14 @@
       <c r="C141" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="D141" s="103"/>
+      <c r="D141" s="102"/>
       <c r="E141" s="43"/>
       <c r="F141" s="43"/>
-      <c r="G141" s="103"/>
-      <c r="H141" s="103"/>
-      <c r="I141" s="103"/>
-      <c r="J141" s="103"/>
-      <c r="K141" s="103"/>
+      <c r="G141" s="102"/>
+      <c r="H141" s="102"/>
+      <c r="I141" s="102"/>
+      <c r="J141" s="102"/>
+      <c r="K141" s="102"/>
       <c r="L141" s="30"/>
       <c r="M141" s="30"/>
       <c r="N141" s="30"/>
@@ -7724,14 +7723,14 @@
       <c r="C142" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="D142" s="103"/>
+      <c r="D142" s="102"/>
       <c r="E142" s="43"/>
       <c r="F142" s="43"/>
-      <c r="G142" s="103"/>
-      <c r="H142" s="103"/>
-      <c r="I142" s="103"/>
-      <c r="J142" s="103"/>
-      <c r="K142" s="103"/>
+      <c r="G142" s="102"/>
+      <c r="H142" s="102"/>
+      <c r="I142" s="102"/>
+      <c r="J142" s="102"/>
+      <c r="K142" s="102"/>
       <c r="L142" s="30"/>
       <c r="M142" s="30"/>
       <c r="N142" s="30"/>
@@ -7748,14 +7747,14 @@
       <c r="C143" s="20" t="s">
         <v>140</v>
       </c>
-      <c r="D143" s="103"/>
+      <c r="D143" s="102"/>
       <c r="E143" s="43"/>
       <c r="F143" s="43"/>
-      <c r="G143" s="103"/>
-      <c r="H143" s="103"/>
-      <c r="I143" s="103"/>
-      <c r="J143" s="103"/>
-      <c r="K143" s="103"/>
+      <c r="G143" s="102"/>
+      <c r="H143" s="102"/>
+      <c r="I143" s="102"/>
+      <c r="J143" s="102"/>
+      <c r="K143" s="102"/>
       <c r="L143" s="30"/>
       <c r="M143" s="30"/>
       <c r="N143" s="30"/>
@@ -7772,14 +7771,14 @@
       <c r="C144" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="D144" s="103"/>
+      <c r="D144" s="102"/>
       <c r="E144" s="43"/>
       <c r="F144" s="43"/>
-      <c r="G144" s="103"/>
-      <c r="H144" s="103"/>
-      <c r="I144" s="103"/>
-      <c r="J144" s="103"/>
-      <c r="K144" s="103"/>
+      <c r="G144" s="102"/>
+      <c r="H144" s="102"/>
+      <c r="I144" s="102"/>
+      <c r="J144" s="102"/>
+      <c r="K144" s="102"/>
       <c r="L144" s="30"/>
       <c r="M144" s="30"/>
       <c r="N144" s="30"/>
@@ -7796,14 +7795,14 @@
       <c r="C145" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="D145" s="103"/>
+      <c r="D145" s="102"/>
       <c r="E145" s="43"/>
       <c r="F145" s="43"/>
-      <c r="G145" s="103"/>
-      <c r="H145" s="103"/>
-      <c r="I145" s="103"/>
-      <c r="J145" s="103"/>
-      <c r="K145" s="103"/>
+      <c r="G145" s="102"/>
+      <c r="H145" s="102"/>
+      <c r="I145" s="102"/>
+      <c r="J145" s="102"/>
+      <c r="K145" s="102"/>
       <c r="L145" s="30"/>
       <c r="M145" s="30"/>
       <c r="N145" s="30"/>
@@ -7820,14 +7819,14 @@
       <c r="C146" s="54" t="s">
         <v>140</v>
       </c>
-      <c r="D146" s="103"/>
+      <c r="D146" s="102"/>
       <c r="E146" s="43"/>
       <c r="F146" s="43"/>
-      <c r="G146" s="103"/>
-      <c r="H146" s="103"/>
-      <c r="I146" s="103"/>
-      <c r="J146" s="103"/>
-      <c r="K146" s="103"/>
+      <c r="G146" s="102"/>
+      <c r="H146" s="102"/>
+      <c r="I146" s="102"/>
+      <c r="J146" s="102"/>
+      <c r="K146" s="102"/>
       <c r="L146" s="30"/>
       <c r="M146" s="30"/>
       <c r="N146" s="30"/>
@@ -7844,14 +7843,14 @@
       <c r="C147" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="D147" s="103"/>
+      <c r="D147" s="102"/>
       <c r="E147" s="43"/>
       <c r="F147" s="43"/>
-      <c r="G147" s="103"/>
-      <c r="H147" s="103"/>
-      <c r="I147" s="103"/>
-      <c r="J147" s="103"/>
-      <c r="K147" s="103"/>
+      <c r="G147" s="102"/>
+      <c r="H147" s="102"/>
+      <c r="I147" s="102"/>
+      <c r="J147" s="102"/>
+      <c r="K147" s="102"/>
       <c r="L147" s="30"/>
       <c r="M147" s="30"/>
       <c r="N147" s="30"/>
@@ -7868,14 +7867,14 @@
       <c r="C148" s="54" t="s">
         <v>140</v>
       </c>
-      <c r="D148" s="103"/>
+      <c r="D148" s="102"/>
       <c r="E148" s="43"/>
       <c r="F148" s="43"/>
-      <c r="G148" s="103"/>
-      <c r="H148" s="103"/>
-      <c r="I148" s="103"/>
-      <c r="J148" s="103"/>
-      <c r="K148" s="103"/>
+      <c r="G148" s="102"/>
+      <c r="H148" s="102"/>
+      <c r="I148" s="102"/>
+      <c r="J148" s="102"/>
+      <c r="K148" s="102"/>
       <c r="L148" s="30"/>
       <c r="M148" s="30"/>
       <c r="N148" s="30"/>
@@ -7892,14 +7891,14 @@
       <c r="C149" s="54" t="s">
         <v>142</v>
       </c>
-      <c r="D149" s="103"/>
+      <c r="D149" s="102"/>
       <c r="E149" s="43"/>
       <c r="F149" s="43"/>
-      <c r="G149" s="103"/>
-      <c r="H149" s="103"/>
-      <c r="I149" s="103"/>
-      <c r="J149" s="103"/>
-      <c r="K149" s="103"/>
+      <c r="G149" s="102"/>
+      <c r="H149" s="102"/>
+      <c r="I149" s="102"/>
+      <c r="J149" s="102"/>
+      <c r="K149" s="102"/>
       <c r="L149" s="30"/>
       <c r="M149" s="30"/>
       <c r="N149" s="30"/>
@@ -7916,14 +7915,14 @@
       <c r="C150" s="54" t="s">
         <v>140</v>
       </c>
-      <c r="D150" s="103"/>
+      <c r="D150" s="102"/>
       <c r="E150" s="43"/>
       <c r="F150" s="43"/>
-      <c r="G150" s="103"/>
-      <c r="H150" s="103"/>
-      <c r="I150" s="103"/>
-      <c r="J150" s="103"/>
-      <c r="K150" s="103"/>
+      <c r="G150" s="102"/>
+      <c r="H150" s="102"/>
+      <c r="I150" s="102"/>
+      <c r="J150" s="102"/>
+      <c r="K150" s="102"/>
       <c r="L150" s="30"/>
       <c r="M150" s="30"/>
       <c r="N150" s="30"/>
@@ -7940,14 +7939,14 @@
       <c r="C151" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="D151" s="103"/>
+      <c r="D151" s="102"/>
       <c r="E151" s="43"/>
       <c r="F151" s="43"/>
-      <c r="G151" s="103"/>
-      <c r="H151" s="103"/>
-      <c r="I151" s="103"/>
-      <c r="J151" s="103"/>
-      <c r="K151" s="103"/>
+      <c r="G151" s="102"/>
+      <c r="H151" s="102"/>
+      <c r="I151" s="102"/>
+      <c r="J151" s="102"/>
+      <c r="K151" s="102"/>
       <c r="L151" s="30"/>
       <c r="M151" s="30"/>
       <c r="N151" s="30"/>
@@ -7964,14 +7963,14 @@
       <c r="C152" s="54" t="s">
         <v>142</v>
       </c>
-      <c r="D152" s="103"/>
+      <c r="D152" s="102"/>
       <c r="E152" s="43"/>
       <c r="F152" s="43"/>
-      <c r="G152" s="103"/>
-      <c r="H152" s="103"/>
-      <c r="I152" s="103"/>
-      <c r="J152" s="103"/>
-      <c r="K152" s="103"/>
+      <c r="G152" s="102"/>
+      <c r="H152" s="102"/>
+      <c r="I152" s="102"/>
+      <c r="J152" s="102"/>
+      <c r="K152" s="102"/>
       <c r="L152" s="30"/>
       <c r="M152" s="30"/>
       <c r="N152" s="30"/>
@@ -7988,14 +7987,14 @@
       <c r="C153" s="54" t="s">
         <v>140</v>
       </c>
-      <c r="D153" s="103"/>
+      <c r="D153" s="102"/>
       <c r="E153" s="43"/>
       <c r="F153" s="43"/>
-      <c r="G153" s="103"/>
-      <c r="H153" s="103"/>
-      <c r="I153" s="103"/>
-      <c r="J153" s="103"/>
-      <c r="K153" s="103"/>
+      <c r="G153" s="102"/>
+      <c r="H153" s="102"/>
+      <c r="I153" s="102"/>
+      <c r="J153" s="102"/>
+      <c r="K153" s="102"/>
       <c r="L153" s="30"/>
       <c r="M153" s="30"/>
       <c r="N153" s="30"/>
@@ -8012,14 +8011,14 @@
       <c r="C154" s="55" t="s">
         <v>142</v>
       </c>
-      <c r="D154" s="103"/>
+      <c r="D154" s="102"/>
       <c r="E154" s="43"/>
       <c r="F154" s="43"/>
-      <c r="G154" s="103"/>
-      <c r="H154" s="103"/>
-      <c r="I154" s="103"/>
-      <c r="J154" s="103"/>
-      <c r="K154" s="103"/>
+      <c r="G154" s="102"/>
+      <c r="H154" s="102"/>
+      <c r="I154" s="102"/>
+      <c r="J154" s="102"/>
+      <c r="K154" s="102"/>
       <c r="L154" s="30"/>
       <c r="M154" s="30"/>
       <c r="N154" s="30"/>
@@ -8036,14 +8035,14 @@
       <c r="C155" s="20" t="s">
         <v>140</v>
       </c>
-      <c r="D155" s="103"/>
+      <c r="D155" s="102"/>
       <c r="E155" s="43"/>
       <c r="F155" s="43"/>
-      <c r="G155" s="103"/>
-      <c r="H155" s="103"/>
-      <c r="I155" s="103"/>
-      <c r="J155" s="103"/>
-      <c r="K155" s="103"/>
+      <c r="G155" s="102"/>
+      <c r="H155" s="102"/>
+      <c r="I155" s="102"/>
+      <c r="J155" s="102"/>
+      <c r="K155" s="102"/>
       <c r="L155" s="30"/>
       <c r="M155" s="30"/>
       <c r="N155" s="30"/>
@@ -8060,14 +8059,14 @@
       <c r="C156" s="20" t="s">
         <v>142</v>
       </c>
-      <c r="D156" s="103"/>
+      <c r="D156" s="102"/>
       <c r="E156" s="43"/>
       <c r="F156" s="43"/>
-      <c r="G156" s="103"/>
-      <c r="H156" s="103"/>
-      <c r="I156" s="103"/>
-      <c r="J156" s="103"/>
-      <c r="K156" s="103"/>
+      <c r="G156" s="102"/>
+      <c r="H156" s="102"/>
+      <c r="I156" s="102"/>
+      <c r="J156" s="102"/>
+      <c r="K156" s="102"/>
       <c r="L156" s="30"/>
       <c r="M156" s="30"/>
       <c r="N156" s="30"/>
@@ -8084,14 +8083,14 @@
       <c r="C157" s="54" t="s">
         <v>140</v>
       </c>
-      <c r="D157" s="103"/>
+      <c r="D157" s="102"/>
       <c r="E157" s="43"/>
       <c r="F157" s="43"/>
-      <c r="G157" s="103"/>
-      <c r="H157" s="103"/>
-      <c r="I157" s="103"/>
-      <c r="J157" s="103"/>
-      <c r="K157" s="103"/>
+      <c r="G157" s="102"/>
+      <c r="H157" s="102"/>
+      <c r="I157" s="102"/>
+      <c r="J157" s="102"/>
+      <c r="K157" s="102"/>
       <c r="L157" s="30"/>
       <c r="M157" s="30"/>
       <c r="N157" s="30"/>
@@ -8108,14 +8107,14 @@
       <c r="C158" s="54" t="s">
         <v>140</v>
       </c>
-      <c r="D158" s="103"/>
+      <c r="D158" s="102"/>
       <c r="E158" s="47"/>
       <c r="F158" s="43"/>
-      <c r="G158" s="103"/>
-      <c r="H158" s="103"/>
-      <c r="I158" s="103"/>
-      <c r="J158" s="103"/>
-      <c r="K158" s="103"/>
+      <c r="G158" s="102"/>
+      <c r="H158" s="102"/>
+      <c r="I158" s="102"/>
+      <c r="J158" s="102"/>
+      <c r="K158" s="102"/>
       <c r="L158" s="30"/>
       <c r="M158" s="30"/>
       <c r="N158" s="30"/>
@@ -8132,14 +8131,14 @@
       <c r="C159" s="54" t="s">
         <v>140</v>
       </c>
-      <c r="D159" s="103"/>
+      <c r="D159" s="102"/>
       <c r="E159" s="43"/>
       <c r="F159" s="43"/>
-      <c r="G159" s="103"/>
-      <c r="H159" s="103"/>
-      <c r="I159" s="103"/>
-      <c r="J159" s="103"/>
-      <c r="K159" s="103"/>
+      <c r="G159" s="102"/>
+      <c r="H159" s="102"/>
+      <c r="I159" s="102"/>
+      <c r="J159" s="102"/>
+      <c r="K159" s="102"/>
       <c r="L159" s="30"/>
       <c r="M159" s="30"/>
       <c r="N159" s="30"/>
@@ -8156,14 +8155,14 @@
       <c r="C160" s="54" t="s">
         <v>140</v>
       </c>
-      <c r="D160" s="103"/>
+      <c r="D160" s="102"/>
       <c r="E160" s="43"/>
       <c r="F160" s="43"/>
-      <c r="G160" s="103"/>
-      <c r="H160" s="103"/>
-      <c r="I160" s="103"/>
-      <c r="J160" s="103"/>
-      <c r="K160" s="103"/>
+      <c r="G160" s="102"/>
+      <c r="H160" s="102"/>
+      <c r="I160" s="102"/>
+      <c r="J160" s="102"/>
+      <c r="K160" s="102"/>
       <c r="L160" s="30"/>
       <c r="M160" s="30"/>
       <c r="N160" s="30"/>
@@ -8180,14 +8179,14 @@
       <c r="C161" s="54" t="s">
         <v>140</v>
       </c>
-      <c r="D161" s="103"/>
+      <c r="D161" s="102"/>
       <c r="E161" s="43"/>
       <c r="F161" s="43"/>
-      <c r="G161" s="103"/>
-      <c r="H161" s="103"/>
-      <c r="I161" s="103"/>
-      <c r="J161" s="103"/>
-      <c r="K161" s="103"/>
+      <c r="G161" s="102"/>
+      <c r="H161" s="102"/>
+      <c r="I161" s="102"/>
+      <c r="J161" s="102"/>
+      <c r="K161" s="102"/>
       <c r="L161" s="30"/>
       <c r="M161" s="30"/>
       <c r="N161" s="30"/>
@@ -8204,14 +8203,14 @@
       <c r="C162" s="54" t="s">
         <v>141</v>
       </c>
-      <c r="D162" s="103"/>
+      <c r="D162" s="102"/>
       <c r="E162" s="43"/>
       <c r="F162" s="43"/>
-      <c r="G162" s="103"/>
-      <c r="H162" s="103"/>
-      <c r="I162" s="103"/>
-      <c r="J162" s="103"/>
-      <c r="K162" s="103"/>
+      <c r="G162" s="102"/>
+      <c r="H162" s="102"/>
+      <c r="I162" s="102"/>
+      <c r="J162" s="102"/>
+      <c r="K162" s="102"/>
       <c r="L162" s="30"/>
       <c r="M162" s="30"/>
       <c r="N162" s="30"/>
@@ -8228,14 +8227,14 @@
       <c r="C163" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="D163" s="103"/>
+      <c r="D163" s="102"/>
       <c r="E163" s="43"/>
       <c r="F163" s="43"/>
-      <c r="G163" s="103"/>
-      <c r="H163" s="103"/>
-      <c r="I163" s="103"/>
-      <c r="J163" s="103"/>
-      <c r="K163" s="103"/>
+      <c r="G163" s="102"/>
+      <c r="H163" s="102"/>
+      <c r="I163" s="102"/>
+      <c r="J163" s="102"/>
+      <c r="K163" s="102"/>
       <c r="L163" s="30"/>
       <c r="M163" s="30"/>
       <c r="N163" s="30"/>
@@ -8252,14 +8251,14 @@
       <c r="C164" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="D164" s="103"/>
+      <c r="D164" s="102"/>
       <c r="E164" s="43"/>
       <c r="F164" s="43"/>
-      <c r="G164" s="103"/>
-      <c r="H164" s="103"/>
-      <c r="I164" s="103"/>
-      <c r="J164" s="103"/>
-      <c r="K164" s="103"/>
+      <c r="G164" s="102"/>
+      <c r="H164" s="102"/>
+      <c r="I164" s="102"/>
+      <c r="J164" s="102"/>
+      <c r="K164" s="102"/>
       <c r="L164" s="30"/>
       <c r="M164" s="30"/>
       <c r="N164" s="30"/>
@@ -8276,14 +8275,14 @@
       <c r="C165" s="54" t="s">
         <v>140</v>
       </c>
-      <c r="D165" s="103"/>
+      <c r="D165" s="102"/>
       <c r="E165" s="43"/>
       <c r="F165" s="43"/>
-      <c r="G165" s="103"/>
-      <c r="H165" s="103"/>
-      <c r="I165" s="103"/>
-      <c r="J165" s="103"/>
-      <c r="K165" s="103"/>
+      <c r="G165" s="102"/>
+      <c r="H165" s="102"/>
+      <c r="I165" s="102"/>
+      <c r="J165" s="102"/>
+      <c r="K165" s="102"/>
       <c r="L165" s="30"/>
       <c r="M165" s="30"/>
       <c r="N165" s="30"/>
@@ -8300,14 +8299,14 @@
       <c r="C166" s="54" t="s">
         <v>140</v>
       </c>
-      <c r="D166" s="103"/>
+      <c r="D166" s="102"/>
       <c r="E166" s="43"/>
       <c r="F166" s="43"/>
-      <c r="G166" s="103"/>
-      <c r="H166" s="103"/>
-      <c r="I166" s="103"/>
-      <c r="J166" s="103"/>
-      <c r="K166" s="103"/>
+      <c r="G166" s="102"/>
+      <c r="H166" s="102"/>
+      <c r="I166" s="102"/>
+      <c r="J166" s="102"/>
+      <c r="K166" s="102"/>
       <c r="L166" s="30"/>
       <c r="M166" s="30"/>
       <c r="N166" s="30"/>
@@ -8324,14 +8323,14 @@
       <c r="C167" s="54" t="s">
         <v>13</v>
       </c>
-      <c r="D167" s="103"/>
+      <c r="D167" s="102"/>
       <c r="E167" s="43"/>
       <c r="F167" s="43"/>
-      <c r="G167" s="103"/>
-      <c r="H167" s="103"/>
-      <c r="I167" s="103"/>
-      <c r="J167" s="103"/>
-      <c r="K167" s="103"/>
+      <c r="G167" s="102"/>
+      <c r="H167" s="102"/>
+      <c r="I167" s="102"/>
+      <c r="J167" s="102"/>
+      <c r="K167" s="102"/>
       <c r="L167" s="30"/>
       <c r="M167" s="30"/>
       <c r="N167" s="30"/>
@@ -8348,14 +8347,14 @@
       <c r="C168" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="D168" s="103"/>
+      <c r="D168" s="102"/>
       <c r="E168" s="43"/>
       <c r="F168" s="43"/>
-      <c r="G168" s="103"/>
-      <c r="H168" s="103"/>
-      <c r="I168" s="103"/>
-      <c r="J168" s="103"/>
-      <c r="K168" s="103"/>
+      <c r="G168" s="102"/>
+      <c r="H168" s="102"/>
+      <c r="I168" s="102"/>
+      <c r="J168" s="102"/>
+      <c r="K168" s="102"/>
       <c r="L168" s="30"/>
       <c r="M168" s="30"/>
       <c r="N168" s="30"/>
@@ -8372,14 +8371,14 @@
       <c r="C169" s="54" t="s">
         <v>140</v>
       </c>
-      <c r="D169" s="103"/>
+      <c r="D169" s="102"/>
       <c r="E169" s="43"/>
       <c r="F169" s="43"/>
-      <c r="G169" s="103"/>
-      <c r="H169" s="103"/>
-      <c r="I169" s="103"/>
-      <c r="J169" s="103"/>
-      <c r="K169" s="103"/>
+      <c r="G169" s="102"/>
+      <c r="H169" s="102"/>
+      <c r="I169" s="102"/>
+      <c r="J169" s="102"/>
+      <c r="K169" s="102"/>
       <c r="L169" s="30"/>
       <c r="M169" s="30"/>
       <c r="N169" s="30"/>
@@ -8396,14 +8395,14 @@
       <c r="C170" s="54" t="s">
         <v>140</v>
       </c>
-      <c r="D170" s="103"/>
+      <c r="D170" s="102"/>
       <c r="E170" s="43"/>
       <c r="F170" s="43"/>
-      <c r="G170" s="103"/>
-      <c r="H170" s="103"/>
-      <c r="I170" s="103"/>
-      <c r="J170" s="103"/>
-      <c r="K170" s="103"/>
+      <c r="G170" s="102"/>
+      <c r="H170" s="102"/>
+      <c r="I170" s="102"/>
+      <c r="J170" s="102"/>
+      <c r="K170" s="102"/>
       <c r="L170" s="30"/>
       <c r="M170" s="30"/>
       <c r="N170" s="30"/>
@@ -8420,14 +8419,14 @@
       <c r="C171" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="D171" s="103"/>
+      <c r="D171" s="102"/>
       <c r="E171" s="43"/>
       <c r="F171" s="43"/>
-      <c r="G171" s="103"/>
-      <c r="H171" s="103"/>
-      <c r="I171" s="103"/>
-      <c r="J171" s="103"/>
-      <c r="K171" s="103"/>
+      <c r="G171" s="102"/>
+      <c r="H171" s="102"/>
+      <c r="I171" s="102"/>
+      <c r="J171" s="102"/>
+      <c r="K171" s="102"/>
       <c r="L171" s="30"/>
       <c r="M171" s="30"/>
       <c r="N171" s="30"/>
@@ -8444,14 +8443,14 @@
       <c r="C172" s="56" t="s">
         <v>3</v>
       </c>
-      <c r="D172" s="103"/>
-      <c r="E172" s="103"/>
-      <c r="F172" s="103"/>
-      <c r="G172" s="103"/>
-      <c r="H172" s="103"/>
-      <c r="I172" s="103"/>
-      <c r="J172" s="103"/>
-      <c r="K172" s="103"/>
+      <c r="D172" s="102"/>
+      <c r="E172" s="102"/>
+      <c r="F172" s="102"/>
+      <c r="G172" s="102"/>
+      <c r="H172" s="102"/>
+      <c r="I172" s="102"/>
+      <c r="J172" s="102"/>
+      <c r="K172" s="102"/>
       <c r="L172" s="30"/>
       <c r="M172" s="30"/>
       <c r="N172" s="30"/>
@@ -8468,14 +8467,14 @@
       <c r="C173" s="54" t="s">
         <v>140</v>
       </c>
-      <c r="D173" s="103"/>
-      <c r="E173" s="103"/>
-      <c r="F173" s="103"/>
-      <c r="G173" s="103"/>
-      <c r="H173" s="103"/>
-      <c r="I173" s="103"/>
-      <c r="J173" s="103"/>
-      <c r="K173" s="103"/>
+      <c r="D173" s="102"/>
+      <c r="E173" s="102"/>
+      <c r="F173" s="102"/>
+      <c r="G173" s="102"/>
+      <c r="H173" s="102"/>
+      <c r="I173" s="102"/>
+      <c r="J173" s="102"/>
+      <c r="K173" s="102"/>
       <c r="L173" s="30"/>
       <c r="M173" s="30"/>
       <c r="N173" s="30"/>
@@ -8492,14 +8491,14 @@
       <c r="C174" s="54" t="s">
         <v>140</v>
       </c>
-      <c r="D174" s="103"/>
-      <c r="E174" s="103"/>
-      <c r="F174" s="103"/>
-      <c r="G174" s="103"/>
-      <c r="H174" s="103"/>
-      <c r="I174" s="103"/>
-      <c r="J174" s="103"/>
-      <c r="K174" s="103"/>
+      <c r="D174" s="102"/>
+      <c r="E174" s="102"/>
+      <c r="F174" s="102"/>
+      <c r="G174" s="102"/>
+      <c r="H174" s="102"/>
+      <c r="I174" s="102"/>
+      <c r="J174" s="102"/>
+      <c r="K174" s="102"/>
       <c r="L174" s="30"/>
       <c r="M174" s="30"/>
       <c r="N174" s="30"/>
@@ -8516,14 +8515,14 @@
       <c r="C175" s="54" t="s">
         <v>140</v>
       </c>
-      <c r="D175" s="103"/>
-      <c r="E175" s="103"/>
-      <c r="F175" s="103"/>
-      <c r="G175" s="103"/>
-      <c r="H175" s="103"/>
-      <c r="I175" s="103"/>
-      <c r="J175" s="103"/>
-      <c r="K175" s="103"/>
+      <c r="D175" s="102"/>
+      <c r="E175" s="102"/>
+      <c r="F175" s="102"/>
+      <c r="G175" s="102"/>
+      <c r="H175" s="102"/>
+      <c r="I175" s="102"/>
+      <c r="J175" s="102"/>
+      <c r="K175" s="102"/>
       <c r="L175" s="30"/>
       <c r="M175" s="30"/>
       <c r="N175" s="30"/>
@@ -8540,14 +8539,14 @@
       <c r="C176" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="D176" s="103"/>
-      <c r="E176" s="103"/>
-      <c r="F176" s="103"/>
-      <c r="G176" s="103"/>
-      <c r="H176" s="103"/>
-      <c r="I176" s="103"/>
-      <c r="J176" s="103"/>
-      <c r="K176" s="103"/>
+      <c r="D176" s="102"/>
+      <c r="E176" s="102"/>
+      <c r="F176" s="102"/>
+      <c r="G176" s="102"/>
+      <c r="H176" s="102"/>
+      <c r="I176" s="102"/>
+      <c r="J176" s="102"/>
+      <c r="K176" s="102"/>
       <c r="L176" s="30"/>
       <c r="M176" s="30"/>
       <c r="N176" s="30"/>
@@ -8564,14 +8563,14 @@
       <c r="C177" s="54" t="s">
         <v>140</v>
       </c>
-      <c r="D177" s="103"/>
-      <c r="E177" s="103"/>
-      <c r="F177" s="103"/>
-      <c r="G177" s="103"/>
-      <c r="H177" s="103"/>
-      <c r="I177" s="103"/>
-      <c r="J177" s="103"/>
-      <c r="K177" s="103"/>
+      <c r="D177" s="102"/>
+      <c r="E177" s="102"/>
+      <c r="F177" s="102"/>
+      <c r="G177" s="102"/>
+      <c r="H177" s="102"/>
+      <c r="I177" s="102"/>
+      <c r="J177" s="102"/>
+      <c r="K177" s="102"/>
       <c r="L177" s="30"/>
       <c r="M177" s="30"/>
       <c r="N177" s="30"/>
@@ -8588,14 +8587,14 @@
       <c r="C178" s="54" t="s">
         <v>140</v>
       </c>
-      <c r="D178" s="103"/>
-      <c r="E178" s="103"/>
-      <c r="F178" s="103"/>
-      <c r="G178" s="103"/>
-      <c r="H178" s="103"/>
-      <c r="I178" s="103"/>
-      <c r="J178" s="103"/>
-      <c r="K178" s="103"/>
+      <c r="D178" s="102"/>
+      <c r="E178" s="102"/>
+      <c r="F178" s="102"/>
+      <c r="G178" s="102"/>
+      <c r="H178" s="102"/>
+      <c r="I178" s="102"/>
+      <c r="J178" s="102"/>
+      <c r="K178" s="102"/>
       <c r="L178" s="30"/>
       <c r="M178" s="30"/>
       <c r="N178" s="30"/>
@@ -8612,14 +8611,14 @@
       <c r="C179" s="54" t="s">
         <v>140</v>
       </c>
-      <c r="D179" s="103"/>
-      <c r="E179" s="103"/>
-      <c r="F179" s="103"/>
-      <c r="G179" s="103"/>
-      <c r="H179" s="103"/>
-      <c r="I179" s="103"/>
-      <c r="J179" s="103"/>
-      <c r="K179" s="103"/>
+      <c r="D179" s="102"/>
+      <c r="E179" s="102"/>
+      <c r="F179" s="102"/>
+      <c r="G179" s="102"/>
+      <c r="H179" s="102"/>
+      <c r="I179" s="102"/>
+      <c r="J179" s="102"/>
+      <c r="K179" s="102"/>
       <c r="L179" s="30"/>
       <c r="M179" s="30"/>
       <c r="N179" s="30"/>
@@ -8636,14 +8635,14 @@
       <c r="C180" s="54" t="s">
         <v>140</v>
       </c>
-      <c r="D180" s="103"/>
-      <c r="E180" s="103"/>
-      <c r="F180" s="103"/>
-      <c r="G180" s="103"/>
-      <c r="H180" s="103"/>
-      <c r="I180" s="103"/>
-      <c r="J180" s="103"/>
-      <c r="K180" s="103"/>
+      <c r="D180" s="102"/>
+      <c r="E180" s="102"/>
+      <c r="F180" s="102"/>
+      <c r="G180" s="102"/>
+      <c r="H180" s="102"/>
+      <c r="I180" s="102"/>
+      <c r="J180" s="102"/>
+      <c r="K180" s="102"/>
       <c r="L180" s="30"/>
       <c r="M180" s="30"/>
       <c r="N180" s="30"/>
@@ -8660,14 +8659,14 @@
       <c r="C181" s="54" t="s">
         <v>141</v>
       </c>
-      <c r="D181" s="103"/>
-      <c r="E181" s="103"/>
-      <c r="F181" s="103"/>
-      <c r="G181" s="103"/>
-      <c r="H181" s="103"/>
-      <c r="I181" s="103"/>
-      <c r="J181" s="103"/>
-      <c r="K181" s="103"/>
+      <c r="D181" s="102"/>
+      <c r="E181" s="102"/>
+      <c r="F181" s="102"/>
+      <c r="G181" s="102"/>
+      <c r="H181" s="102"/>
+      <c r="I181" s="102"/>
+      <c r="J181" s="102"/>
+      <c r="K181" s="102"/>
       <c r="L181" s="30"/>
       <c r="M181" s="30"/>
       <c r="N181" s="30"/>
@@ -8684,14 +8683,14 @@
       <c r="C182" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="D182" s="103"/>
-      <c r="E182" s="103"/>
-      <c r="F182" s="103"/>
-      <c r="G182" s="103"/>
-      <c r="H182" s="103"/>
-      <c r="I182" s="103"/>
-      <c r="J182" s="103"/>
-      <c r="K182" s="103"/>
+      <c r="D182" s="102"/>
+      <c r="E182" s="102"/>
+      <c r="F182" s="102"/>
+      <c r="G182" s="102"/>
+      <c r="H182" s="102"/>
+      <c r="I182" s="102"/>
+      <c r="J182" s="102"/>
+      <c r="K182" s="102"/>
       <c r="L182" s="30"/>
       <c r="M182" s="30"/>
       <c r="N182" s="30"/>
@@ -8708,14 +8707,14 @@
       <c r="C183" s="54" t="s">
         <v>140</v>
       </c>
-      <c r="D183" s="103"/>
-      <c r="E183" s="103"/>
-      <c r="F183" s="103"/>
-      <c r="G183" s="103"/>
-      <c r="H183" s="103"/>
-      <c r="I183" s="103"/>
-      <c r="J183" s="103"/>
-      <c r="K183" s="103"/>
+      <c r="D183" s="102"/>
+      <c r="E183" s="102"/>
+      <c r="F183" s="102"/>
+      <c r="G183" s="102"/>
+      <c r="H183" s="102"/>
+      <c r="I183" s="102"/>
+      <c r="J183" s="102"/>
+      <c r="K183" s="102"/>
       <c r="L183" s="30"/>
       <c r="M183" s="30"/>
       <c r="N183" s="30"/>
@@ -8732,14 +8731,14 @@
       <c r="C184" s="54" t="s">
         <v>140</v>
       </c>
-      <c r="D184" s="103"/>
-      <c r="E184" s="103"/>
-      <c r="F184" s="103"/>
-      <c r="G184" s="103"/>
-      <c r="H184" s="103"/>
-      <c r="I184" s="103"/>
-      <c r="J184" s="103"/>
-      <c r="K184" s="103"/>
+      <c r="D184" s="102"/>
+      <c r="E184" s="102"/>
+      <c r="F184" s="102"/>
+      <c r="G184" s="102"/>
+      <c r="H184" s="102"/>
+      <c r="I184" s="102"/>
+      <c r="J184" s="102"/>
+      <c r="K184" s="102"/>
       <c r="L184" s="30"/>
       <c r="M184" s="30"/>
       <c r="N184" s="30"/>
@@ -8756,14 +8755,14 @@
       <c r="C185" s="54" t="s">
         <v>142</v>
       </c>
-      <c r="D185" s="103"/>
-      <c r="E185" s="103"/>
-      <c r="F185" s="103"/>
-      <c r="G185" s="103"/>
-      <c r="H185" s="103"/>
-      <c r="I185" s="103"/>
-      <c r="J185" s="103"/>
-      <c r="K185" s="103"/>
+      <c r="D185" s="102"/>
+      <c r="E185" s="102"/>
+      <c r="F185" s="102"/>
+      <c r="G185" s="102"/>
+      <c r="H185" s="102"/>
+      <c r="I185" s="102"/>
+      <c r="J185" s="102"/>
+      <c r="K185" s="102"/>
       <c r="L185" s="30"/>
       <c r="M185" s="30"/>
       <c r="N185" s="30"/>
@@ -8780,14 +8779,14 @@
       <c r="C186" s="54" t="s">
         <v>140</v>
       </c>
-      <c r="D186" s="103"/>
-      <c r="E186" s="103"/>
-      <c r="F186" s="103"/>
-      <c r="G186" s="103"/>
-      <c r="H186" s="103"/>
-      <c r="I186" s="103"/>
-      <c r="J186" s="103"/>
-      <c r="K186" s="103"/>
+      <c r="D186" s="102"/>
+      <c r="E186" s="102"/>
+      <c r="F186" s="102"/>
+      <c r="G186" s="102"/>
+      <c r="H186" s="102"/>
+      <c r="I186" s="102"/>
+      <c r="J186" s="102"/>
+      <c r="K186" s="102"/>
       <c r="L186" s="30"/>
       <c r="M186" s="30"/>
       <c r="N186" s="30"/>
@@ -8804,14 +8803,14 @@
       <c r="C187" s="54" t="s">
         <v>141</v>
       </c>
-      <c r="D187" s="103"/>
-      <c r="E187" s="103"/>
-      <c r="F187" s="103"/>
-      <c r="G187" s="103"/>
-      <c r="H187" s="103"/>
-      <c r="I187" s="103"/>
-      <c r="J187" s="103"/>
-      <c r="K187" s="103"/>
+      <c r="D187" s="102"/>
+      <c r="E187" s="102"/>
+      <c r="F187" s="102"/>
+      <c r="G187" s="102"/>
+      <c r="H187" s="102"/>
+      <c r="I187" s="102"/>
+      <c r="J187" s="102"/>
+      <c r="K187" s="102"/>
       <c r="L187" s="30"/>
       <c r="M187" s="30"/>
       <c r="N187" s="30"/>
@@ -8828,14 +8827,14 @@
       <c r="C188" s="54" t="s">
         <v>141</v>
       </c>
-      <c r="D188" s="103"/>
-      <c r="E188" s="103"/>
-      <c r="F188" s="103"/>
-      <c r="G188" s="103"/>
-      <c r="H188" s="103"/>
-      <c r="I188" s="103"/>
-      <c r="J188" s="103"/>
-      <c r="K188" s="103"/>
+      <c r="D188" s="102"/>
+      <c r="E188" s="102"/>
+      <c r="F188" s="102"/>
+      <c r="G188" s="102"/>
+      <c r="H188" s="102"/>
+      <c r="I188" s="102"/>
+      <c r="J188" s="102"/>
+      <c r="K188" s="102"/>
       <c r="L188" s="30"/>
       <c r="M188" s="30"/>
       <c r="N188" s="30"/>
@@ -8852,14 +8851,14 @@
       <c r="C189" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="D189" s="103"/>
-      <c r="E189" s="103"/>
-      <c r="F189" s="103"/>
-      <c r="G189" s="103"/>
-      <c r="H189" s="103"/>
-      <c r="I189" s="103"/>
-      <c r="J189" s="103"/>
-      <c r="K189" s="103"/>
+      <c r="D189" s="102"/>
+      <c r="E189" s="102"/>
+      <c r="F189" s="102"/>
+      <c r="G189" s="102"/>
+      <c r="H189" s="102"/>
+      <c r="I189" s="102"/>
+      <c r="J189" s="102"/>
+      <c r="K189" s="102"/>
       <c r="L189" s="30"/>
       <c r="M189" s="30"/>
       <c r="N189" s="30"/>
@@ -8876,14 +8875,14 @@
       <c r="C190" s="54" t="s">
         <v>140</v>
       </c>
-      <c r="D190" s="103"/>
-      <c r="E190" s="103"/>
-      <c r="F190" s="103"/>
-      <c r="G190" s="103"/>
-      <c r="H190" s="103"/>
-      <c r="I190" s="103"/>
-      <c r="J190" s="103"/>
-      <c r="K190" s="103"/>
+      <c r="D190" s="102"/>
+      <c r="E190" s="102"/>
+      <c r="F190" s="102"/>
+      <c r="G190" s="102"/>
+      <c r="H190" s="102"/>
+      <c r="I190" s="102"/>
+      <c r="J190" s="102"/>
+      <c r="K190" s="102"/>
       <c r="L190" s="30"/>
       <c r="M190" s="30"/>
       <c r="N190" s="30"/>
@@ -8900,14 +8899,14 @@
       <c r="C191" s="54" t="s">
         <v>143</v>
       </c>
-      <c r="D191" s="103"/>
-      <c r="E191" s="103"/>
-      <c r="F191" s="103"/>
-      <c r="G191" s="103"/>
-      <c r="H191" s="103"/>
-      <c r="I191" s="103"/>
-      <c r="J191" s="103"/>
-      <c r="K191" s="103"/>
+      <c r="D191" s="102"/>
+      <c r="E191" s="102"/>
+      <c r="F191" s="102"/>
+      <c r="G191" s="102"/>
+      <c r="H191" s="102"/>
+      <c r="I191" s="102"/>
+      <c r="J191" s="102"/>
+      <c r="K191" s="102"/>
       <c r="L191" s="30"/>
       <c r="M191" s="30"/>
       <c r="N191" s="30"/>
@@ -8924,14 +8923,14 @@
       <c r="C192" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="D192" s="103"/>
-      <c r="E192" s="103"/>
-      <c r="F192" s="103"/>
-      <c r="G192" s="103"/>
-      <c r="H192" s="103"/>
-      <c r="I192" s="103"/>
-      <c r="J192" s="103"/>
-      <c r="K192" s="103"/>
+      <c r="D192" s="102"/>
+      <c r="E192" s="102"/>
+      <c r="F192" s="102"/>
+      <c r="G192" s="102"/>
+      <c r="H192" s="102"/>
+      <c r="I192" s="102"/>
+      <c r="J192" s="102"/>
+      <c r="K192" s="102"/>
       <c r="L192" s="30"/>
       <c r="M192" s="30"/>
       <c r="N192" s="30"/>
@@ -8948,14 +8947,14 @@
       <c r="C193" s="54" t="s">
         <v>142</v>
       </c>
-      <c r="D193" s="103"/>
-      <c r="E193" s="103"/>
-      <c r="F193" s="103"/>
-      <c r="G193" s="103"/>
-      <c r="H193" s="103"/>
-      <c r="I193" s="103"/>
-      <c r="J193" s="103"/>
-      <c r="K193" s="103"/>
+      <c r="D193" s="102"/>
+      <c r="E193" s="102"/>
+      <c r="F193" s="102"/>
+      <c r="G193" s="102"/>
+      <c r="H193" s="102"/>
+      <c r="I193" s="102"/>
+      <c r="J193" s="102"/>
+      <c r="K193" s="102"/>
       <c r="L193" s="30"/>
       <c r="M193" s="30"/>
       <c r="N193" s="30"/>
@@ -8972,14 +8971,14 @@
       <c r="C194" s="54" t="s">
         <v>140</v>
       </c>
-      <c r="D194" s="103"/>
-      <c r="E194" s="103"/>
-      <c r="F194" s="103"/>
-      <c r="G194" s="103"/>
-      <c r="H194" s="103"/>
-      <c r="I194" s="103"/>
-      <c r="J194" s="103"/>
-      <c r="K194" s="103"/>
+      <c r="D194" s="102"/>
+      <c r="E194" s="102"/>
+      <c r="F194" s="102"/>
+      <c r="G194" s="102"/>
+      <c r="H194" s="102"/>
+      <c r="I194" s="102"/>
+      <c r="J194" s="102"/>
+      <c r="K194" s="102"/>
       <c r="L194" s="30"/>
       <c r="M194" s="30"/>
       <c r="N194" s="30"/>
@@ -8996,14 +8995,14 @@
       <c r="C195" s="54" t="s">
         <v>140</v>
       </c>
-      <c r="D195" s="103"/>
-      <c r="E195" s="103"/>
-      <c r="F195" s="103"/>
-      <c r="G195" s="103"/>
-      <c r="H195" s="103"/>
-      <c r="I195" s="103"/>
-      <c r="J195" s="103"/>
-      <c r="K195" s="103"/>
+      <c r="D195" s="102"/>
+      <c r="E195" s="102"/>
+      <c r="F195" s="102"/>
+      <c r="G195" s="102"/>
+      <c r="H195" s="102"/>
+      <c r="I195" s="102"/>
+      <c r="J195" s="102"/>
+      <c r="K195" s="102"/>
       <c r="L195" s="30"/>
       <c r="M195" s="30"/>
       <c r="N195" s="30"/>
@@ -9020,14 +9019,14 @@
       <c r="C196" s="54" t="s">
         <v>140</v>
       </c>
-      <c r="D196" s="103"/>
-      <c r="E196" s="103"/>
-      <c r="F196" s="103"/>
-      <c r="G196" s="103"/>
-      <c r="H196" s="103"/>
-      <c r="I196" s="103"/>
-      <c r="J196" s="103"/>
-      <c r="K196" s="103"/>
+      <c r="D196" s="102"/>
+      <c r="E196" s="102"/>
+      <c r="F196" s="102"/>
+      <c r="G196" s="102"/>
+      <c r="H196" s="102"/>
+      <c r="I196" s="102"/>
+      <c r="J196" s="102"/>
+      <c r="K196" s="102"/>
       <c r="L196" s="30"/>
       <c r="M196" s="30"/>
       <c r="N196" s="30"/>
@@ -9044,14 +9043,14 @@
       <c r="C197" s="54" t="s">
         <v>140</v>
       </c>
-      <c r="D197" s="103"/>
-      <c r="E197" s="103"/>
-      <c r="F197" s="103"/>
-      <c r="G197" s="103"/>
-      <c r="H197" s="103"/>
-      <c r="I197" s="103"/>
-      <c r="J197" s="103"/>
-      <c r="K197" s="103"/>
+      <c r="D197" s="102"/>
+      <c r="E197" s="102"/>
+      <c r="F197" s="102"/>
+      <c r="G197" s="102"/>
+      <c r="H197" s="102"/>
+      <c r="I197" s="102"/>
+      <c r="J197" s="102"/>
+      <c r="K197" s="102"/>
       <c r="L197" s="30"/>
       <c r="M197" s="30"/>
       <c r="N197" s="30"/>
@@ -9068,14 +9067,14 @@
       <c r="C198" s="54" t="s">
         <v>140</v>
       </c>
-      <c r="D198" s="103"/>
-      <c r="E198" s="103"/>
-      <c r="F198" s="103"/>
-      <c r="G198" s="103"/>
-      <c r="H198" s="103"/>
-      <c r="I198" s="103"/>
-      <c r="J198" s="103"/>
-      <c r="K198" s="103"/>
+      <c r="D198" s="102"/>
+      <c r="E198" s="102"/>
+      <c r="F198" s="102"/>
+      <c r="G198" s="102"/>
+      <c r="H198" s="102"/>
+      <c r="I198" s="102"/>
+      <c r="J198" s="102"/>
+      <c r="K198" s="102"/>
       <c r="L198" s="30"/>
       <c r="M198" s="30"/>
       <c r="N198" s="30"/>
@@ -9092,14 +9091,14 @@
       <c r="C199" s="54" t="s">
         <v>140</v>
       </c>
-      <c r="D199" s="103"/>
-      <c r="E199" s="103"/>
-      <c r="F199" s="103"/>
-      <c r="G199" s="103"/>
-      <c r="H199" s="103"/>
-      <c r="I199" s="103"/>
-      <c r="J199" s="103"/>
-      <c r="K199" s="103"/>
+      <c r="D199" s="102"/>
+      <c r="E199" s="102"/>
+      <c r="F199" s="102"/>
+      <c r="G199" s="102"/>
+      <c r="H199" s="102"/>
+      <c r="I199" s="102"/>
+      <c r="J199" s="102"/>
+      <c r="K199" s="102"/>
       <c r="L199" s="30"/>
       <c r="M199" s="30"/>
       <c r="N199" s="30"/>
@@ -9116,14 +9115,14 @@
       <c r="C200" s="54" t="s">
         <v>140</v>
       </c>
-      <c r="D200" s="103"/>
-      <c r="E200" s="103"/>
-      <c r="F200" s="103"/>
-      <c r="G200" s="103"/>
-      <c r="H200" s="103"/>
-      <c r="I200" s="103"/>
-      <c r="J200" s="103"/>
-      <c r="K200" s="103"/>
+      <c r="D200" s="102"/>
+      <c r="E200" s="102"/>
+      <c r="F200" s="102"/>
+      <c r="G200" s="102"/>
+      <c r="H200" s="102"/>
+      <c r="I200" s="102"/>
+      <c r="J200" s="102"/>
+      <c r="K200" s="102"/>
       <c r="L200" s="30"/>
       <c r="M200" s="30"/>
       <c r="N200" s="30"/>
@@ -9140,14 +9139,14 @@
       <c r="C201" s="54" t="s">
         <v>140</v>
       </c>
-      <c r="D201" s="103"/>
-      <c r="E201" s="103"/>
-      <c r="F201" s="103"/>
-      <c r="G201" s="103"/>
-      <c r="H201" s="103"/>
-      <c r="I201" s="103"/>
-      <c r="J201" s="103"/>
-      <c r="K201" s="103"/>
+      <c r="D201" s="102"/>
+      <c r="E201" s="102"/>
+      <c r="F201" s="102"/>
+      <c r="G201" s="102"/>
+      <c r="H201" s="102"/>
+      <c r="I201" s="102"/>
+      <c r="J201" s="102"/>
+      <c r="K201" s="102"/>
       <c r="L201" s="30"/>
       <c r="M201" s="30"/>
       <c r="N201" s="30"/>
@@ -9164,14 +9163,14 @@
       <c r="C202" s="54" t="s">
         <v>141</v>
       </c>
-      <c r="D202" s="103"/>
-      <c r="E202" s="103"/>
-      <c r="F202" s="103"/>
-      <c r="G202" s="103"/>
-      <c r="H202" s="103"/>
-      <c r="I202" s="103"/>
-      <c r="J202" s="103"/>
-      <c r="K202" s="103"/>
+      <c r="D202" s="102"/>
+      <c r="E202" s="102"/>
+      <c r="F202" s="102"/>
+      <c r="G202" s="102"/>
+      <c r="H202" s="102"/>
+      <c r="I202" s="102"/>
+      <c r="J202" s="102"/>
+      <c r="K202" s="102"/>
       <c r="L202" s="30"/>
       <c r="M202" s="30"/>
       <c r="N202" s="30"/>
@@ -9188,14 +9187,14 @@
       <c r="C203" s="54" t="s">
         <v>141</v>
       </c>
-      <c r="D203" s="103"/>
-      <c r="E203" s="103"/>
-      <c r="F203" s="103"/>
-      <c r="G203" s="103"/>
-      <c r="H203" s="103"/>
-      <c r="I203" s="103"/>
-      <c r="J203" s="103"/>
-      <c r="K203" s="103"/>
+      <c r="D203" s="102"/>
+      <c r="E203" s="102"/>
+      <c r="F203" s="102"/>
+      <c r="G203" s="102"/>
+      <c r="H203" s="102"/>
+      <c r="I203" s="102"/>
+      <c r="J203" s="102"/>
+      <c r="K203" s="102"/>
       <c r="L203" s="30"/>
       <c r="M203" s="30"/>
       <c r="N203" s="30"/>
@@ -9212,14 +9211,14 @@
       <c r="C204" s="54" t="s">
         <v>141</v>
       </c>
-      <c r="D204" s="103"/>
-      <c r="E204" s="103"/>
-      <c r="F204" s="103"/>
-      <c r="G204" s="103"/>
-      <c r="H204" s="103"/>
-      <c r="I204" s="103"/>
-      <c r="J204" s="103"/>
-      <c r="K204" s="103"/>
+      <c r="D204" s="102"/>
+      <c r="E204" s="102"/>
+      <c r="F204" s="102"/>
+      <c r="G204" s="102"/>
+      <c r="H204" s="102"/>
+      <c r="I204" s="102"/>
+      <c r="J204" s="102"/>
+      <c r="K204" s="102"/>
       <c r="L204" s="30"/>
       <c r="M204" s="30"/>
       <c r="N204" s="30"/>
@@ -9236,14 +9235,14 @@
       <c r="C205" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="D205" s="103"/>
-      <c r="E205" s="103"/>
-      <c r="F205" s="103"/>
-      <c r="G205" s="103"/>
-      <c r="H205" s="103"/>
-      <c r="I205" s="103"/>
-      <c r="J205" s="103"/>
-      <c r="K205" s="103"/>
+      <c r="D205" s="102"/>
+      <c r="E205" s="102"/>
+      <c r="F205" s="102"/>
+      <c r="G205" s="102"/>
+      <c r="H205" s="102"/>
+      <c r="I205" s="102"/>
+      <c r="J205" s="102"/>
+      <c r="K205" s="102"/>
       <c r="L205" s="30"/>
       <c r="M205" s="30"/>
       <c r="N205" s="30"/>
@@ -9260,14 +9259,14 @@
       <c r="C206" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="D206" s="103"/>
-      <c r="E206" s="103"/>
-      <c r="F206" s="103"/>
-      <c r="G206" s="103"/>
-      <c r="H206" s="103"/>
-      <c r="I206" s="103"/>
-      <c r="J206" s="103"/>
-      <c r="K206" s="103"/>
+      <c r="D206" s="102"/>
+      <c r="E206" s="102"/>
+      <c r="F206" s="102"/>
+      <c r="G206" s="102"/>
+      <c r="H206" s="102"/>
+      <c r="I206" s="102"/>
+      <c r="J206" s="102"/>
+      <c r="K206" s="102"/>
       <c r="L206" s="30"/>
       <c r="M206" s="30"/>
       <c r="N206" s="30"/>
@@ -9284,14 +9283,14 @@
       <c r="C207" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="D207" s="103"/>
-      <c r="E207" s="103"/>
-      <c r="F207" s="103"/>
-      <c r="G207" s="103"/>
-      <c r="H207" s="103"/>
-      <c r="I207" s="103"/>
-      <c r="J207" s="103"/>
-      <c r="K207" s="103"/>
+      <c r="D207" s="102"/>
+      <c r="E207" s="102"/>
+      <c r="F207" s="102"/>
+      <c r="G207" s="102"/>
+      <c r="H207" s="102"/>
+      <c r="I207" s="102"/>
+      <c r="J207" s="102"/>
+      <c r="K207" s="102"/>
       <c r="L207" s="30"/>
       <c r="M207" s="30"/>
       <c r="N207" s="30"/>
@@ -9308,14 +9307,14 @@
       <c r="C208" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="D208" s="103"/>
-      <c r="E208" s="103"/>
-      <c r="F208" s="103"/>
-      <c r="G208" s="103"/>
-      <c r="H208" s="103"/>
-      <c r="I208" s="103"/>
-      <c r="J208" s="103"/>
-      <c r="K208" s="103"/>
+      <c r="D208" s="102"/>
+      <c r="E208" s="102"/>
+      <c r="F208" s="102"/>
+      <c r="G208" s="102"/>
+      <c r="H208" s="102"/>
+      <c r="I208" s="102"/>
+      <c r="J208" s="102"/>
+      <c r="K208" s="102"/>
       <c r="L208" s="30"/>
       <c r="M208" s="30"/>
       <c r="N208" s="30"/>
@@ -9332,14 +9331,14 @@
       <c r="C209" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="D209" s="103"/>
-      <c r="E209" s="103"/>
-      <c r="F209" s="103"/>
-      <c r="G209" s="103"/>
-      <c r="H209" s="103"/>
-      <c r="I209" s="103"/>
-      <c r="J209" s="103"/>
-      <c r="K209" s="103"/>
+      <c r="D209" s="102"/>
+      <c r="E209" s="102"/>
+      <c r="F209" s="102"/>
+      <c r="G209" s="102"/>
+      <c r="H209" s="102"/>
+      <c r="I209" s="102"/>
+      <c r="J209" s="102"/>
+      <c r="K209" s="102"/>
       <c r="L209" s="30"/>
       <c r="M209" s="30"/>
       <c r="N209" s="30"/>
@@ -9356,14 +9355,14 @@
       <c r="C210" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="D210" s="103"/>
-      <c r="E210" s="103"/>
-      <c r="F210" s="103"/>
-      <c r="G210" s="103"/>
-      <c r="H210" s="103"/>
-      <c r="I210" s="103"/>
-      <c r="J210" s="103"/>
-      <c r="K210" s="103"/>
+      <c r="D210" s="102"/>
+      <c r="E210" s="102"/>
+      <c r="F210" s="102"/>
+      <c r="G210" s="102"/>
+      <c r="H210" s="102"/>
+      <c r="I210" s="102"/>
+      <c r="J210" s="102"/>
+      <c r="K210" s="102"/>
       <c r="L210" s="30"/>
       <c r="M210" s="30"/>
       <c r="N210" s="30"/>
@@ -9380,14 +9379,14 @@
       <c r="C211" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="D211" s="103"/>
-      <c r="E211" s="103"/>
-      <c r="F211" s="103"/>
-      <c r="G211" s="103"/>
-      <c r="H211" s="103"/>
-      <c r="I211" s="103"/>
-      <c r="J211" s="103"/>
-      <c r="K211" s="103"/>
+      <c r="D211" s="102"/>
+      <c r="E211" s="102"/>
+      <c r="F211" s="102"/>
+      <c r="G211" s="102"/>
+      <c r="H211" s="102"/>
+      <c r="I211" s="102"/>
+      <c r="J211" s="102"/>
+      <c r="K211" s="102"/>
       <c r="L211" s="30"/>
       <c r="M211" s="30"/>
       <c r="N211" s="30"/>
@@ -9404,14 +9403,14 @@
       <c r="C212" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="D212" s="103"/>
-      <c r="E212" s="103"/>
-      <c r="F212" s="103"/>
-      <c r="G212" s="103"/>
-      <c r="H212" s="103"/>
-      <c r="I212" s="103"/>
-      <c r="J212" s="103"/>
-      <c r="K212" s="103"/>
+      <c r="D212" s="102"/>
+      <c r="E212" s="102"/>
+      <c r="F212" s="102"/>
+      <c r="G212" s="102"/>
+      <c r="H212" s="102"/>
+      <c r="I212" s="102"/>
+      <c r="J212" s="102"/>
+      <c r="K212" s="102"/>
       <c r="L212" s="30"/>
       <c r="M212" s="30"/>
       <c r="N212" s="30"/>
@@ -9424,14 +9423,14 @@
       <c r="A213" s="30"/>
       <c r="B213" s="36"/>
       <c r="C213" s="43"/>
-      <c r="D213" s="103"/>
-      <c r="E213" s="103"/>
-      <c r="F213" s="103"/>
-      <c r="G213" s="103"/>
-      <c r="H213" s="103"/>
-      <c r="I213" s="103"/>
-      <c r="J213" s="103"/>
-      <c r="K213" s="103"/>
+      <c r="D213" s="102"/>
+      <c r="E213" s="102"/>
+      <c r="F213" s="102"/>
+      <c r="G213" s="102"/>
+      <c r="H213" s="102"/>
+      <c r="I213" s="102"/>
+      <c r="J213" s="102"/>
+      <c r="K213" s="102"/>
       <c r="L213" s="30"/>
       <c r="M213" s="30"/>
       <c r="N213" s="30"/>
@@ -9444,14 +9443,14 @@
       <c r="A214" s="30"/>
       <c r="B214" s="36"/>
       <c r="C214" s="43"/>
-      <c r="D214" s="103"/>
-      <c r="E214" s="103"/>
-      <c r="F214" s="103"/>
-      <c r="G214" s="103"/>
-      <c r="H214" s="103"/>
-      <c r="I214" s="103"/>
-      <c r="J214" s="103"/>
-      <c r="K214" s="103"/>
+      <c r="D214" s="102"/>
+      <c r="E214" s="102"/>
+      <c r="F214" s="102"/>
+      <c r="G214" s="102"/>
+      <c r="H214" s="102"/>
+      <c r="I214" s="102"/>
+      <c r="J214" s="102"/>
+      <c r="K214" s="102"/>
       <c r="L214" s="30"/>
       <c r="M214" s="30"/>
       <c r="N214" s="30"/>
@@ -9462,16 +9461,16 @@
     </row>
     <row r="215" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A215" s="30"/>
-      <c r="B215" s="103"/>
-      <c r="C215" s="103"/>
-      <c r="D215" s="103"/>
-      <c r="E215" s="103"/>
-      <c r="F215" s="103"/>
-      <c r="G215" s="103"/>
-      <c r="H215" s="103"/>
-      <c r="I215" s="103"/>
-      <c r="J215" s="103"/>
-      <c r="K215" s="103"/>
+      <c r="B215" s="102"/>
+      <c r="C215" s="102"/>
+      <c r="D215" s="102"/>
+      <c r="E215" s="102"/>
+      <c r="F215" s="102"/>
+      <c r="G215" s="102"/>
+      <c r="H215" s="102"/>
+      <c r="I215" s="102"/>
+      <c r="J215" s="102"/>
+      <c r="K215" s="102"/>
       <c r="L215" s="30"/>
       <c r="M215" s="30"/>
       <c r="N215" s="30"/>
@@ -9482,16 +9481,16 @@
     </row>
     <row r="216" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A216" s="30"/>
-      <c r="B216" s="103"/>
-      <c r="C216" s="103"/>
-      <c r="D216" s="103"/>
-      <c r="E216" s="103"/>
-      <c r="F216" s="103"/>
-      <c r="G216" s="103"/>
-      <c r="H216" s="103"/>
-      <c r="I216" s="103"/>
-      <c r="J216" s="103"/>
-      <c r="K216" s="103"/>
+      <c r="B216" s="102"/>
+      <c r="C216" s="102"/>
+      <c r="D216" s="102"/>
+      <c r="E216" s="102"/>
+      <c r="F216" s="102"/>
+      <c r="G216" s="102"/>
+      <c r="H216" s="102"/>
+      <c r="I216" s="102"/>
+      <c r="J216" s="102"/>
+      <c r="K216" s="102"/>
       <c r="L216" s="30"/>
       <c r="M216" s="30"/>
       <c r="N216" s="30"/>
@@ -9562,7 +9561,7 @@
       <c r="F2" s="82" t="s">
         <v>152</v>
       </c>
-      <c r="H2" s="114" t="s">
+      <c r="H2" s="103" t="s">
         <v>200</v>
       </c>
     </row>
@@ -9611,7 +9610,10 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="87"/>
-      <c r="B5" s="83"/>
+      <c r="B5" s="83" t="str">
+        <f t="shared" ref="B5:B68" si="1">CONCATENATE($A$1,A5)</f>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C5" s="90" t="s">
         <v>157</v>
       </c>
@@ -9619,7 +9621,10 @@
         <v>17</v>
       </c>
       <c r="E5" s="87"/>
-      <c r="F5" s="84"/>
+      <c r="F5" s="83" t="str">
+        <f t="shared" ref="F5:F68" si="2">CONCATENATE($E$1,E5)</f>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G5" s="86" t="str">
         <f t="shared" si="0"/>
         <v>ALAN SOUTO</v>
@@ -9627,7 +9632,10 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="87"/>
-      <c r="B6" s="84"/>
+      <c r="B6" s="83" t="str">
+        <f t="shared" si="1"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C6" s="90" t="s">
         <v>157</v>
       </c>
@@ -9635,7 +9643,10 @@
         <v>37</v>
       </c>
       <c r="E6" s="87"/>
-      <c r="F6" s="84"/>
+      <c r="F6" s="83" t="str">
+        <f t="shared" si="2"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G6" s="86" t="str">
         <f t="shared" si="0"/>
         <v>ALAN SOUTO</v>
@@ -9643,7 +9654,10 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="87"/>
-      <c r="B7" s="84"/>
+      <c r="B7" s="83" t="str">
+        <f t="shared" si="1"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C7" s="90" t="s">
         <v>157</v>
       </c>
@@ -9651,7 +9665,10 @@
         <v>50</v>
       </c>
       <c r="E7" s="87"/>
-      <c r="F7" s="84"/>
+      <c r="F7" s="83" t="str">
+        <f t="shared" si="2"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G7" s="86" t="str">
         <f t="shared" si="0"/>
         <v>ALAN SOUTO</v>
@@ -9659,7 +9676,10 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="83"/>
-      <c r="B8" s="83"/>
+      <c r="B8" s="83" t="str">
+        <f t="shared" si="1"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C8" s="85" t="s">
         <v>157</v>
       </c>
@@ -9667,7 +9687,10 @@
         <v>108</v>
       </c>
       <c r="E8" s="83"/>
-      <c r="F8" s="83"/>
+      <c r="F8" s="83" t="str">
+        <f t="shared" si="2"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G8" s="86" t="str">
         <f t="shared" si="0"/>
         <v>ALAN SOUTO</v>
@@ -9675,7 +9698,10 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="87"/>
-      <c r="B9" s="84"/>
+      <c r="B9" s="83" t="str">
+        <f t="shared" si="1"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C9" s="90" t="s">
         <v>157</v>
       </c>
@@ -9683,7 +9709,10 @@
         <v>55</v>
       </c>
       <c r="E9" s="87"/>
-      <c r="F9" s="84"/>
+      <c r="F9" s="83" t="str">
+        <f t="shared" si="2"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G9" s="86" t="str">
         <f t="shared" si="0"/>
         <v>ALAN SOUTO</v>
@@ -9691,7 +9720,10 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="87"/>
-      <c r="B10" s="84"/>
+      <c r="B10" s="83" t="str">
+        <f t="shared" si="1"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C10" s="90" t="s">
         <v>157</v>
       </c>
@@ -9699,7 +9731,10 @@
         <v>60</v>
       </c>
       <c r="E10" s="87"/>
-      <c r="F10" s="84"/>
+      <c r="F10" s="83" t="str">
+        <f t="shared" si="2"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G10" s="86" t="str">
         <f t="shared" si="0"/>
         <v>ALAN SOUTO</v>
@@ -9707,7 +9742,10 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="83"/>
-      <c r="B11" s="83"/>
+      <c r="B11" s="83" t="str">
+        <f t="shared" si="1"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C11" s="85" t="s">
         <v>157</v>
       </c>
@@ -9715,7 +9753,10 @@
         <v>109</v>
       </c>
       <c r="E11" s="83"/>
-      <c r="F11" s="83"/>
+      <c r="F11" s="83" t="str">
+        <f t="shared" si="2"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G11" s="86" t="str">
         <f t="shared" si="0"/>
         <v>ALAN SOUTO</v>
@@ -9723,7 +9764,10 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="83"/>
-      <c r="B12" s="83"/>
+      <c r="B12" s="83" t="str">
+        <f t="shared" si="1"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C12" s="85" t="s">
         <v>157</v>
       </c>
@@ -9731,7 +9775,10 @@
         <v>111</v>
       </c>
       <c r="E12" s="83"/>
-      <c r="F12" s="83"/>
+      <c r="F12" s="83" t="str">
+        <f t="shared" si="2"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G12" s="86" t="str">
         <f t="shared" si="0"/>
         <v>ALAN SOUTO</v>
@@ -9739,7 +9786,10 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="83"/>
-      <c r="B13" s="83"/>
+      <c r="B13" s="83" t="str">
+        <f t="shared" si="1"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C13" s="85" t="s">
         <v>157</v>
       </c>
@@ -9747,7 +9797,10 @@
         <v>110</v>
       </c>
       <c r="E13" s="83"/>
-      <c r="F13" s="83"/>
+      <c r="F13" s="83" t="str">
+        <f t="shared" si="2"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G13" s="86" t="str">
         <f t="shared" si="0"/>
         <v>ALAN SOUTO</v>
@@ -9755,13 +9808,19 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="87"/>
-      <c r="B14" s="84"/>
+      <c r="B14" s="83" t="str">
+        <f t="shared" si="1"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C14" s="90" t="s">
         <v>157</v>
       </c>
       <c r="D14" s="89"/>
       <c r="E14" s="87"/>
-      <c r="F14" s="84"/>
+      <c r="F14" s="83" t="str">
+        <f t="shared" si="2"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G14" s="86" t="str">
         <f t="shared" si="0"/>
         <v>ALAN SOUTO</v>
@@ -9769,13 +9828,19 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="87"/>
-      <c r="B15" s="84"/>
+      <c r="B15" s="83" t="str">
+        <f t="shared" si="1"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C15" s="90" t="s">
         <v>157</v>
       </c>
       <c r="D15" s="89"/>
       <c r="E15" s="87"/>
-      <c r="F15" s="84"/>
+      <c r="F15" s="83" t="str">
+        <f t="shared" si="2"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G15" s="86" t="str">
         <f t="shared" si="0"/>
         <v>ALAN SOUTO</v>
@@ -9783,13 +9848,19 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="87"/>
-      <c r="B16" s="84"/>
+      <c r="B16" s="83" t="str">
+        <f t="shared" si="1"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C16" s="90" t="s">
         <v>157</v>
       </c>
       <c r="D16" s="89"/>
       <c r="E16" s="83"/>
-      <c r="F16" s="84"/>
+      <c r="F16" s="83" t="str">
+        <f t="shared" si="2"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G16" s="86" t="str">
         <f t="shared" si="0"/>
         <v>ALAN SOUTO</v>
@@ -9797,13 +9868,19 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="87"/>
-      <c r="B17" s="84"/>
+      <c r="B17" s="83" t="str">
+        <f t="shared" si="1"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C17" s="90" t="s">
         <v>157</v>
       </c>
       <c r="D17" s="89"/>
       <c r="E17" s="87"/>
-      <c r="F17" s="84"/>
+      <c r="F17" s="83" t="str">
+        <f t="shared" si="2"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G17" s="86" t="str">
         <f t="shared" si="0"/>
         <v>ALAN SOUTO</v>
@@ -9811,13 +9888,19 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="83"/>
-      <c r="B18" s="84"/>
+      <c r="B18" s="83" t="str">
+        <f t="shared" si="1"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C18" s="90" t="s">
         <v>157</v>
       </c>
       <c r="D18" s="89"/>
       <c r="E18" s="87"/>
-      <c r="F18" s="84"/>
+      <c r="F18" s="83" t="str">
+        <f t="shared" si="2"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G18" s="86" t="str">
         <f t="shared" si="0"/>
         <v>ALAN SOUTO</v>
@@ -9825,7 +9908,10 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="83"/>
-      <c r="B19" s="84"/>
+      <c r="B19" s="83" t="str">
+        <f t="shared" si="1"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C19" s="91" t="s">
         <v>160</v>
       </c>
@@ -9833,7 +9919,10 @@
         <v>161</v>
       </c>
       <c r="E19" s="87"/>
-      <c r="F19" s="84"/>
+      <c r="F19" s="83" t="str">
+        <f t="shared" si="2"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G19" s="86" t="str">
         <f t="shared" si="0"/>
         <v>JEBNET</v>
@@ -9841,7 +9930,10 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="87"/>
-      <c r="B20" s="84"/>
+      <c r="B20" s="83" t="str">
+        <f t="shared" si="1"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C20" s="91" t="s">
         <v>160</v>
       </c>
@@ -9849,7 +9941,10 @@
         <v>14</v>
       </c>
       <c r="E20" s="87"/>
-      <c r="F20" s="84"/>
+      <c r="F20" s="83" t="str">
+        <f t="shared" si="2"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G20" s="86" t="str">
         <f t="shared" si="0"/>
         <v>JEBNET</v>
@@ -9857,7 +9952,10 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="87"/>
-      <c r="B21" s="84"/>
+      <c r="B21" s="83" t="str">
+        <f t="shared" si="1"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C21" s="91" t="s">
         <v>160</v>
       </c>
@@ -9865,7 +9963,10 @@
         <v>18</v>
       </c>
       <c r="E21" s="87"/>
-      <c r="F21" s="84"/>
+      <c r="F21" s="83" t="str">
+        <f t="shared" si="2"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G21" s="86" t="str">
         <f t="shared" si="0"/>
         <v>JEBNET</v>
@@ -9873,7 +9974,10 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="87"/>
-      <c r="B22" s="84"/>
+      <c r="B22" s="83" t="str">
+        <f t="shared" si="1"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C22" s="91" t="s">
         <v>160</v>
       </c>
@@ -9881,7 +9985,10 @@
         <v>28</v>
       </c>
       <c r="E22" s="83"/>
-      <c r="F22" s="84"/>
+      <c r="F22" s="83" t="str">
+        <f t="shared" si="2"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G22" s="86" t="str">
         <f t="shared" si="0"/>
         <v>JEBNET</v>
@@ -9889,7 +9996,10 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="87"/>
-      <c r="B23" s="84"/>
+      <c r="B23" s="83" t="str">
+        <f t="shared" si="1"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C23" s="91" t="s">
         <v>160</v>
       </c>
@@ -9897,7 +10007,10 @@
         <v>162</v>
       </c>
       <c r="E23" s="87"/>
-      <c r="F23" s="84"/>
+      <c r="F23" s="83" t="str">
+        <f t="shared" si="2"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G23" s="86" t="str">
         <f t="shared" si="0"/>
         <v>JEBNET</v>
@@ -9905,7 +10018,10 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="87"/>
-      <c r="B24" s="84"/>
+      <c r="B24" s="83" t="str">
+        <f t="shared" si="1"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C24" s="91" t="s">
         <v>160</v>
       </c>
@@ -9913,7 +10029,10 @@
         <v>163</v>
       </c>
       <c r="E24" s="87"/>
-      <c r="F24" s="84"/>
+      <c r="F24" s="83" t="str">
+        <f t="shared" si="2"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G24" s="86" t="str">
         <f t="shared" si="0"/>
         <v>JEBNET</v>
@@ -9921,7 +10040,10 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="87"/>
-      <c r="B25" s="84"/>
+      <c r="B25" s="83" t="str">
+        <f t="shared" si="1"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C25" s="91" t="s">
         <v>160</v>
       </c>
@@ -9929,7 +10051,10 @@
         <v>164</v>
       </c>
       <c r="E25" s="87"/>
-      <c r="F25" s="84"/>
+      <c r="F25" s="83" t="str">
+        <f t="shared" si="2"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G25" s="86" t="str">
         <f t="shared" si="0"/>
         <v>JEBNET</v>
@@ -9937,7 +10062,10 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="83"/>
-      <c r="B26" s="84"/>
+      <c r="B26" s="83" t="str">
+        <f t="shared" si="1"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C26" s="91" t="s">
         <v>160</v>
       </c>
@@ -9945,7 +10073,10 @@
         <v>165</v>
       </c>
       <c r="E26" s="87"/>
-      <c r="F26" s="84"/>
+      <c r="F26" s="83" t="str">
+        <f t="shared" si="2"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G26" s="86" t="str">
         <f t="shared" si="0"/>
         <v>JEBNET</v>
@@ -9953,7 +10084,10 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="87"/>
-      <c r="B27" s="84"/>
+      <c r="B27" s="83" t="str">
+        <f t="shared" si="1"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C27" s="91" t="s">
         <v>160</v>
       </c>
@@ -9961,7 +10095,10 @@
         <v>130</v>
       </c>
       <c r="E27" s="83"/>
-      <c r="F27" s="84"/>
+      <c r="F27" s="83" t="str">
+        <f t="shared" si="2"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G27" s="86" t="str">
         <f t="shared" si="0"/>
         <v>JEBNET</v>
@@ -9969,7 +10106,10 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="87"/>
-      <c r="B28" s="84"/>
+      <c r="B28" s="83" t="str">
+        <f t="shared" si="1"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C28" s="91" t="s">
         <v>160</v>
       </c>
@@ -9977,7 +10117,10 @@
         <v>49</v>
       </c>
       <c r="E28" s="87"/>
-      <c r="F28" s="84"/>
+      <c r="F28" s="83" t="str">
+        <f t="shared" si="2"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G28" s="86" t="str">
         <f t="shared" si="0"/>
         <v>JEBNET</v>
@@ -9985,7 +10128,10 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="87"/>
-      <c r="B29" s="84"/>
+      <c r="B29" s="83" t="str">
+        <f t="shared" si="1"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C29" s="91" t="s">
         <v>160</v>
       </c>
@@ -9993,7 +10139,10 @@
         <v>134</v>
       </c>
       <c r="E29" s="87"/>
-      <c r="F29" s="84"/>
+      <c r="F29" s="83" t="str">
+        <f t="shared" si="2"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G29" s="86" t="str">
         <f t="shared" si="0"/>
         <v>JEBNET</v>
@@ -10001,7 +10150,10 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="87"/>
-      <c r="B30" s="84"/>
+      <c r="B30" s="83" t="str">
+        <f t="shared" si="1"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C30" s="91" t="s">
         <v>160</v>
       </c>
@@ -10009,7 +10161,10 @@
         <v>65</v>
       </c>
       <c r="E30" s="87"/>
-      <c r="F30" s="84"/>
+      <c r="F30" s="83" t="str">
+        <f t="shared" si="2"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G30" s="86" t="str">
         <f t="shared" si="0"/>
         <v>JEBNET</v>
@@ -10017,7 +10172,10 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="87"/>
-      <c r="B31" s="84"/>
+      <c r="B31" s="83" t="str">
+        <f t="shared" si="1"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C31" s="91" t="s">
         <v>160</v>
       </c>
@@ -10025,7 +10183,10 @@
         <v>71</v>
       </c>
       <c r="E31" s="87"/>
-      <c r="F31" s="84"/>
+      <c r="F31" s="83" t="str">
+        <f t="shared" si="2"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G31" s="86" t="str">
         <f t="shared" si="0"/>
         <v>JEBNET</v>
@@ -10033,7 +10194,10 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="83"/>
-      <c r="B32" s="84"/>
+      <c r="B32" s="83" t="str">
+        <f t="shared" si="1"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C32" s="91" t="s">
         <v>160</v>
       </c>
@@ -10041,7 +10205,10 @@
         <v>72</v>
       </c>
       <c r="E32" s="87"/>
-      <c r="F32" s="84"/>
+      <c r="F32" s="83" t="str">
+        <f t="shared" si="2"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G32" s="86" t="str">
         <f t="shared" si="0"/>
         <v>JEBNET</v>
@@ -10052,7 +10219,7 @@
         <v>85991012568</v>
       </c>
       <c r="B33" s="83" t="str">
-        <f>CONCATENATE(A1,A33)</f>
+        <f t="shared" si="1"/>
         <v>WA.ME/5585991012568</v>
       </c>
       <c r="C33" s="88" t="s">
@@ -10065,20 +10232,20 @@
         <v>85991012568</v>
       </c>
       <c r="F33" s="83" t="str">
-        <f>CONCATENATE(E1,E33)</f>
+        <f t="shared" si="2"/>
         <v>WA.ME/5585991012568</v>
       </c>
       <c r="G33" s="86" t="str">
         <f t="shared" si="0"/>
         <v>JOSE LEONARDO</v>
       </c>
-      <c r="H33">
-        <v>64652564368</v>
-      </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="87"/>
-      <c r="B34" s="84"/>
+      <c r="B34" s="83" t="str">
+        <f t="shared" si="1"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C34" s="88" t="s">
         <v>158</v>
       </c>
@@ -10086,7 +10253,10 @@
         <v>24</v>
       </c>
       <c r="E34" s="87"/>
-      <c r="F34" s="84"/>
+      <c r="F34" s="83" t="str">
+        <f t="shared" si="2"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G34" s="86" t="str">
         <f t="shared" si="0"/>
         <v>JOSE LEONARDO</v>
@@ -10094,7 +10264,10 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="87"/>
-      <c r="B35" s="84"/>
+      <c r="B35" s="83" t="str">
+        <f t="shared" si="1"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C35" s="88" t="s">
         <v>158</v>
       </c>
@@ -10102,15 +10275,21 @@
         <v>31</v>
       </c>
       <c r="E35" s="87"/>
-      <c r="F35" s="84"/>
+      <c r="F35" s="83" t="str">
+        <f t="shared" si="2"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G35" s="86" t="str">
-        <f t="shared" ref="G35:G66" si="1">C35</f>
+        <f t="shared" ref="G35:G66" si="3">C35</f>
         <v>JOSE LEONARDO</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="87"/>
-      <c r="B36" s="84"/>
+      <c r="B36" s="83" t="str">
+        <f t="shared" si="1"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C36" s="88" t="s">
         <v>158</v>
       </c>
@@ -10118,15 +10297,21 @@
         <v>35</v>
       </c>
       <c r="E36" s="87"/>
-      <c r="F36" s="84"/>
+      <c r="F36" s="83" t="str">
+        <f t="shared" si="2"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G36" s="86" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>JOSE LEONARDO</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="87"/>
-      <c r="B37" s="84"/>
+      <c r="B37" s="83" t="str">
+        <f t="shared" si="1"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C37" s="88" t="s">
         <v>158</v>
       </c>
@@ -10134,15 +10319,21 @@
         <v>159</v>
       </c>
       <c r="E37" s="87"/>
-      <c r="F37" s="84"/>
+      <c r="F37" s="83" t="str">
+        <f t="shared" si="2"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G37" s="86" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>JOSE LEONARDO</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="87"/>
-      <c r="B38" s="84"/>
+      <c r="B38" s="83" t="str">
+        <f t="shared" si="1"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C38" s="88" t="s">
         <v>158</v>
       </c>
@@ -10150,15 +10341,21 @@
         <v>129</v>
       </c>
       <c r="E38" s="87"/>
-      <c r="F38" s="84"/>
+      <c r="F38" s="83" t="str">
+        <f t="shared" si="2"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G38" s="86" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>JOSE LEONARDO</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="87"/>
-      <c r="B39" s="84"/>
+      <c r="B39" s="83" t="str">
+        <f t="shared" si="1"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C39" s="88" t="s">
         <v>158</v>
       </c>
@@ -10166,15 +10363,21 @@
         <v>90</v>
       </c>
       <c r="E39" s="87"/>
-      <c r="F39" s="84"/>
+      <c r="F39" s="83" t="str">
+        <f t="shared" si="2"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G39" s="86" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>JOSE LEONARDO</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="87"/>
-      <c r="B40" s="84"/>
+      <c r="B40" s="83" t="str">
+        <f t="shared" si="1"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C40" s="88" t="s">
         <v>158</v>
       </c>
@@ -10182,31 +10385,48 @@
         <v>38</v>
       </c>
       <c r="E40" s="87"/>
-      <c r="F40" s="84"/>
+      <c r="F40" s="83" t="str">
+        <f t="shared" si="2"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G40" s="86" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>JOSE LEONARDO</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="87"/>
-      <c r="B41" s="84"/>
+      <c r="B41" s="83" t="str">
+        <f t="shared" si="1"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C41" s="88" t="s">
         <v>158</v>
       </c>
       <c r="D41" s="89" t="s">
         <v>188</v>
       </c>
-      <c r="E41" s="87"/>
-      <c r="F41" s="84"/>
+      <c r="E41" s="87">
+        <v>85981012568</v>
+      </c>
+      <c r="F41" s="83" t="str">
+        <f t="shared" si="2"/>
+        <v>WA.ME/5585981012568</v>
+      </c>
       <c r="G41" s="86" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>JOSE LEONARDO</v>
+      </c>
+      <c r="H41">
+        <v>64652564368</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="87"/>
-      <c r="B42" s="84"/>
+      <c r="B42" s="83" t="str">
+        <f t="shared" si="1"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C42" s="88" t="s">
         <v>158</v>
       </c>
@@ -10214,15 +10434,21 @@
         <v>40</v>
       </c>
       <c r="E42" s="87"/>
-      <c r="F42" s="84"/>
+      <c r="F42" s="83" t="str">
+        <f t="shared" si="2"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G42" s="86" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>JOSE LEONARDO</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="87"/>
-      <c r="B43" s="84"/>
+      <c r="B43" s="83" t="str">
+        <f t="shared" si="1"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C43" s="88" t="s">
         <v>158</v>
       </c>
@@ -10230,15 +10456,21 @@
         <v>41</v>
       </c>
       <c r="E43" s="87"/>
-      <c r="F43" s="84"/>
+      <c r="F43" s="83" t="str">
+        <f t="shared" si="2"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G43" s="86" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>JOSE LEONARDO</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="87"/>
-      <c r="B44" s="84"/>
+      <c r="B44" s="83" t="str">
+        <f t="shared" si="1"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C44" s="88" t="s">
         <v>158</v>
       </c>
@@ -10246,15 +10478,21 @@
         <v>42</v>
       </c>
       <c r="E44" s="87"/>
-      <c r="F44" s="84"/>
+      <c r="F44" s="83" t="str">
+        <f t="shared" si="2"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G44" s="86" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>JOSE LEONARDO</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="87"/>
-      <c r="B45" s="84"/>
+      <c r="B45" s="83" t="str">
+        <f t="shared" si="1"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C45" s="88" t="s">
         <v>158</v>
       </c>
@@ -10262,15 +10500,21 @@
         <v>43</v>
       </c>
       <c r="E45" s="87"/>
-      <c r="F45" s="84"/>
+      <c r="F45" s="83" t="str">
+        <f t="shared" si="2"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G45" s="86" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>JOSE LEONARDO</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="87"/>
-      <c r="B46" s="84"/>
+      <c r="B46" s="83" t="str">
+        <f t="shared" si="1"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C46" s="88" t="s">
         <v>158</v>
       </c>
@@ -10278,15 +10522,21 @@
         <v>189</v>
       </c>
       <c r="E46" s="87"/>
-      <c r="F46" s="84"/>
+      <c r="F46" s="83" t="str">
+        <f t="shared" si="2"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G46" s="86" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>JOSE LEONARDO</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="87"/>
-      <c r="B47" s="84"/>
+      <c r="B47" s="83" t="str">
+        <f t="shared" si="1"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C47" s="88" t="s">
         <v>158</v>
       </c>
@@ -10294,15 +10544,21 @@
         <v>46</v>
       </c>
       <c r="E47" s="87"/>
-      <c r="F47" s="84"/>
+      <c r="F47" s="83" t="str">
+        <f t="shared" si="2"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G47" s="86" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>JOSE LEONARDO</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="87"/>
-      <c r="B48" s="84"/>
+      <c r="B48" s="83" t="str">
+        <f t="shared" si="1"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C48" s="88" t="s">
         <v>158</v>
       </c>
@@ -10310,15 +10566,21 @@
         <v>190</v>
       </c>
       <c r="E48" s="87"/>
-      <c r="F48" s="84"/>
+      <c r="F48" s="83" t="str">
+        <f t="shared" si="2"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G48" s="86" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>JOSE LEONARDO</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="87"/>
-      <c r="B49" s="84"/>
+      <c r="B49" s="83" t="str">
+        <f t="shared" si="1"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C49" s="88" t="s">
         <v>158</v>
       </c>
@@ -10326,15 +10588,21 @@
         <v>51</v>
       </c>
       <c r="E49" s="87"/>
-      <c r="F49" s="84"/>
+      <c r="F49" s="83" t="str">
+        <f t="shared" si="2"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G49" s="86" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>JOSE LEONARDO</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="87"/>
-      <c r="B50" s="84"/>
+      <c r="B50" s="83" t="str">
+        <f t="shared" si="1"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C50" s="88" t="s">
         <v>158</v>
       </c>
@@ -10342,15 +10610,21 @@
         <v>57</v>
       </c>
       <c r="E50" s="87"/>
-      <c r="F50" s="84"/>
+      <c r="F50" s="83" t="str">
+        <f t="shared" si="2"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G50" s="86" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>JOSE LEONARDO</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" s="87"/>
-      <c r="B51" s="84"/>
+      <c r="B51" s="83" t="str">
+        <f t="shared" si="1"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C51" s="88" t="s">
         <v>158</v>
       </c>
@@ -10358,15 +10632,21 @@
         <v>93</v>
       </c>
       <c r="E51" s="87"/>
-      <c r="F51" s="84"/>
+      <c r="F51" s="83" t="str">
+        <f t="shared" si="2"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G51" s="86" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>JOSE LEONARDO</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" s="87"/>
-      <c r="B52" s="84"/>
+      <c r="B52" s="83" t="str">
+        <f t="shared" si="1"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C52" s="88" t="s">
         <v>158</v>
       </c>
@@ -10374,15 +10654,21 @@
         <v>63</v>
       </c>
       <c r="E52" s="87"/>
-      <c r="F52" s="84"/>
+      <c r="F52" s="83" t="str">
+        <f t="shared" si="2"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G52" s="86" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>JOSE LEONARDO</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" s="87"/>
-      <c r="B53" s="84"/>
+      <c r="B53" s="83" t="str">
+        <f t="shared" si="1"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C53" s="88" t="s">
         <v>158</v>
       </c>
@@ -10390,15 +10676,21 @@
         <v>64</v>
       </c>
       <c r="E53" s="87"/>
-      <c r="F53" s="84"/>
+      <c r="F53" s="83" t="str">
+        <f t="shared" si="2"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G53" s="86" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>JOSE LEONARDO</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" s="87"/>
-      <c r="B54" s="84"/>
+      <c r="B54" s="83" t="str">
+        <f t="shared" si="1"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C54" s="88" t="s">
         <v>158</v>
       </c>
@@ -10406,15 +10698,21 @@
         <v>98</v>
       </c>
       <c r="E54" s="87"/>
-      <c r="F54" s="84"/>
+      <c r="F54" s="83" t="str">
+        <f t="shared" si="2"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G54" s="86" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>JOSE LEONARDO</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" s="87"/>
-      <c r="B55" s="84"/>
+      <c r="B55" s="83" t="str">
+        <f t="shared" si="1"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C55" s="88" t="s">
         <v>158</v>
       </c>
@@ -10422,15 +10720,21 @@
         <v>70</v>
       </c>
       <c r="E55" s="87"/>
-      <c r="F55" s="84"/>
+      <c r="F55" s="83" t="str">
+        <f t="shared" si="2"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G55" s="86" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>JOSE LEONARDO</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" s="87"/>
-      <c r="B56" s="84"/>
+      <c r="B56" s="83" t="str">
+        <f t="shared" si="1"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C56" s="88" t="s">
         <v>158</v>
       </c>
@@ -10438,15 +10742,21 @@
         <v>74</v>
       </c>
       <c r="E56" s="87"/>
-      <c r="F56" s="84"/>
+      <c r="F56" s="83" t="str">
+        <f t="shared" si="2"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G56" s="86" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>JOSE LEONARDO</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" s="83"/>
-      <c r="B57" s="92"/>
+      <c r="B57" s="83" t="str">
+        <f t="shared" si="1"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C57" s="85" t="s">
         <v>166</v>
       </c>
@@ -10454,15 +10764,21 @@
         <v>170</v>
       </c>
       <c r="E57" s="83"/>
-      <c r="F57" s="92"/>
+      <c r="F57" s="83" t="str">
+        <f t="shared" si="2"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G57" s="86" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>MAILSON FRANCISCO</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" s="83"/>
-      <c r="B58" s="92"/>
+      <c r="B58" s="83" t="str">
+        <f t="shared" si="1"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C58" s="85" t="s">
         <v>166</v>
       </c>
@@ -10470,15 +10786,21 @@
         <v>168</v>
       </c>
       <c r="E58" s="83"/>
-      <c r="F58" s="92"/>
+      <c r="F58" s="83" t="str">
+        <f t="shared" si="2"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G58" s="86" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>MAILSON FRANCISCO</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" s="83"/>
-      <c r="B59" s="83"/>
+      <c r="B59" s="83" t="str">
+        <f t="shared" si="1"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C59" s="85" t="s">
         <v>166</v>
       </c>
@@ -10486,15 +10808,21 @@
         <v>185</v>
       </c>
       <c r="E59" s="83"/>
-      <c r="F59" s="83"/>
+      <c r="F59" s="83" t="str">
+        <f t="shared" si="2"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G59" s="86" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>MAILSON FRANCISCO</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" s="83"/>
-      <c r="B60" s="83"/>
+      <c r="B60" s="83" t="str">
+        <f t="shared" si="1"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C60" s="85" t="s">
         <v>166</v>
       </c>
@@ -10502,15 +10830,21 @@
         <v>117</v>
       </c>
       <c r="E60" s="83"/>
-      <c r="F60" s="83"/>
+      <c r="F60" s="83" t="str">
+        <f t="shared" si="2"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G60" s="86" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>MAILSON FRANCISCO</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" s="83"/>
-      <c r="B61" s="83"/>
+      <c r="B61" s="83" t="str">
+        <f t="shared" si="1"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C61" s="85" t="s">
         <v>166</v>
       </c>
@@ -10518,15 +10852,21 @@
         <v>116</v>
       </c>
       <c r="E61" s="83"/>
-      <c r="F61" s="83"/>
+      <c r="F61" s="83" t="str">
+        <f t="shared" si="2"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G61" s="86" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>MAILSON FRANCISCO</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" s="83"/>
-      <c r="B62" s="83"/>
+      <c r="B62" s="83" t="str">
+        <f t="shared" si="1"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C62" s="85" t="s">
         <v>166</v>
       </c>
@@ -10534,15 +10874,21 @@
         <v>187</v>
       </c>
       <c r="E62" s="83"/>
-      <c r="F62" s="83"/>
+      <c r="F62" s="83" t="str">
+        <f t="shared" si="2"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G62" s="86" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>MAILSON FRANCISCO</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" s="83"/>
-      <c r="B63" s="83"/>
+      <c r="B63" s="83" t="str">
+        <f t="shared" si="1"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C63" s="85" t="s">
         <v>166</v>
       </c>
@@ -10550,15 +10896,21 @@
         <v>118</v>
       </c>
       <c r="E63" s="83"/>
-      <c r="F63" s="83"/>
+      <c r="F63" s="83" t="str">
+        <f t="shared" si="2"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G63" s="86" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>MAILSON FRANCISCO</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" s="83"/>
-      <c r="B64" s="83"/>
+      <c r="B64" s="83" t="str">
+        <f t="shared" si="1"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C64" s="85" t="s">
         <v>166</v>
       </c>
@@ -10566,15 +10918,21 @@
         <v>113</v>
       </c>
       <c r="E64" s="83"/>
-      <c r="F64" s="83"/>
+      <c r="F64" s="83" t="str">
+        <f t="shared" si="2"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G64" s="86" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>MAILSON FRANCISCO</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" s="83"/>
-      <c r="B65" s="83"/>
+      <c r="B65" s="83" t="str">
+        <f t="shared" si="1"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C65" s="85" t="s">
         <v>166</v>
       </c>
@@ -10582,15 +10940,21 @@
         <v>119</v>
       </c>
       <c r="E65" s="83"/>
-      <c r="F65" s="83"/>
+      <c r="F65" s="83" t="str">
+        <f t="shared" si="2"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G65" s="86" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>MAILSON FRANCISCO</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" s="83"/>
-      <c r="B66" s="83"/>
+      <c r="B66" s="83" t="str">
+        <f t="shared" si="1"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C66" s="85" t="s">
         <v>166</v>
       </c>
@@ -10598,15 +10962,21 @@
         <v>192</v>
       </c>
       <c r="E66" s="83"/>
-      <c r="F66" s="83"/>
+      <c r="F66" s="83" t="str">
+        <f t="shared" si="2"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G66" s="86" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>MAILSON FRANCISCO</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" s="87"/>
-      <c r="B67" s="84"/>
+      <c r="B67" s="83" t="str">
+        <f t="shared" si="1"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C67" s="85" t="s">
         <v>166</v>
       </c>
@@ -10614,15 +10984,21 @@
         <v>193</v>
       </c>
       <c r="E67" s="87"/>
-      <c r="F67" s="84"/>
+      <c r="F67" s="83" t="str">
+        <f t="shared" si="2"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G67" s="86" t="str">
-        <f t="shared" ref="G67:G98" si="2">C67</f>
+        <f t="shared" ref="G67:G98" si="4">C67</f>
         <v>MAILSON FRANCISCO</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" s="83"/>
-      <c r="B68" s="92"/>
+      <c r="B68" s="83" t="str">
+        <f t="shared" si="1"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C68" s="85" t="s">
         <v>166</v>
       </c>
@@ -10630,15 +11006,21 @@
         <v>169</v>
       </c>
       <c r="E68" s="83"/>
-      <c r="F68" s="92"/>
+      <c r="F68" s="83" t="str">
+        <f t="shared" si="2"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G68" s="86" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>MAILSON FRANCISCO</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" s="83"/>
-      <c r="B69" s="92"/>
+      <c r="B69" s="83" t="str">
+        <f t="shared" ref="B69:B132" si="5">CONCATENATE($A$1,A69)</f>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C69" s="85" t="s">
         <v>166</v>
       </c>
@@ -10646,15 +11028,21 @@
         <v>167</v>
       </c>
       <c r="E69" s="83"/>
-      <c r="F69" s="92"/>
+      <c r="F69" s="83" t="str">
+        <f t="shared" ref="F69:F132" si="6">CONCATENATE($E$1,E69)</f>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G69" s="86" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>MAILSON FRANCISCO</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" s="83"/>
-      <c r="B70" s="83"/>
+      <c r="B70" s="83" t="str">
+        <f t="shared" si="5"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C70" s="85" t="s">
         <v>166</v>
       </c>
@@ -10662,675 +11050,933 @@
         <v>112</v>
       </c>
       <c r="E70" s="83"/>
-      <c r="F70" s="83"/>
+      <c r="F70" s="83" t="str">
+        <f t="shared" si="6"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G70" s="86" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>MAILSON FRANCISCO</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" s="83"/>
-      <c r="B71" s="83"/>
+      <c r="B71" s="83" t="str">
+        <f t="shared" si="5"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C71" s="85" t="s">
         <v>166</v>
       </c>
       <c r="D71" s="83"/>
       <c r="E71" s="83"/>
-      <c r="F71" s="83"/>
+      <c r="F71" s="83" t="str">
+        <f t="shared" si="6"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G71" s="86" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>MAILSON FRANCISCO</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" s="83"/>
-      <c r="B72" s="83"/>
+      <c r="B72" s="83" t="str">
+        <f t="shared" si="5"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C72" s="85" t="s">
         <v>166</v>
       </c>
       <c r="D72" s="83"/>
       <c r="E72" s="83"/>
-      <c r="F72" s="83"/>
+      <c r="F72" s="83" t="str">
+        <f t="shared" si="6"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G72" s="86" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>MAILSON FRANCISCO</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" s="83"/>
-      <c r="B73" s="83"/>
+      <c r="B73" s="83" t="str">
+        <f t="shared" si="5"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C73" s="85" t="s">
         <v>166</v>
       </c>
       <c r="D73" s="83"/>
       <c r="E73" s="83"/>
-      <c r="F73" s="83"/>
+      <c r="F73" s="83" t="str">
+        <f t="shared" si="6"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G73" s="86" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>MAILSON FRANCISCO</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" s="83"/>
-      <c r="B74" s="83"/>
+      <c r="B74" s="83" t="str">
+        <f t="shared" si="5"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C74" s="85" t="s">
         <v>166</v>
       </c>
       <c r="D74" s="83"/>
       <c r="E74" s="83"/>
-      <c r="F74" s="83"/>
+      <c r="F74" s="83" t="str">
+        <f t="shared" si="6"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G74" s="86" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>MAILSON FRANCISCO</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" s="83"/>
-      <c r="B75" s="83"/>
+      <c r="B75" s="83" t="str">
+        <f t="shared" si="5"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C75" s="85" t="s">
         <v>166</v>
       </c>
       <c r="D75" s="83"/>
       <c r="E75" s="83"/>
-      <c r="F75" s="83"/>
+      <c r="F75" s="83" t="str">
+        <f t="shared" si="6"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G75" s="86" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>MAILSON FRANCISCO</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" s="83"/>
-      <c r="B76" s="83"/>
+      <c r="B76" s="83" t="str">
+        <f t="shared" si="5"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C76" s="85" t="s">
         <v>166</v>
       </c>
       <c r="D76" s="83"/>
       <c r="E76" s="83"/>
-      <c r="F76" s="83"/>
+      <c r="F76" s="83" t="str">
+        <f t="shared" si="6"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G76" s="86" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>MAILSON FRANCISCO</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" s="87"/>
-      <c r="B77" s="84"/>
-      <c r="C77" s="93" t="s">
+      <c r="B77" s="83" t="str">
+        <f t="shared" si="5"/>
+        <v>WA.ME/55</v>
+      </c>
+      <c r="C77" s="92" t="s">
         <v>156</v>
       </c>
       <c r="D77" s="89" t="s">
         <v>102</v>
       </c>
       <c r="E77" s="87"/>
-      <c r="F77" s="84"/>
+      <c r="F77" s="83" t="str">
+        <f t="shared" si="6"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G77" s="86" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>MARCOS VICTOR</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" s="87"/>
-      <c r="B78" s="84"/>
-      <c r="C78" s="93" t="s">
+      <c r="B78" s="83" t="str">
+        <f t="shared" si="5"/>
+        <v>WA.ME/55</v>
+      </c>
+      <c r="C78" s="92" t="s">
         <v>156</v>
       </c>
       <c r="D78" s="89" t="s">
         <v>15</v>
       </c>
       <c r="E78" s="87"/>
-      <c r="F78" s="84"/>
+      <c r="F78" s="83" t="str">
+        <f t="shared" si="6"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G78" s="86" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>MARCOS VICTOR</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" s="87"/>
-      <c r="B79" s="84"/>
-      <c r="C79" s="93" t="s">
+      <c r="B79" s="83" t="str">
+        <f t="shared" si="5"/>
+        <v>WA.ME/55</v>
+      </c>
+      <c r="C79" s="92" t="s">
         <v>156</v>
       </c>
       <c r="D79" s="89" t="s">
         <v>105</v>
       </c>
       <c r="E79" s="87"/>
-      <c r="F79" s="84"/>
+      <c r="F79" s="83" t="str">
+        <f t="shared" si="6"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G79" s="86" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>MARCOS VICTOR</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" s="87"/>
-      <c r="B80" s="84"/>
-      <c r="C80" s="93" t="s">
+      <c r="B80" s="83" t="str">
+        <f t="shared" si="5"/>
+        <v>WA.ME/55</v>
+      </c>
+      <c r="C80" s="92" t="s">
         <v>156</v>
       </c>
       <c r="D80" s="89" t="s">
         <v>97</v>
       </c>
       <c r="E80" s="87"/>
-      <c r="F80" s="84"/>
+      <c r="F80" s="83" t="str">
+        <f t="shared" si="6"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G80" s="86" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>MARCOS VICTOR</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" s="87"/>
-      <c r="B81" s="84"/>
-      <c r="C81" s="93" t="s">
+      <c r="B81" s="83" t="str">
+        <f t="shared" si="5"/>
+        <v>WA.ME/55</v>
+      </c>
+      <c r="C81" s="92" t="s">
         <v>156</v>
       </c>
       <c r="D81" s="89" t="s">
         <v>16</v>
       </c>
       <c r="E81" s="87"/>
-      <c r="F81" s="84"/>
+      <c r="F81" s="83" t="str">
+        <f t="shared" si="6"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G81" s="86" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>MARCOS VICTOR</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" s="87"/>
-      <c r="B82" s="84"/>
-      <c r="C82" s="93" t="s">
+      <c r="B82" s="83" t="str">
+        <f t="shared" si="5"/>
+        <v>WA.ME/55</v>
+      </c>
+      <c r="C82" s="92" t="s">
         <v>156</v>
       </c>
       <c r="D82" s="89" t="s">
         <v>19</v>
       </c>
       <c r="E82" s="87"/>
-      <c r="F82" s="84"/>
+      <c r="F82" s="83" t="str">
+        <f t="shared" si="6"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G82" s="86" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>MARCOS VICTOR</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" s="87"/>
-      <c r="B83" s="84"/>
-      <c r="C83" s="93" t="s">
+      <c r="B83" s="83" t="str">
+        <f t="shared" si="5"/>
+        <v>WA.ME/55</v>
+      </c>
+      <c r="C83" s="92" t="s">
         <v>156</v>
       </c>
       <c r="D83" s="89" t="s">
         <v>20</v>
       </c>
       <c r="E83" s="87"/>
-      <c r="F83" s="84"/>
+      <c r="F83" s="83" t="str">
+        <f t="shared" si="6"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G83" s="86" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>MARCOS VICTOR</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" s="87"/>
-      <c r="B84" s="84"/>
-      <c r="C84" s="93" t="s">
+      <c r="B84" s="83" t="str">
+        <f t="shared" si="5"/>
+        <v>WA.ME/55</v>
+      </c>
+      <c r="C84" s="92" t="s">
         <v>156</v>
       </c>
       <c r="D84" s="89" t="s">
         <v>87</v>
       </c>
       <c r="E84" s="87"/>
-      <c r="F84" s="84"/>
+      <c r="F84" s="83" t="str">
+        <f t="shared" si="6"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G84" s="86" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>MARCOS VICTOR</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" s="87"/>
-      <c r="B85" s="84"/>
-      <c r="C85" s="93" t="s">
+      <c r="B85" s="83" t="str">
+        <f t="shared" si="5"/>
+        <v>WA.ME/55</v>
+      </c>
+      <c r="C85" s="92" t="s">
         <v>156</v>
       </c>
       <c r="D85" s="89" t="s">
         <v>22</v>
       </c>
       <c r="E85" s="87"/>
-      <c r="F85" s="84"/>
+      <c r="F85" s="83" t="str">
+        <f t="shared" si="6"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G85" s="86" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>MARCOS VICTOR</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" s="87"/>
-      <c r="B86" s="84"/>
-      <c r="C86" s="93" t="s">
+      <c r="B86" s="83" t="str">
+        <f t="shared" si="5"/>
+        <v>WA.ME/55</v>
+      </c>
+      <c r="C86" s="92" t="s">
         <v>156</v>
       </c>
       <c r="D86" s="89" t="s">
         <v>88</v>
       </c>
       <c r="E86" s="87"/>
-      <c r="F86" s="84"/>
+      <c r="F86" s="83" t="str">
+        <f t="shared" si="6"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G86" s="86" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>MARCOS VICTOR</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" s="87"/>
-      <c r="B87" s="84"/>
-      <c r="C87" s="93" t="s">
+      <c r="B87" s="83" t="str">
+        <f t="shared" si="5"/>
+        <v>WA.ME/55</v>
+      </c>
+      <c r="C87" s="92" t="s">
         <v>156</v>
       </c>
       <c r="D87" s="89" t="s">
         <v>126</v>
       </c>
       <c r="E87" s="87"/>
-      <c r="F87" s="84"/>
+      <c r="F87" s="83" t="str">
+        <f t="shared" si="6"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G87" s="86" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>MARCOS VICTOR</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" s="87"/>
-      <c r="B88" s="84"/>
-      <c r="C88" s="93" t="s">
+      <c r="B88" s="83" t="str">
+        <f t="shared" si="5"/>
+        <v>WA.ME/55</v>
+      </c>
+      <c r="C88" s="92" t="s">
         <v>156</v>
       </c>
       <c r="D88" s="89" t="s">
         <v>184</v>
       </c>
       <c r="E88" s="87"/>
-      <c r="F88" s="84"/>
+      <c r="F88" s="83" t="str">
+        <f t="shared" si="6"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G88" s="86" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>MARCOS VICTOR</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" s="87"/>
-      <c r="B89" s="84"/>
-      <c r="C89" s="93" t="s">
+      <c r="B89" s="83" t="str">
+        <f t="shared" si="5"/>
+        <v>WA.ME/55</v>
+      </c>
+      <c r="C89" s="92" t="s">
         <v>156</v>
       </c>
       <c r="D89" s="89" t="s">
         <v>27</v>
       </c>
       <c r="E89" s="87"/>
-      <c r="F89" s="84"/>
+      <c r="F89" s="83" t="str">
+        <f t="shared" si="6"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G89" s="86" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>MARCOS VICTOR</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" s="87"/>
-      <c r="B90" s="84"/>
-      <c r="C90" s="93" t="s">
+      <c r="B90" s="83" t="str">
+        <f t="shared" si="5"/>
+        <v>WA.ME/55</v>
+      </c>
+      <c r="C90" s="92" t="s">
         <v>156</v>
       </c>
       <c r="D90" s="89" t="s">
         <v>127</v>
       </c>
       <c r="E90" s="87"/>
-      <c r="F90" s="84"/>
+      <c r="F90" s="83" t="str">
+        <f t="shared" si="6"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G90" s="86" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>MARCOS VICTOR</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" s="87"/>
-      <c r="B91" s="84"/>
-      <c r="C91" s="93" t="s">
+      <c r="B91" s="83" t="str">
+        <f t="shared" si="5"/>
+        <v>WA.ME/55</v>
+      </c>
+      <c r="C91" s="92" t="s">
         <v>156</v>
       </c>
       <c r="D91" s="89" t="s">
         <v>89</v>
       </c>
       <c r="E91" s="87"/>
-      <c r="F91" s="84"/>
+      <c r="F91" s="83" t="str">
+        <f t="shared" si="6"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G91" s="86" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>MARCOS VICTOR</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" s="87"/>
-      <c r="B92" s="84"/>
-      <c r="C92" s="93" t="s">
+      <c r="B92" s="83" t="str">
+        <f t="shared" si="5"/>
+        <v>WA.ME/55</v>
+      </c>
+      <c r="C92" s="92" t="s">
         <v>156</v>
       </c>
       <c r="D92" s="89" t="s">
         <v>30</v>
       </c>
       <c r="E92" s="87"/>
-      <c r="F92" s="84"/>
+      <c r="F92" s="83" t="str">
+        <f t="shared" si="6"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G92" s="86" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>MARCOS VICTOR</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" s="87"/>
-      <c r="B93" s="84"/>
-      <c r="C93" s="93" t="s">
+      <c r="B93" s="83" t="str">
+        <f t="shared" si="5"/>
+        <v>WA.ME/55</v>
+      </c>
+      <c r="C93" s="92" t="s">
         <v>156</v>
       </c>
       <c r="D93" s="89" t="s">
         <v>32</v>
       </c>
       <c r="E93" s="87"/>
-      <c r="F93" s="84"/>
+      <c r="F93" s="83" t="str">
+        <f t="shared" si="6"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G93" s="86" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>MARCOS VICTOR</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" s="87"/>
-      <c r="B94" s="84"/>
-      <c r="C94" s="93" t="s">
+      <c r="B94" s="83" t="str">
+        <f t="shared" si="5"/>
+        <v>WA.ME/55</v>
+      </c>
+      <c r="C94" s="92" t="s">
         <v>156</v>
       </c>
       <c r="D94" s="89" t="s">
         <v>33</v>
       </c>
       <c r="E94" s="87"/>
-      <c r="F94" s="84"/>
+      <c r="F94" s="83" t="str">
+        <f t="shared" si="6"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G94" s="86" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>MARCOS VICTOR</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" s="87"/>
-      <c r="B95" s="84"/>
-      <c r="C95" s="93" t="s">
+      <c r="B95" s="83" t="str">
+        <f t="shared" si="5"/>
+        <v>WA.ME/55</v>
+      </c>
+      <c r="C95" s="92" t="s">
         <v>156</v>
       </c>
       <c r="D95" s="89" t="s">
         <v>128</v>
       </c>
       <c r="E95" s="87"/>
-      <c r="F95" s="84"/>
+      <c r="F95" s="83" t="str">
+        <f t="shared" si="6"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G95" s="86" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>MARCOS VICTOR</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" s="87"/>
-      <c r="B96" s="84"/>
-      <c r="C96" s="93" t="s">
+      <c r="B96" s="83" t="str">
+        <f t="shared" si="5"/>
+        <v>WA.ME/55</v>
+      </c>
+      <c r="C96" s="92" t="s">
         <v>156</v>
       </c>
       <c r="D96" s="89" t="s">
         <v>44</v>
       </c>
       <c r="E96" s="87"/>
-      <c r="F96" s="84"/>
+      <c r="F96" s="83" t="str">
+        <f t="shared" si="6"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G96" s="86" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>MARCOS VICTOR</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" s="87"/>
-      <c r="B97" s="84"/>
-      <c r="C97" s="93" t="s">
+      <c r="B97" s="83" t="str">
+        <f t="shared" si="5"/>
+        <v>WA.ME/55</v>
+      </c>
+      <c r="C97" s="92" t="s">
         <v>156</v>
       </c>
       <c r="D97" s="89" t="s">
         <v>104</v>
       </c>
       <c r="E97" s="87"/>
-      <c r="F97" s="84"/>
+      <c r="F97" s="83" t="str">
+        <f t="shared" si="6"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G97" s="86" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>MARCOS VICTOR</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" s="87"/>
-      <c r="B98" s="84"/>
-      <c r="C98" s="93" t="s">
+      <c r="B98" s="83" t="str">
+        <f t="shared" si="5"/>
+        <v>WA.ME/55</v>
+      </c>
+      <c r="C98" s="92" t="s">
         <v>156</v>
       </c>
       <c r="D98" s="89" t="s">
         <v>45</v>
       </c>
       <c r="E98" s="87"/>
-      <c r="F98" s="84"/>
+      <c r="F98" s="83" t="str">
+        <f t="shared" si="6"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G98" s="86" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>MARCOS VICTOR</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" s="87"/>
-      <c r="B99" s="84"/>
-      <c r="C99" s="93" t="s">
+      <c r="B99" s="83" t="str">
+        <f t="shared" si="5"/>
+        <v>WA.ME/55</v>
+      </c>
+      <c r="C99" s="92" t="s">
         <v>156</v>
       </c>
       <c r="D99" s="89" t="s">
         <v>191</v>
       </c>
       <c r="E99" s="87"/>
-      <c r="F99" s="84"/>
+      <c r="F99" s="83" t="str">
+        <f t="shared" si="6"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G99" s="86" t="str">
-        <f t="shared" ref="G99:G130" si="3">C99</f>
+        <f t="shared" ref="G99:G130" si="7">C99</f>
         <v>MARCOS VICTOR</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" s="87"/>
-      <c r="B100" s="84"/>
-      <c r="C100" s="93" t="s">
+      <c r="B100" s="83" t="str">
+        <f t="shared" si="5"/>
+        <v>WA.ME/55</v>
+      </c>
+      <c r="C100" s="92" t="s">
         <v>156</v>
       </c>
       <c r="D100" s="89" t="s">
         <v>131</v>
       </c>
       <c r="E100" s="87"/>
-      <c r="F100" s="84"/>
+      <c r="F100" s="83" t="str">
+        <f t="shared" si="6"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G100" s="86" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>MARCOS VICTOR</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" s="87"/>
-      <c r="B101" s="84"/>
-      <c r="C101" s="93" t="s">
+      <c r="B101" s="83" t="str">
+        <f t="shared" si="5"/>
+        <v>WA.ME/55</v>
+      </c>
+      <c r="C101" s="92" t="s">
         <v>156</v>
       </c>
       <c r="D101" s="89" t="s">
         <v>91</v>
       </c>
       <c r="E101" s="87"/>
-      <c r="F101" s="84"/>
+      <c r="F101" s="83" t="str">
+        <f t="shared" si="6"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G101" s="86" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>MARCOS VICTOR</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" s="87"/>
-      <c r="B102" s="84"/>
-      <c r="C102" s="93" t="s">
+      <c r="B102" s="83" t="str">
+        <f t="shared" si="5"/>
+        <v>WA.ME/55</v>
+      </c>
+      <c r="C102" s="92" t="s">
         <v>156</v>
       </c>
       <c r="D102" s="89" t="s">
         <v>53</v>
       </c>
       <c r="E102" s="87"/>
-      <c r="F102" s="84"/>
+      <c r="F102" s="83" t="str">
+        <f t="shared" si="6"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G102" s="86" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>MARCOS VICTOR</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103" s="87"/>
-      <c r="B103" s="84"/>
-      <c r="C103" s="93" t="s">
+      <c r="B103" s="83" t="str">
+        <f t="shared" si="5"/>
+        <v>WA.ME/55</v>
+      </c>
+      <c r="C103" s="92" t="s">
         <v>156</v>
       </c>
       <c r="D103" s="89" t="s">
         <v>92</v>
       </c>
       <c r="E103" s="87"/>
-      <c r="F103" s="84"/>
+      <c r="F103" s="83" t="str">
+        <f t="shared" si="6"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G103" s="86" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>MARCOS VICTOR</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" s="87"/>
-      <c r="B104" s="84"/>
-      <c r="C104" s="93" t="s">
+      <c r="B104" s="83" t="str">
+        <f t="shared" si="5"/>
+        <v>WA.ME/55</v>
+      </c>
+      <c r="C104" s="92" t="s">
         <v>156</v>
       </c>
       <c r="D104" s="89" t="s">
         <v>58</v>
       </c>
       <c r="E104" s="87"/>
-      <c r="F104" s="84"/>
+      <c r="F104" s="83" t="str">
+        <f t="shared" si="6"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G104" s="86" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>MARCOS VICTOR</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105" s="87"/>
-      <c r="B105" s="84"/>
-      <c r="C105" s="93" t="s">
+      <c r="B105" s="83" t="str">
+        <f t="shared" si="5"/>
+        <v>WA.ME/55</v>
+      </c>
+      <c r="C105" s="92" t="s">
         <v>156</v>
       </c>
       <c r="D105" s="89" t="s">
         <v>59</v>
       </c>
       <c r="E105" s="87"/>
-      <c r="F105" s="84"/>
+      <c r="F105" s="83" t="str">
+        <f t="shared" si="6"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G105" s="86" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>MARCOS VICTOR</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106" s="87"/>
-      <c r="B106" s="84"/>
-      <c r="C106" s="93" t="s">
+      <c r="B106" s="83" t="str">
+        <f t="shared" si="5"/>
+        <v>WA.ME/55</v>
+      </c>
+      <c r="C106" s="92" t="s">
         <v>156</v>
       </c>
       <c r="D106" s="89" t="s">
         <v>62</v>
       </c>
       <c r="E106" s="87"/>
-      <c r="F106" s="84"/>
+      <c r="F106" s="83" t="str">
+        <f t="shared" si="6"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G106" s="86" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>MARCOS VICTOR</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" s="87"/>
-      <c r="B107" s="84"/>
-      <c r="C107" s="93" t="s">
+      <c r="B107" s="83" t="str">
+        <f t="shared" si="5"/>
+        <v>WA.ME/55</v>
+      </c>
+      <c r="C107" s="92" t="s">
         <v>156</v>
       </c>
       <c r="D107" s="89" t="s">
         <v>67</v>
       </c>
       <c r="E107" s="87"/>
-      <c r="F107" s="84"/>
+      <c r="F107" s="83" t="str">
+        <f t="shared" si="6"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G107" s="86" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>MARCOS VICTOR</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108" s="87"/>
-      <c r="B108" s="84"/>
-      <c r="C108" s="93" t="s">
+      <c r="B108" s="83" t="str">
+        <f t="shared" si="5"/>
+        <v>WA.ME/55</v>
+      </c>
+      <c r="C108" s="92" t="s">
         <v>156</v>
       </c>
       <c r="D108" s="89" t="s">
         <v>68</v>
       </c>
       <c r="E108" s="87"/>
-      <c r="F108" s="84"/>
+      <c r="F108" s="83" t="str">
+        <f t="shared" si="6"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G108" s="86" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>MARCOS VICTOR</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109" s="87"/>
-      <c r="B109" s="84"/>
-      <c r="C109" s="93" t="s">
+      <c r="B109" s="83" t="str">
+        <f t="shared" si="5"/>
+        <v>WA.ME/55</v>
+      </c>
+      <c r="C109" s="92" t="s">
         <v>156</v>
       </c>
       <c r="D109" s="89" t="s">
         <v>69</v>
       </c>
       <c r="E109" s="87"/>
-      <c r="F109" s="84"/>
+      <c r="F109" s="83" t="str">
+        <f t="shared" si="6"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G109" s="86" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>MARCOS VICTOR</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110" s="83"/>
-      <c r="B110" s="84"/>
-      <c r="C110" s="93" t="s">
+      <c r="B110" s="83" t="str">
+        <f t="shared" si="5"/>
+        <v>WA.ME/55</v>
+      </c>
+      <c r="C110" s="92" t="s">
         <v>156</v>
       </c>
       <c r="D110" s="89" t="s">
         <v>194</v>
       </c>
       <c r="E110" s="83"/>
-      <c r="F110" s="84"/>
+      <c r="F110" s="83" t="str">
+        <f t="shared" si="6"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G110" s="86" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>MARCOS VICTOR</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111" s="87"/>
-      <c r="B111" s="84"/>
-      <c r="C111" s="93" t="s">
+      <c r="B111" s="83" t="str">
+        <f t="shared" si="5"/>
+        <v>WA.ME/55</v>
+      </c>
+      <c r="C111" s="92" t="s">
         <v>156</v>
       </c>
       <c r="D111" s="89" t="s">
         <v>75</v>
       </c>
       <c r="E111" s="87"/>
-      <c r="F111" s="84"/>
+      <c r="F111" s="83" t="str">
+        <f t="shared" si="6"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G111" s="86" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>MARCOS VICTOR</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112" s="87"/>
-      <c r="B112" s="84"/>
-      <c r="C112" s="93" t="s">
+      <c r="B112" s="83" t="str">
+        <f t="shared" si="5"/>
+        <v>WA.ME/55</v>
+      </c>
+      <c r="C112" s="92" t="s">
         <v>156</v>
       </c>
       <c r="D112" s="89" t="s">
         <v>76</v>
       </c>
       <c r="E112" s="87"/>
-      <c r="F112" s="84"/>
+      <c r="F112" s="83" t="str">
+        <f t="shared" si="6"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G112" s="86" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>MARCOS VICTOR</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" s="87"/>
-      <c r="B113" s="84"/>
+      <c r="B113" s="83" t="str">
+        <f t="shared" si="5"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C113" s="90" t="s">
         <v>195</v>
       </c>
@@ -11338,15 +11984,21 @@
         <v>56</v>
       </c>
       <c r="E113" s="87"/>
-      <c r="F113" s="84"/>
+      <c r="F113" s="83" t="str">
+        <f t="shared" si="6"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G113" s="86" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>PALMARES</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114" s="87"/>
-      <c r="B114" s="84"/>
+      <c r="B114" s="83" t="str">
+        <f t="shared" si="5"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C114" s="90" t="s">
         <v>195</v>
       </c>
@@ -11354,15 +12006,21 @@
         <v>73</v>
       </c>
       <c r="E114" s="83"/>
-      <c r="F114" s="84"/>
+      <c r="F114" s="83" t="str">
+        <f t="shared" si="6"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G114" s="86" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>PALMARES</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115" s="87"/>
-      <c r="B115" s="84"/>
+      <c r="B115" s="83" t="str">
+        <f t="shared" si="5"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C115" s="86" t="s">
         <v>155</v>
       </c>
@@ -11370,15 +12028,21 @@
         <v>121</v>
       </c>
       <c r="E115" s="87"/>
-      <c r="F115" s="84"/>
+      <c r="F115" s="83" t="str">
+        <f t="shared" si="6"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G115" s="86" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>WILLIAM DANTAS</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116" s="87"/>
-      <c r="B116" s="84"/>
+      <c r="B116" s="83" t="str">
+        <f t="shared" si="5"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C116" s="86" t="s">
         <v>155</v>
       </c>
@@ -11386,15 +12050,21 @@
         <v>11</v>
       </c>
       <c r="E116" s="87"/>
-      <c r="F116" s="84"/>
+      <c r="F116" s="83" t="str">
+        <f t="shared" si="6"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G116" s="86" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>WILLIAM DANTAS</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117" s="87"/>
-      <c r="B117" s="84"/>
+      <c r="B117" s="83" t="str">
+        <f t="shared" si="5"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C117" s="86" t="s">
         <v>155</v>
       </c>
@@ -11402,15 +12072,21 @@
         <v>122</v>
       </c>
       <c r="E117" s="87"/>
-      <c r="F117" s="84"/>
+      <c r="F117" s="83" t="str">
+        <f t="shared" si="6"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G117" s="86" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>WILLIAM DANTAS</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118" s="87"/>
-      <c r="B118" s="84"/>
+      <c r="B118" s="83" t="str">
+        <f t="shared" si="5"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C118" s="86" t="s">
         <v>155</v>
       </c>
@@ -11418,15 +12094,21 @@
         <v>123</v>
       </c>
       <c r="E118" s="87"/>
-      <c r="F118" s="84"/>
+      <c r="F118" s="83" t="str">
+        <f t="shared" si="6"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G118" s="86" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>WILLIAM DANTAS</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119" s="87"/>
-      <c r="B119" s="84"/>
+      <c r="B119" s="83" t="str">
+        <f t="shared" si="5"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C119" s="86" t="s">
         <v>155</v>
       </c>
@@ -11434,15 +12116,21 @@
         <v>21</v>
       </c>
       <c r="E119" s="87"/>
-      <c r="F119" s="84"/>
+      <c r="F119" s="83" t="str">
+        <f t="shared" si="6"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G119" s="86" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>WILLIAM DANTAS</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A120" s="87"/>
-      <c r="B120" s="84"/>
+      <c r="B120" s="83" t="str">
+        <f t="shared" si="5"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C120" s="86" t="s">
         <v>155</v>
       </c>
@@ -11450,15 +12138,21 @@
         <v>23</v>
       </c>
       <c r="E120" s="87"/>
-      <c r="F120" s="84"/>
+      <c r="F120" s="83" t="str">
+        <f t="shared" si="6"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G120" s="86" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>WILLIAM DANTAS</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121" s="87"/>
-      <c r="B121" s="84"/>
+      <c r="B121" s="83" t="str">
+        <f t="shared" si="5"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C121" s="86" t="s">
         <v>155</v>
       </c>
@@ -11466,15 +12160,21 @@
         <v>100</v>
       </c>
       <c r="E121" s="87"/>
-      <c r="F121" s="84"/>
+      <c r="F121" s="83" t="str">
+        <f t="shared" si="6"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G121" s="86" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>WILLIAM DANTAS</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A122" s="87"/>
-      <c r="B122" s="84"/>
+      <c r="B122" s="83" t="str">
+        <f t="shared" si="5"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C122" s="86" t="s">
         <v>155</v>
       </c>
@@ -11482,15 +12182,21 @@
         <v>125</v>
       </c>
       <c r="E122" s="87"/>
-      <c r="F122" s="84"/>
+      <c r="F122" s="83" t="str">
+        <f t="shared" si="6"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G122" s="86" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>WILLIAM DANTAS</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A123" s="87"/>
-      <c r="B123" s="84"/>
+      <c r="B123" s="83" t="str">
+        <f t="shared" si="5"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C123" s="86" t="s">
         <v>155</v>
       </c>
@@ -11498,15 +12204,21 @@
         <v>186</v>
       </c>
       <c r="E123" s="87"/>
-      <c r="F123" s="84"/>
+      <c r="F123" s="83" t="str">
+        <f t="shared" si="6"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G123" s="86" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>WILLIAM DANTAS</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A124" s="87"/>
-      <c r="B124" s="84"/>
+      <c r="B124" s="83" t="str">
+        <f t="shared" si="5"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C124" s="86" t="s">
         <v>155</v>
       </c>
@@ -11514,15 +12226,21 @@
         <v>25</v>
       </c>
       <c r="E124" s="87"/>
-      <c r="F124" s="84"/>
+      <c r="F124" s="83" t="str">
+        <f t="shared" si="6"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G124" s="86" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>WILLIAM DANTAS</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A125" s="87"/>
-      <c r="B125" s="84"/>
+      <c r="B125" s="83" t="str">
+        <f t="shared" si="5"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C125" s="86" t="s">
         <v>155</v>
       </c>
@@ -11530,15 +12248,21 @@
         <v>34</v>
       </c>
       <c r="E125" s="87"/>
-      <c r="F125" s="84"/>
+      <c r="F125" s="83" t="str">
+        <f t="shared" si="6"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G125" s="86" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>WILLIAM DANTAS</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126" s="87"/>
-      <c r="B126" s="84"/>
+      <c r="B126" s="83" t="str">
+        <f t="shared" si="5"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C126" s="86" t="s">
         <v>155</v>
       </c>
@@ -11546,15 +12270,21 @@
         <v>39</v>
       </c>
       <c r="E126" s="87"/>
-      <c r="F126" s="84"/>
+      <c r="F126" s="83" t="str">
+        <f t="shared" si="6"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G126" s="86" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>WILLIAM DANTAS</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127" s="87"/>
-      <c r="B127" s="84"/>
+      <c r="B127" s="83" t="str">
+        <f t="shared" si="5"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C127" s="86" t="s">
         <v>155</v>
       </c>
@@ -11562,15 +12292,21 @@
         <v>48</v>
       </c>
       <c r="E127" s="87"/>
-      <c r="F127" s="84"/>
+      <c r="F127" s="83" t="str">
+        <f t="shared" si="6"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G127" s="86" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>WILLIAM DANTAS</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A128" s="87"/>
-      <c r="B128" s="84"/>
+      <c r="B128" s="83" t="str">
+        <f t="shared" si="5"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C128" s="86" t="s">
         <v>155</v>
       </c>
@@ -11578,15 +12314,21 @@
         <v>52</v>
       </c>
       <c r="E128" s="87"/>
-      <c r="F128" s="84"/>
+      <c r="F128" s="83" t="str">
+        <f t="shared" si="6"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G128" s="86" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>WILLIAM DANTAS</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A129" s="87"/>
-      <c r="B129" s="84"/>
+      <c r="B129" s="83" t="str">
+        <f t="shared" si="5"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C129" s="86" t="s">
         <v>155</v>
       </c>
@@ -11594,15 +12336,21 @@
         <v>132</v>
       </c>
       <c r="E129" s="87"/>
-      <c r="F129" s="84"/>
+      <c r="F129" s="83" t="str">
+        <f t="shared" si="6"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G129" s="86" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>WILLIAM DANTAS</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A130" s="87"/>
-      <c r="B130" s="84"/>
+      <c r="B130" s="83" t="str">
+        <f t="shared" si="5"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C130" s="86" t="s">
         <v>155</v>
       </c>
@@ -11610,15 +12358,21 @@
         <v>54</v>
       </c>
       <c r="E130" s="87"/>
-      <c r="F130" s="84"/>
+      <c r="F130" s="83" t="str">
+        <f t="shared" si="6"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G130" s="86" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>WILLIAM DANTAS</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A131" s="87"/>
-      <c r="B131" s="84"/>
+      <c r="B131" s="83" t="str">
+        <f t="shared" si="5"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C131" s="86" t="s">
         <v>155</v>
       </c>
@@ -11626,15 +12380,21 @@
         <v>133</v>
       </c>
       <c r="E131" s="87"/>
-      <c r="F131" s="84"/>
+      <c r="F131" s="83" t="str">
+        <f t="shared" si="6"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G131" s="86" t="str">
-        <f t="shared" ref="G131:G137" si="4">C131</f>
+        <f t="shared" ref="G131:G137" si="8">C131</f>
         <v>WILLIAM DANTAS</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A132" s="87"/>
-      <c r="B132" s="84"/>
+      <c r="B132" s="83" t="str">
+        <f t="shared" si="5"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C132" s="86" t="s">
         <v>155</v>
       </c>
@@ -11642,15 +12402,21 @@
         <v>61</v>
       </c>
       <c r="E132" s="87"/>
-      <c r="F132" s="84"/>
+      <c r="F132" s="83" t="str">
+        <f t="shared" si="6"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G132" s="86" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>WILLIAM DANTAS</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A133" s="83"/>
-      <c r="B133" s="84"/>
+      <c r="B133" s="83" t="str">
+        <f t="shared" ref="B133:B137" si="9">CONCATENATE($A$1,A133)</f>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C133" s="86" t="s">
         <v>155</v>
       </c>
@@ -11658,15 +12424,21 @@
         <v>103</v>
       </c>
       <c r="E133" s="83"/>
-      <c r="F133" s="84"/>
+      <c r="F133" s="83" t="str">
+        <f t="shared" ref="F133:F137" si="10">CONCATENATE($E$1,E133)</f>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G133" s="86" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>WILLIAM DANTAS</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A134" s="87"/>
-      <c r="B134" s="84"/>
+      <c r="B134" s="83" t="str">
+        <f t="shared" si="9"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C134" s="86" t="s">
         <v>155</v>
       </c>
@@ -11674,15 +12446,21 @@
         <v>77</v>
       </c>
       <c r="E134" s="87"/>
-      <c r="F134" s="84"/>
+      <c r="F134" s="83" t="str">
+        <f t="shared" si="10"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G134" s="86" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>WILLIAM DANTAS</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A135" s="83"/>
-      <c r="B135" s="84"/>
+      <c r="B135" s="83" t="str">
+        <f t="shared" si="9"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C135" s="86" t="s">
         <v>155</v>
       </c>
@@ -11690,15 +12468,21 @@
         <v>135</v>
       </c>
       <c r="E135" s="83"/>
-      <c r="F135" s="84"/>
+      <c r="F135" s="83" t="str">
+        <f t="shared" si="10"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G135" s="86" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>WILLIAM DANTAS</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A136" s="83"/>
-      <c r="B136" s="84"/>
+      <c r="B136" s="83" t="str">
+        <f t="shared" si="9"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C136" s="86" t="s">
         <v>155</v>
       </c>
@@ -11706,15 +12490,21 @@
         <v>94</v>
       </c>
       <c r="E136" s="87"/>
-      <c r="F136" s="84"/>
+      <c r="F136" s="83" t="str">
+        <f t="shared" si="10"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G136" s="86" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>WILLIAM DANTAS</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A137" s="87"/>
-      <c r="B137" s="84"/>
+      <c r="B137" s="83" t="str">
+        <f t="shared" si="9"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="C137" s="86" t="s">
         <v>155</v>
       </c>
@@ -11722,9 +12512,12 @@
         <v>136</v>
       </c>
       <c r="E137" s="87"/>
-      <c r="F137" s="84"/>
+      <c r="F137" s="83" t="str">
+        <f t="shared" si="10"/>
+        <v>WA.ME/55</v>
+      </c>
       <c r="G137" s="86" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>WILLIAM DANTAS</v>
       </c>
     </row>

--- a/PREMIO.xlsx
+++ b/PREMIO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alan Souto\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA667B8D-27AF-499F-91BD-1F4A1ED3A9C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FBD5FA2-C878-4FC8-84FD-FEBA72DE4CE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EBBE1F25-C943-4A3A-8B11-92CFB5DB310C}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1198" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1194" uniqueCount="318">
   <si>
     <t>COLABORADOR :</t>
   </si>
@@ -898,9 +898,6 @@
   </si>
   <si>
     <t>070.058.973-23</t>
-  </si>
-  <si>
-    <t>042.868.413-08</t>
   </si>
   <si>
     <t>001.058.623-71</t>
@@ -3643,10 +3640,10 @@
         <v>0</v>
       </c>
       <c r="B28" s="68" t="s">
+        <v>315</v>
+      </c>
+      <c r="C28" s="80" t="s">
         <v>316</v>
-      </c>
-      <c r="C28" s="80" t="s">
-        <v>317</v>
       </c>
       <c r="D28" s="69">
         <v>0</v>
@@ -4455,10 +4452,10 @@
         <v>0</v>
       </c>
       <c r="B44" s="68" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C44" s="80" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D44" s="69">
         <v>0</v>
@@ -6390,7 +6387,7 @@
         <v>0</v>
       </c>
       <c r="I83" s="60">
-        <v>0</v>
+        <v>190.73</v>
       </c>
       <c r="J83" s="58">
         <v>0</v>
@@ -6442,7 +6439,7 @@
         <v>0</v>
       </c>
       <c r="I84" s="60">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="J84" s="59">
         <v>0</v>
@@ -6494,7 +6491,7 @@
         <v>0</v>
       </c>
       <c r="I85" s="60">
-        <v>0</v>
+        <v>200.9</v>
       </c>
       <c r="J85" s="59">
         <v>0</v>
@@ -6546,7 +6543,7 @@
         <v>0</v>
       </c>
       <c r="I86" s="60">
-        <v>0</v>
+        <v>402</v>
       </c>
       <c r="J86" s="59">
         <v>0</v>
@@ -6598,7 +6595,7 @@
         <v>0</v>
       </c>
       <c r="I87" s="60">
-        <v>0</v>
+        <v>308.7</v>
       </c>
       <c r="J87" s="59">
         <v>0</v>
@@ -6650,7 +6647,7 @@
         <v>0</v>
       </c>
       <c r="I88" s="60">
-        <v>0</v>
+        <v>367.2</v>
       </c>
       <c r="J88" s="59">
         <v>0</v>
@@ -6702,7 +6699,7 @@
         <v>0</v>
       </c>
       <c r="I89" s="60">
-        <v>0</v>
+        <v>202.8</v>
       </c>
       <c r="J89" s="59">
         <v>0</v>
@@ -6753,9 +6750,7 @@
       <c r="H90" s="66">
         <v>0</v>
       </c>
-      <c r="I90" s="60">
-        <v>0</v>
-      </c>
+      <c r="I90" s="60"/>
       <c r="J90" s="59">
         <v>0</v>
       </c>
@@ -6804,7 +6799,7 @@
         <v>0</v>
       </c>
       <c r="I91" s="60">
-        <v>0</v>
+        <v>390</v>
       </c>
       <c r="J91" s="59">
         <v>0</v>
@@ -6856,7 +6851,7 @@
         <v>0</v>
       </c>
       <c r="I92" s="60">
-        <v>0</v>
+        <v>83.33</v>
       </c>
       <c r="J92" s="59">
         <v>0</v>
@@ -6908,7 +6903,7 @@
         <v>0</v>
       </c>
       <c r="I93" s="60">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="J93" s="59">
         <v>0</v>
@@ -6960,7 +6955,7 @@
         <v>0</v>
       </c>
       <c r="I94" s="60">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="J94" s="59">
         <v>0</v>
@@ -7012,7 +7007,7 @@
         <v>0</v>
       </c>
       <c r="I95" s="60">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="J95" s="59">
         <v>0</v>
@@ -7064,7 +7059,7 @@
         <v>0</v>
       </c>
       <c r="I96" s="60">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="J96" s="59">
         <v>0</v>
@@ -7116,7 +7111,7 @@
         <v>0</v>
       </c>
       <c r="I97" s="60">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="J97" s="59">
         <v>0</v>
@@ -7168,7 +7163,7 @@
         <v>0</v>
       </c>
       <c r="I98" s="60">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="J98" s="59">
         <v>0</v>
@@ -7220,7 +7215,7 @@
         <v>0</v>
       </c>
       <c r="I99" s="60">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="J99" s="59">
         <v>0</v>
@@ -7272,7 +7267,7 @@
         <v>0</v>
       </c>
       <c r="I100" s="60">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="J100" s="59">
         <v>0</v>
@@ -7324,7 +7319,7 @@
         <v>0</v>
       </c>
       <c r="I101" s="60">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="J101" s="59">
         <v>0</v>
@@ -7376,7 +7371,7 @@
         <v>0</v>
       </c>
       <c r="I102" s="60">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="J102" s="59">
         <v>0</v>
@@ -7428,7 +7423,7 @@
         <v>0</v>
       </c>
       <c r="I103" s="60">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="J103" s="59">
         <v>0</v>
@@ -7459,7 +7454,7 @@
     <row r="104" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A104" s="94"/>
       <c r="B104" s="62" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C104" s="62" t="s">
         <v>143</v>
@@ -7480,7 +7475,7 @@
         <v>0</v>
       </c>
       <c r="I104" s="60">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="J104" s="59">
         <v>0</v>
@@ -12400,7 +12395,7 @@
       </c>
       <c r="H98" t="str">
         <f>IFERROR(VLOOKUP(D98,CPF!A:D,4,0),"NAO ENCONTRADO")</f>
-        <v>042.868.413-08</v>
+        <v>NAO ENCONTRADO</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.3">
@@ -46819,18 +46814,10 @@
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A68" s="57" t="s">
-        <v>184</v>
-      </c>
-      <c r="B68" s="57" t="s">
-        <v>197</v>
-      </c>
-      <c r="C68" s="57" t="s">
-        <v>253</v>
-      </c>
-      <c r="D68" s="57" t="s">
-        <v>284</v>
-      </c>
+      <c r="A68" s="57"/>
+      <c r="B68" s="57"/>
+      <c r="C68" s="57"/>
+      <c r="D68" s="57"/>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" s="57" t="s">
@@ -46843,7 +46830,7 @@
         <v>253</v>
       </c>
       <c r="D69" s="57" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
@@ -46857,7 +46844,7 @@
         <v>253</v>
       </c>
       <c r="D70" s="57" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
@@ -46871,7 +46858,7 @@
         <v>253</v>
       </c>
       <c r="D71" s="57" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
@@ -46879,13 +46866,13 @@
         <v>54</v>
       </c>
       <c r="B72" s="57" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C72" s="57" t="s">
         <v>253</v>
       </c>
       <c r="D72" s="57" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
@@ -46899,7 +46886,7 @@
         <v>253</v>
       </c>
       <c r="D73" s="57" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
@@ -46913,7 +46900,7 @@
         <v>253</v>
       </c>
       <c r="D74" s="57" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
@@ -46927,7 +46914,7 @@
         <v>253</v>
       </c>
       <c r="D75" s="57" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
@@ -46941,7 +46928,7 @@
         <v>253</v>
       </c>
       <c r="D76" s="57" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
@@ -46955,7 +46942,7 @@
         <v>253</v>
       </c>
       <c r="D77" s="57" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
@@ -46969,7 +46956,7 @@
         <v>253</v>
       </c>
       <c r="D78" s="57" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
@@ -46983,7 +46970,7 @@
         <v>253</v>
       </c>
       <c r="D79" s="57" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
@@ -46997,12 +46984,12 @@
         <v>253</v>
       </c>
       <c r="D80" s="57" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" s="57" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B81" s="57" t="s">
         <v>197</v>
@@ -47011,7 +46998,7 @@
         <v>253</v>
       </c>
       <c r="D81" s="57" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
@@ -47025,7 +47012,7 @@
         <v>253</v>
       </c>
       <c r="D82" s="57" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
@@ -47039,7 +47026,7 @@
         <v>253</v>
       </c>
       <c r="D83" s="57" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
@@ -47047,41 +47034,41 @@
         <v>116</v>
       </c>
       <c r="B84" s="57" t="s">
+        <v>301</v>
+      </c>
+      <c r="C84" s="57" t="s">
         <v>302</v>
       </c>
-      <c r="C84" s="57" t="s">
+      <c r="D84" s="57" t="s">
         <v>303</v>
-      </c>
-      <c r="D84" s="57" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" s="57" t="s">
+        <v>304</v>
+      </c>
+      <c r="B85" s="57" t="s">
         <v>305</v>
       </c>
-      <c r="B85" s="57" t="s">
+      <c r="C85" s="57" t="s">
+        <v>302</v>
+      </c>
+      <c r="D85" s="57" t="s">
         <v>306</v>
-      </c>
-      <c r="C85" s="57" t="s">
-        <v>303</v>
-      </c>
-      <c r="D85" s="57" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" s="57" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B86" s="57" t="s">
         <v>197</v>
       </c>
       <c r="C86" s="57" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D86" s="57" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
@@ -47092,10 +47079,10 @@
         <v>197</v>
       </c>
       <c r="C87" s="57" t="s">
+        <v>309</v>
+      </c>
+      <c r="D87" s="57" t="s">
         <v>310</v>
-      </c>
-      <c r="D87" s="57" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
@@ -47106,10 +47093,10 @@
         <v>197</v>
       </c>
       <c r="C88" s="57" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D88" s="57" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
@@ -47120,10 +47107,10 @@
         <v>197</v>
       </c>
       <c r="C89" s="57" t="s">
+        <v>312</v>
+      </c>
+      <c r="D89" s="57" t="s">
         <v>313</v>
-      </c>
-      <c r="D89" s="57" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.3">
@@ -47134,10 +47121,10 @@
         <v>197</v>
       </c>
       <c r="C90" s="57" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D90" s="57" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
   </sheetData>

--- a/PREMIO.xlsx
+++ b/PREMIO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alan Souto\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{688AA62F-04EC-4DDB-B4F3-F204EC4F8A7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8902E1BF-177A-414E-B6E1-1109C368B377}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{EBBE1F25-C943-4A3A-8B11-92CFB5DB310C}"/>
   </bookViews>
@@ -9896,9 +9896,9 @@
         <f t="shared" si="0"/>
         <v>ALAN SOUTO</v>
       </c>
-      <c r="H4" t="str">
+      <c r="H4">
         <f>IFERROR(VLOOKUP(D4,CPF!A:D,4,0),"NAO ENCONTRADO")</f>
-        <v>646.525.643-68</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
@@ -45841,9 +45841,7 @@
       <c r="C3" s="56" t="s">
         <v>194</v>
       </c>
-      <c r="D3" s="56" t="s">
-        <v>195</v>
-      </c>
+      <c r="D3" s="56"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="56" t="s">
@@ -47043,8 +47041,8 @@
       <c r="A91" s="91" t="s">
         <v>95</v>
       </c>
-      <c r="D91">
-        <v>11122233344</v>
+      <c r="D91" s="56" t="s">
+        <v>195</v>
       </c>
     </row>
   </sheetData>

--- a/PREMIO.xlsx
+++ b/PREMIO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alan Souto\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8902E1BF-177A-414E-B6E1-1109C368B377}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4065F84C-58D8-4FDA-BF12-78AE1B9B3276}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{EBBE1F25-C943-4A3A-8B11-92CFB5DB310C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EBBE1F25-C943-4A3A-8B11-92CFB5DB310C}"/>
   </bookViews>
   <sheets>
     <sheet name="RELATORIO CONTROLADORIA" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1181" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1180" uniqueCount="321">
   <si>
     <t>COLABORADOR :</t>
   </si>
@@ -2511,10 +2511,10 @@
       </c>
       <c r="C2" s="68"/>
       <c r="D2" s="69">
-        <v>62</v>
+        <v>56.5</v>
       </c>
       <c r="E2" s="69">
-        <v>249.8</v>
+        <v>258.89999999999998</v>
       </c>
       <c r="F2" s="69">
         <v>231</v>
@@ -2529,10 +2529,10 @@
         <v>4940</v>
       </c>
       <c r="J2" s="69">
-        <v>6245</v>
+        <v>6472</v>
       </c>
       <c r="K2" s="69">
-        <v>6183</v>
+        <v>6415.5</v>
       </c>
       <c r="L2" s="69">
         <v>0</v>
@@ -2544,19 +2544,19 @@
         <v>1459</v>
       </c>
       <c r="O2" s="69">
-        <v>1649</v>
+        <v>1648.5</v>
       </c>
       <c r="P2" s="69">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="Q2" s="69">
-        <v>19474.099999999999</v>
+        <v>21026.3</v>
       </c>
       <c r="R2" s="68"/>
     </row>
     <row r="3" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="70">
-        <v>6.0600000000000001E-2</v>
+        <v>5.7700000000000001E-2</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>116</v>
@@ -2565,10 +2565,10 @@
         <v>3</v>
       </c>
       <c r="D3" s="72">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="E3" s="72">
-        <v>3.96</v>
+        <v>4.16</v>
       </c>
       <c r="F3" s="73">
         <v>6</v>
@@ -2581,10 +2581,10 @@
         <v>57</v>
       </c>
       <c r="J3" s="72">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="K3" s="72">
-        <v>97</v>
+        <v>102.2</v>
       </c>
       <c r="L3" s="74"/>
       <c r="M3" s="74"/>
@@ -2595,10 +2595,10 @@
         <v>21</v>
       </c>
       <c r="P3" s="73">
-        <v>4.62</v>
+        <v>4.8600000000000003</v>
       </c>
       <c r="Q3" s="76">
-        <v>351.84</v>
+        <v>372.64</v>
       </c>
       <c r="R3" s="77" t="s">
         <v>10</v>
@@ -2606,7 +2606,7 @@
     </row>
     <row r="4" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="78">
-        <v>4.1700000000000001E-2</v>
+        <v>4.0399999999999998E-2</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>175</v>
@@ -2615,10 +2615,10 @@
         <v>135</v>
       </c>
       <c r="D4" s="72">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="E4" s="72">
-        <v>3.84</v>
+        <v>3.96</v>
       </c>
       <c r="F4" s="73">
         <v>4</v>
@@ -2631,10 +2631,10 @@
         <v>76</v>
       </c>
       <c r="J4" s="72">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="K4" s="72">
-        <v>95.8</v>
+        <v>99</v>
       </c>
       <c r="L4" s="74"/>
       <c r="M4" s="74"/>
@@ -2645,7 +2645,7 @@
         <v>23</v>
       </c>
       <c r="P4" s="73">
-        <v>4.17</v>
+        <v>4.3</v>
       </c>
       <c r="Q4" s="76">
         <v>0</v>
@@ -2656,7 +2656,7 @@
     </row>
     <row r="5" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="78">
-        <v>4.8800000000000003E-2</v>
+        <v>4.5999999999999999E-2</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>99</v>
@@ -2665,10 +2665,10 @@
         <v>135</v>
       </c>
       <c r="D5" s="72">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="E5" s="72">
-        <v>3.28</v>
+        <v>3.48</v>
       </c>
       <c r="F5" s="73">
         <v>4</v>
@@ -2683,10 +2683,10 @@
         <v>76</v>
       </c>
       <c r="J5" s="72">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="K5" s="72">
-        <v>81.3</v>
+        <v>86.5</v>
       </c>
       <c r="L5" s="74"/>
       <c r="M5" s="74"/>
@@ -2697,7 +2697,7 @@
         <v>22</v>
       </c>
       <c r="P5" s="73">
-        <v>3.69</v>
+        <v>3.93</v>
       </c>
       <c r="Q5" s="76">
         <v>0</v>
@@ -2752,7 +2752,7 @@
     </row>
     <row r="7" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="84">
-        <v>7.5300000000000006E-2</v>
+        <v>7.22E-2</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>117</v>
@@ -2761,10 +2761,10 @@
         <v>3</v>
       </c>
       <c r="D7" s="72">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="E7" s="72">
-        <v>3.72</v>
+        <v>3.88</v>
       </c>
       <c r="F7" s="73">
         <v>7</v>
@@ -2779,10 +2779,10 @@
         <v>67</v>
       </c>
       <c r="J7" s="72">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="K7" s="72">
-        <v>89.7</v>
+        <v>93.9</v>
       </c>
       <c r="L7" s="74"/>
       <c r="M7" s="74"/>
@@ -2793,18 +2793,18 @@
         <v>20</v>
       </c>
       <c r="P7" s="73">
-        <v>4.49</v>
+        <v>4.6900000000000004</v>
       </c>
       <c r="Q7" s="76">
-        <v>338.88</v>
+        <v>355.52</v>
       </c>
       <c r="R7" s="77" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="70">
-        <v>5.0599999999999999E-2</v>
+      <c r="A8" s="78">
+        <v>4.7600000000000003E-2</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>118</v>
@@ -2813,10 +2813,10 @@
         <v>135</v>
       </c>
       <c r="D8" s="72">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="E8" s="72">
-        <v>3.16</v>
+        <v>3.36</v>
       </c>
       <c r="F8" s="73">
         <v>4</v>
@@ -2829,10 +2829,10 @@
         <v>66</v>
       </c>
       <c r="J8" s="72">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="K8" s="72">
-        <v>78.2</v>
+        <v>83.4</v>
       </c>
       <c r="L8" s="74"/>
       <c r="M8" s="74"/>
@@ -2843,7 +2843,7 @@
         <v>21</v>
       </c>
       <c r="P8" s="73">
-        <v>3.72</v>
+        <v>3.97</v>
       </c>
       <c r="Q8" s="76">
         <v>0</v>
@@ -2898,7 +2898,7 @@
     </row>
     <row r="10" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="78">
-        <v>4.0800000000000003E-2</v>
+        <v>3.8800000000000001E-2</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>15</v>
@@ -2907,10 +2907,10 @@
         <v>137</v>
       </c>
       <c r="D10" s="72">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E10" s="72">
-        <v>3.92</v>
+        <v>4.12</v>
       </c>
       <c r="F10" s="73">
         <v>4</v>
@@ -2925,10 +2925,10 @@
         <v>66</v>
       </c>
       <c r="J10" s="72">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="K10" s="72">
-        <v>97.9</v>
+        <v>103</v>
       </c>
       <c r="L10" s="74"/>
       <c r="M10" s="74"/>
@@ -2939,10 +2939,10 @@
         <v>23</v>
       </c>
       <c r="P10" s="73">
-        <v>4.26</v>
+        <v>4.4800000000000004</v>
       </c>
       <c r="Q10" s="76">
-        <v>669.68</v>
+        <v>690</v>
       </c>
       <c r="R10" s="77" t="s">
         <v>10</v>
@@ -2950,7 +2950,7 @@
     </row>
     <row r="11" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="70">
-        <v>5.9499999999999997E-2</v>
+        <v>5.8099999999999999E-2</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>16</v>
@@ -2962,7 +2962,7 @@
         <v>1.6</v>
       </c>
       <c r="E11" s="72">
-        <v>3.36</v>
+        <v>3.44</v>
       </c>
       <c r="F11" s="73">
         <v>5</v>
@@ -2975,10 +2975,10 @@
         <v>64</v>
       </c>
       <c r="J11" s="72">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="K11" s="72">
-        <v>82.4</v>
+        <v>84.4</v>
       </c>
       <c r="L11" s="74"/>
       <c r="M11" s="74"/>
@@ -2989,7 +2989,7 @@
         <v>23</v>
       </c>
       <c r="P11" s="73">
-        <v>3.58</v>
+        <v>3.67</v>
       </c>
       <c r="Q11" s="76">
         <v>0</v>
@@ -3144,7 +3144,7 @@
     </row>
     <row r="15" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="84">
-        <v>8.14E-2</v>
+        <v>7.7799999999999994E-2</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>20</v>
@@ -3153,10 +3153,10 @@
         <v>137</v>
       </c>
       <c r="D15" s="72">
+        <v>3.4</v>
+      </c>
+      <c r="E15" s="72">
         <v>3.6</v>
-      </c>
-      <c r="E15" s="72">
-        <v>3.44</v>
       </c>
       <c r="F15" s="73">
         <v>7</v>
@@ -3169,10 +3169,10 @@
         <v>60</v>
       </c>
       <c r="J15" s="72">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="K15" s="72">
-        <v>82.4</v>
+        <v>86.6</v>
       </c>
       <c r="L15" s="74"/>
       <c r="M15" s="74"/>
@@ -3183,10 +3183,10 @@
         <v>21</v>
       </c>
       <c r="P15" s="73">
-        <v>3.93</v>
+        <v>4.12</v>
       </c>
       <c r="Q15" s="76">
-        <v>635.76</v>
+        <v>652.4</v>
       </c>
       <c r="R15" s="77" t="s">
         <v>10</v>
@@ -3194,7 +3194,7 @@
     </row>
     <row r="16" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="70">
-        <v>5.5599999999999997E-2</v>
+        <v>0.05</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>21</v>
@@ -3203,10 +3203,10 @@
         <v>135</v>
       </c>
       <c r="D16" s="72">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="E16" s="72">
-        <v>2.16</v>
+        <v>2.4</v>
       </c>
       <c r="F16" s="73">
         <v>3</v>
@@ -3219,10 +3219,10 @@
         <v>39</v>
       </c>
       <c r="J16" s="72">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="K16" s="72">
-        <v>53.2</v>
+        <v>59.4</v>
       </c>
       <c r="L16" s="74"/>
       <c r="M16" s="74"/>
@@ -3233,7 +3233,7 @@
         <v>20</v>
       </c>
       <c r="P16" s="73">
-        <v>2.66</v>
+        <v>2.97</v>
       </c>
       <c r="Q16" s="76">
         <v>0</v>
@@ -3294,7 +3294,7 @@
     </row>
     <row r="18" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="84">
-        <v>0.10199999999999999</v>
+        <v>9.5200000000000007E-2</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>22</v>
@@ -3303,10 +3303,10 @@
         <v>137</v>
       </c>
       <c r="D18" s="72">
-        <v>6.1</v>
+        <v>5.8</v>
       </c>
       <c r="E18" s="72">
-        <v>3.92</v>
+        <v>4.2</v>
       </c>
       <c r="F18" s="73">
         <v>10</v>
@@ -3319,10 +3319,10 @@
         <v>78</v>
       </c>
       <c r="J18" s="72">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="K18" s="72">
-        <v>91.9</v>
+        <v>99.2</v>
       </c>
       <c r="L18" s="74"/>
       <c r="M18" s="74"/>
@@ -3333,10 +3333,10 @@
         <v>19</v>
       </c>
       <c r="P18" s="73">
-        <v>4.84</v>
+        <v>5.22</v>
       </c>
       <c r="Q18" s="76">
-        <v>938.52</v>
+        <v>982.2</v>
       </c>
       <c r="R18" s="77" t="s">
         <v>10</v>
@@ -3344,7 +3344,7 @@
     </row>
     <row r="19" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="70">
-        <v>6.4500000000000002E-2</v>
+        <v>6.0600000000000001E-2</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>23</v>
@@ -3353,10 +3353,10 @@
         <v>3</v>
       </c>
       <c r="D19" s="72">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="E19" s="72">
-        <v>2.48</v>
+        <v>2.64</v>
       </c>
       <c r="F19" s="73">
         <v>4</v>
@@ -3369,10 +3369,10 @@
         <v>60</v>
       </c>
       <c r="J19" s="72">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="K19" s="72">
-        <v>60.5</v>
+        <v>64.599999999999994</v>
       </c>
       <c r="L19" s="74"/>
       <c r="M19" s="74"/>
@@ -3383,10 +3383,10 @@
         <v>15</v>
       </c>
       <c r="P19" s="73">
-        <v>4.03</v>
+        <v>4.3099999999999996</v>
       </c>
       <c r="Q19" s="76">
-        <v>301.92</v>
+        <v>318.56</v>
       </c>
       <c r="R19" s="77" t="s">
         <v>10</v>
@@ -3394,7 +3394,7 @@
     </row>
     <row r="20" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="85">
-        <v>1.89E-2</v>
+        <v>1.7899999999999999E-2</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>87</v>
@@ -3406,7 +3406,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="72">
-        <v>2.12</v>
+        <v>2.2400000000000002</v>
       </c>
       <c r="F20" s="73">
         <v>1</v>
@@ -3421,10 +3421,10 @@
         <v>43</v>
       </c>
       <c r="J20" s="72">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K20" s="72">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="L20" s="74"/>
       <c r="M20" s="74"/>
@@ -3433,7 +3433,7 @@
         <v>23</v>
       </c>
       <c r="P20" s="73">
-        <v>2.2999999999999998</v>
+        <v>2.4300000000000002</v>
       </c>
       <c r="Q20" s="76">
         <v>0</v>
@@ -3444,7 +3444,7 @@
     </row>
     <row r="21" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="78">
-        <v>3.2599999999999997E-2</v>
+        <v>3.0599999999999999E-2</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>120</v>
@@ -3456,7 +3456,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="72">
-        <v>3.68</v>
+        <v>3.92</v>
       </c>
       <c r="F21" s="73">
         <v>3</v>
@@ -3469,10 +3469,10 @@
         <v>77</v>
       </c>
       <c r="J21" s="72">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="K21" s="72">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="L21" s="74"/>
       <c r="M21" s="74"/>
@@ -3483,10 +3483,10 @@
         <v>20</v>
       </c>
       <c r="P21" s="73">
-        <v>4.5999999999999996</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="Q21" s="76">
-        <v>348</v>
+        <v>372</v>
       </c>
       <c r="R21" s="77" t="s">
         <v>10</v>
@@ -3494,7 +3494,7 @@
     </row>
     <row r="22" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="70">
-        <v>6.3500000000000001E-2</v>
+        <v>5.8000000000000003E-2</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>121</v>
@@ -3503,10 +3503,10 @@
         <v>135</v>
       </c>
       <c r="D22" s="72">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="E22" s="72">
-        <v>2.52</v>
+        <v>2.76</v>
       </c>
       <c r="F22" s="73">
         <v>4</v>
@@ -3521,10 +3521,10 @@
         <v>50</v>
       </c>
       <c r="J22" s="72">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="K22" s="72">
-        <v>61.5</v>
+        <v>67.8</v>
       </c>
       <c r="L22" s="74"/>
       <c r="M22" s="74"/>
@@ -3533,7 +3533,7 @@
         <v>23</v>
       </c>
       <c r="P22" s="73">
-        <v>2.67</v>
+        <v>2.95</v>
       </c>
       <c r="Q22" s="76">
         <v>0</v>
@@ -3592,7 +3592,7 @@
     </row>
     <row r="24" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="78">
-        <v>4.1700000000000001E-2</v>
+        <v>4.1200000000000001E-2</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>27</v>
@@ -3601,10 +3601,10 @@
         <v>137</v>
       </c>
       <c r="D24" s="72">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="E24" s="72">
-        <v>3.84</v>
+        <v>3.88</v>
       </c>
       <c r="F24" s="73">
         <v>4</v>
@@ -3617,10 +3617,10 @@
         <v>73</v>
       </c>
       <c r="J24" s="72">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K24" s="72">
-        <v>95.8</v>
+        <v>96.9</v>
       </c>
       <c r="L24" s="74"/>
       <c r="M24" s="74"/>
@@ -3631,10 +3631,10 @@
         <v>24</v>
       </c>
       <c r="P24" s="73">
-        <v>3.99</v>
+        <v>4.04</v>
       </c>
       <c r="Q24" s="76">
-        <v>647.36</v>
+        <v>651.52</v>
       </c>
       <c r="R24" s="77" t="s">
         <v>10</v>
@@ -3642,7 +3642,7 @@
     </row>
     <row r="25" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="84">
-        <v>8.8599999999999998E-2</v>
+        <v>8.43E-2</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>122</v>
@@ -3651,10 +3651,10 @@
         <v>3</v>
       </c>
       <c r="D25" s="72">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="E25" s="72">
-        <v>3.16</v>
+        <v>3.32</v>
       </c>
       <c r="F25" s="73">
         <v>7</v>
@@ -3667,10 +3667,10 @@
         <v>68</v>
       </c>
       <c r="J25" s="72">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="K25" s="72">
-        <v>75.2</v>
+        <v>79.3</v>
       </c>
       <c r="L25" s="74"/>
       <c r="M25" s="74"/>
@@ -3681,10 +3681,10 @@
         <v>23</v>
       </c>
       <c r="P25" s="73">
-        <v>3.27</v>
+        <v>3.45</v>
       </c>
       <c r="Q25" s="76">
-        <v>225.48</v>
+        <v>237.96</v>
       </c>
       <c r="R25" s="77" t="s">
         <v>10</v>
@@ -3742,7 +3742,7 @@
     </row>
     <row r="27" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="85">
-        <v>0.02</v>
+        <v>1.9599999999999999E-2</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>30</v>
@@ -3754,7 +3754,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="72">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="F27" s="73">
         <v>1</v>
@@ -3767,10 +3767,10 @@
         <v>31</v>
       </c>
       <c r="J27" s="72">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K27" s="72">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L27" s="74"/>
       <c r="M27" s="74"/>
@@ -3781,10 +3781,10 @@
         <v>20</v>
       </c>
       <c r="P27" s="73">
-        <v>2.5</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="Q27" s="76">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="R27" s="77" t="s">
         <v>10</v>
@@ -3836,7 +3836,7 @@
     </row>
     <row r="29" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="78">
-        <v>4.1099999999999998E-2</v>
+        <v>3.85E-2</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>31</v>
@@ -3845,10 +3845,10 @@
         <v>135</v>
       </c>
       <c r="D29" s="72">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E29" s="72">
-        <v>2.92</v>
+        <v>3.12</v>
       </c>
       <c r="F29" s="73">
         <v>3</v>
@@ -3861,10 +3861,10 @@
         <v>58</v>
       </c>
       <c r="J29" s="72">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="K29" s="72">
-        <v>72.900000000000006</v>
+        <v>78</v>
       </c>
       <c r="L29" s="74"/>
       <c r="M29" s="74"/>
@@ -3875,7 +3875,7 @@
         <v>23</v>
       </c>
       <c r="P29" s="73">
-        <v>3.17</v>
+        <v>3.39</v>
       </c>
       <c r="Q29" s="76">
         <v>0</v>
@@ -3886,7 +3886,7 @@
     </row>
     <row r="30" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="85">
-        <v>1.43E-2</v>
+        <v>1.41E-2</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>32</v>
@@ -3898,7 +3898,7 @@
         <v>0</v>
       </c>
       <c r="E30" s="72">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="F30" s="73">
         <v>1</v>
@@ -3913,10 +3913,10 @@
         <v>61</v>
       </c>
       <c r="J30" s="72">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K30" s="72">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L30" s="74"/>
       <c r="M30" s="74"/>
@@ -3927,10 +3927,10 @@
         <v>23</v>
       </c>
       <c r="P30" s="73">
-        <v>3.04</v>
+        <v>3.09</v>
       </c>
       <c r="Q30" s="76">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="R30" s="77" t="s">
         <v>10</v>
@@ -3938,7 +3938,7 @@
     </row>
     <row r="31" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="85">
-        <v>1.6400000000000001E-2</v>
+        <v>1.6299999999999999E-2</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>33</v>
@@ -3950,7 +3950,7 @@
         <v>0</v>
       </c>
       <c r="E31" s="72">
-        <v>4.88</v>
+        <v>4.92</v>
       </c>
       <c r="F31" s="73">
         <v>2</v>
@@ -3963,10 +3963,10 @@
         <v>74</v>
       </c>
       <c r="J31" s="72">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K31" s="72">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="L31" s="74"/>
       <c r="M31" s="74"/>
@@ -3977,10 +3977,10 @@
         <v>23</v>
       </c>
       <c r="P31" s="73">
-        <v>5.3</v>
+        <v>5.35</v>
       </c>
       <c r="Q31" s="76">
-        <v>642</v>
+        <v>648</v>
       </c>
       <c r="R31" s="77" t="s">
         <v>10</v>
@@ -3988,7 +3988,7 @@
     </row>
     <row r="32" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="85">
-        <v>1.8700000000000001E-2</v>
+        <v>1.8200000000000001E-2</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>34</v>
@@ -4000,7 +4000,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="72">
-        <v>4.28</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="F32" s="73">
         <v>2</v>
@@ -4015,10 +4015,10 @@
         <v>94</v>
       </c>
       <c r="J32" s="72">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="K32" s="72">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="L32" s="74"/>
       <c r="M32" s="74"/>
@@ -4029,7 +4029,7 @@
         <v>23</v>
       </c>
       <c r="P32" s="73">
-        <v>4.6500000000000004</v>
+        <v>4.78</v>
       </c>
       <c r="Q32" s="76">
         <v>0</v>
@@ -4040,7 +4040,7 @@
     </row>
     <row r="33" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="80">
-        <v>7.9000000000000008E-3</v>
+        <v>7.7999999999999996E-3</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>35</v>
@@ -4052,7 +4052,7 @@
         <v>0</v>
       </c>
       <c r="E33" s="72">
-        <v>5.08</v>
+        <v>5.16</v>
       </c>
       <c r="F33" s="73">
         <v>1</v>
@@ -4067,10 +4067,10 @@
         <v>109</v>
       </c>
       <c r="J33" s="72">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="K33" s="72">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="L33" s="74"/>
       <c r="M33" s="74"/>
@@ -4081,10 +4081,10 @@
         <v>22</v>
       </c>
       <c r="P33" s="73">
-        <v>5.77</v>
+        <v>5.86</v>
       </c>
       <c r="Q33" s="76">
-        <v>702</v>
+        <v>714</v>
       </c>
       <c r="R33" s="77" t="s">
         <v>10</v>
@@ -4092,7 +4092,7 @@
     </row>
     <row r="34" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="78">
-        <v>3.5299999999999998E-2</v>
+        <v>3.3000000000000002E-2</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>123</v>
@@ -4104,7 +4104,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="72">
-        <v>3.4</v>
+        <v>3.64</v>
       </c>
       <c r="F34" s="73">
         <v>3</v>
@@ -4117,10 +4117,10 @@
         <v>72</v>
       </c>
       <c r="J34" s="72">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="K34" s="72">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="L34" s="74"/>
       <c r="M34" s="74"/>
@@ -4131,7 +4131,7 @@
         <v>23</v>
       </c>
       <c r="P34" s="73">
-        <v>3.7</v>
+        <v>3.96</v>
       </c>
       <c r="Q34" s="76">
         <v>0</v>
@@ -4194,7 +4194,7 @@
     </row>
     <row r="36" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="70">
-        <v>6.0600000000000001E-2</v>
+        <v>5.9400000000000001E-2</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>124</v>
@@ -4206,7 +4206,7 @@
         <v>2</v>
       </c>
       <c r="E36" s="72">
-        <v>3.96</v>
+        <v>4.04</v>
       </c>
       <c r="F36" s="73">
         <v>6</v>
@@ -4219,10 +4219,10 @@
         <v>86</v>
       </c>
       <c r="J36" s="72">
+        <v>101</v>
+      </c>
+      <c r="K36" s="72">
         <v>99</v>
-      </c>
-      <c r="K36" s="72">
-        <v>97</v>
       </c>
       <c r="L36" s="74"/>
       <c r="M36" s="74"/>
@@ -4233,10 +4233,10 @@
         <v>23</v>
       </c>
       <c r="P36" s="73">
-        <v>4.22</v>
+        <v>4.3099999999999996</v>
       </c>
       <c r="Q36" s="76">
-        <v>319.83999999999997</v>
+        <v>328.16</v>
       </c>
       <c r="R36" s="77" t="s">
         <v>10</v>
@@ -4244,7 +4244,7 @@
     </row>
     <row r="37" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="85">
-        <v>2.2700000000000001E-2</v>
+        <v>2.2499999999999999E-2</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>89</v>
@@ -4256,7 +4256,7 @@
         <v>0</v>
       </c>
       <c r="E37" s="72">
-        <v>3.52</v>
+        <v>3.56</v>
       </c>
       <c r="F37" s="73">
         <v>2</v>
@@ -4269,10 +4269,10 @@
         <v>79</v>
       </c>
       <c r="J37" s="72">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K37" s="72">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L37" s="74"/>
       <c r="M37" s="74"/>
@@ -4283,7 +4283,7 @@
         <v>22</v>
       </c>
       <c r="P37" s="73">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="Q37" s="76">
         <v>0</v>
@@ -4294,7 +4294,7 @@
     </row>
     <row r="38" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="85">
-        <v>1.4800000000000001E-2</v>
+        <v>1.4500000000000001E-2</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>38</v>
@@ -4306,7 +4306,7 @@
         <v>0</v>
       </c>
       <c r="E38" s="72">
-        <v>5.4</v>
+        <v>5.52</v>
       </c>
       <c r="F38" s="73">
         <v>2</v>
@@ -4321,10 +4321,10 @@
         <v>68</v>
       </c>
       <c r="J38" s="72">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="K38" s="72">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="L38" s="74"/>
       <c r="M38" s="74"/>
@@ -4335,10 +4335,10 @@
         <v>18</v>
       </c>
       <c r="P38" s="73">
-        <v>7.5</v>
+        <v>7.67</v>
       </c>
       <c r="Q38" s="76">
-        <v>1290</v>
+        <v>1320</v>
       </c>
       <c r="R38" s="77" t="s">
         <v>10</v>
@@ -4346,7 +4346,7 @@
     </row>
     <row r="39" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="85">
-        <v>1.4800000000000001E-2</v>
+        <v>1.47E-2</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>39</v>
@@ -4358,7 +4358,7 @@
         <v>0</v>
       </c>
       <c r="E39" s="72">
-        <v>5.4</v>
+        <v>5.44</v>
       </c>
       <c r="F39" s="73">
         <v>2</v>
@@ -4373,10 +4373,10 @@
         <v>91</v>
       </c>
       <c r="J39" s="72">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="K39" s="72">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L39" s="74"/>
       <c r="M39" s="74"/>
@@ -4387,10 +4387,10 @@
         <v>24</v>
       </c>
       <c r="P39" s="73">
-        <v>5.63</v>
+        <v>5.67</v>
       </c>
       <c r="Q39" s="76">
-        <v>1224</v>
+        <v>1232</v>
       </c>
       <c r="R39" s="77" t="s">
         <v>10</v>
@@ -4398,7 +4398,7 @@
     </row>
     <row r="40" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="85">
-        <v>2.29E-2</v>
+        <v>2.24E-2</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>40</v>
@@ -4410,7 +4410,7 @@
         <v>0</v>
       </c>
       <c r="E40" s="72">
-        <v>5.24</v>
+        <v>5.36</v>
       </c>
       <c r="F40" s="73">
         <v>3</v>
@@ -4423,10 +4423,10 @@
         <v>117</v>
       </c>
       <c r="J40" s="72">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="K40" s="72">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="L40" s="74"/>
       <c r="M40" s="74"/>
@@ -4437,10 +4437,10 @@
         <v>16</v>
       </c>
       <c r="P40" s="73">
-        <v>8.19</v>
+        <v>8.3800000000000008</v>
       </c>
       <c r="Q40" s="76">
-        <v>1230</v>
+        <v>1260</v>
       </c>
       <c r="R40" s="77" t="s">
         <v>10</v>
@@ -4448,7 +4448,7 @@
     </row>
     <row r="41" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="85">
-        <v>2.0799999999999999E-2</v>
+        <v>2.06E-2</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>41</v>
@@ -4460,7 +4460,7 @@
         <v>0</v>
       </c>
       <c r="E41" s="72">
-        <v>3.84</v>
+        <v>3.88</v>
       </c>
       <c r="F41" s="73">
         <v>2</v>
@@ -4475,10 +4475,10 @@
         <v>74</v>
       </c>
       <c r="J41" s="72">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K41" s="72">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L41" s="74"/>
       <c r="M41" s="74"/>
@@ -4489,10 +4489,10 @@
         <v>22</v>
       </c>
       <c r="P41" s="73">
-        <v>4.3600000000000003</v>
+        <v>4.41</v>
       </c>
       <c r="Q41" s="76">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="R41" s="77" t="s">
         <v>10</v>
@@ -4500,7 +4500,7 @@
     </row>
     <row r="42" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="78">
-        <v>3.09E-2</v>
+        <v>0.03</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>42</v>
@@ -4512,7 +4512,7 @@
         <v>0</v>
       </c>
       <c r="E42" s="72">
-        <v>3.88</v>
+        <v>4</v>
       </c>
       <c r="F42" s="73">
         <v>3</v>
@@ -4527,10 +4527,10 @@
         <v>88</v>
       </c>
       <c r="J42" s="72">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="K42" s="72">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="L42" s="74"/>
       <c r="M42" s="74"/>
@@ -4541,10 +4541,10 @@
         <v>20</v>
       </c>
       <c r="P42" s="73">
-        <v>4.8499999999999996</v>
+        <v>5</v>
       </c>
       <c r="Q42" s="76">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="R42" s="77" t="s">
         <v>10</v>
@@ -4552,7 +4552,7 @@
     </row>
     <row r="43" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="78">
-        <v>0.04</v>
+        <v>3.8800000000000001E-2</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>43</v>
@@ -4564,7 +4564,7 @@
         <v>0</v>
       </c>
       <c r="E43" s="72">
-        <v>5</v>
+        <v>5.16</v>
       </c>
       <c r="F43" s="73">
         <v>5</v>
@@ -4579,10 +4579,10 @@
         <v>83</v>
       </c>
       <c r="J43" s="72">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="K43" s="72">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="L43" s="74"/>
       <c r="M43" s="74"/>
@@ -4593,10 +4593,10 @@
         <v>23</v>
       </c>
       <c r="P43" s="73">
-        <v>5.43</v>
+        <v>5.61</v>
       </c>
       <c r="Q43" s="76">
-        <v>1029</v>
+        <v>1220</v>
       </c>
       <c r="R43" s="77" t="s">
         <v>10</v>
@@ -4648,7 +4648,7 @@
     </row>
     <row r="45" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="70">
-        <v>6.0900000000000003E-2</v>
+        <v>5.8799999999999998E-2</v>
       </c>
       <c r="B45" s="4" t="s">
         <v>46</v>
@@ -4657,10 +4657,10 @@
         <v>135</v>
       </c>
       <c r="D45" s="72">
-        <v>2.4</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="E45" s="72">
-        <v>4.5999999999999996</v>
+        <v>4.76</v>
       </c>
       <c r="F45" s="73">
         <v>7</v>
@@ -4673,10 +4673,10 @@
         <v>108</v>
       </c>
       <c r="J45" s="72">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="K45" s="72">
-        <v>112.6</v>
+        <v>116.8</v>
       </c>
       <c r="L45" s="74"/>
       <c r="M45" s="74"/>
@@ -4687,10 +4687,10 @@
         <v>20</v>
       </c>
       <c r="P45" s="73">
-        <v>5.63</v>
+        <v>5.84</v>
       </c>
       <c r="Q45" s="76">
-        <v>350.4</v>
+        <v>367.04</v>
       </c>
       <c r="R45" s="77" t="s">
         <v>10</v>
@@ -4698,7 +4698,7 @@
     </row>
     <row r="46" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="85">
-        <v>2.7E-2</v>
+        <v>2.5999999999999999E-2</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>182</v>
@@ -4710,7 +4710,7 @@
         <v>0</v>
       </c>
       <c r="E46" s="72">
-        <v>2.96</v>
+        <v>3.08</v>
       </c>
       <c r="F46" s="73">
         <v>2</v>
@@ -4725,10 +4725,10 @@
         <v>50</v>
       </c>
       <c r="J46" s="72">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="K46" s="72">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="L46" s="74"/>
       <c r="M46" s="74"/>
@@ -4739,7 +4739,7 @@
         <v>21</v>
       </c>
       <c r="P46" s="73">
-        <v>3.52</v>
+        <v>3.67</v>
       </c>
       <c r="Q46" s="76">
         <v>0</v>
@@ -4750,7 +4750,7 @@
     </row>
     <row r="47" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="85">
-        <v>2.58E-2</v>
+        <v>2.47E-2</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>48</v>
@@ -4762,7 +4762,7 @@
         <v>0</v>
       </c>
       <c r="E47" s="72">
-        <v>6.2</v>
+        <v>6.48</v>
       </c>
       <c r="F47" s="73">
         <v>4</v>
@@ -4775,10 +4775,10 @@
         <v>143</v>
       </c>
       <c r="J47" s="72">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="K47" s="72">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="L47" s="74"/>
       <c r="M47" s="74"/>
@@ -4789,10 +4789,10 @@
         <v>21</v>
       </c>
       <c r="P47" s="73">
-        <v>7.38</v>
+        <v>7.71</v>
       </c>
       <c r="Q47" s="76">
-        <v>964</v>
+        <v>1020</v>
       </c>
       <c r="R47" s="77" t="s">
         <v>10</v>
@@ -4800,7 +4800,7 @@
     </row>
     <row r="48" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="78">
-        <v>4.4400000000000002E-2</v>
+        <v>4.2599999999999999E-2</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>183</v>
@@ -4809,10 +4809,10 @@
         <v>13</v>
       </c>
       <c r="D48" s="72">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="E48" s="72">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="F48" s="73">
         <v>2</v>
@@ -4825,10 +4825,10 @@
         <v>24</v>
       </c>
       <c r="J48" s="72">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K48" s="72">
-        <v>44.8</v>
+        <v>46.9</v>
       </c>
       <c r="L48" s="74"/>
       <c r="M48" s="74"/>
@@ -4839,7 +4839,7 @@
         <v>19</v>
       </c>
       <c r="P48" s="73">
-        <v>2.36</v>
+        <v>2.4700000000000002</v>
       </c>
       <c r="Q48" s="82" t="s">
         <v>13</v>
@@ -4938,7 +4938,7 @@
     </row>
     <row r="51" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="70">
-        <v>5.8799999999999998E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="B51" s="4" t="s">
         <v>50</v>
@@ -4947,10 +4947,10 @@
         <v>3</v>
       </c>
       <c r="D51" s="72">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="E51" s="72">
-        <v>4.08</v>
+        <v>4.3600000000000003</v>
       </c>
       <c r="F51" s="73">
         <v>6</v>
@@ -4963,10 +4963,10 @@
         <v>74</v>
       </c>
       <c r="J51" s="72">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="K51" s="72">
-        <v>100.1</v>
+        <v>107.4</v>
       </c>
       <c r="L51" s="74"/>
       <c r="M51" s="74"/>
@@ -4977,10 +4977,10 @@
         <v>23</v>
       </c>
       <c r="P51" s="73">
-        <v>4.3499999999999996</v>
+        <v>4.67</v>
       </c>
       <c r="Q51" s="76">
-        <v>332.32</v>
+        <v>361.44</v>
       </c>
       <c r="R51" s="77" t="s">
         <v>10</v>
@@ -4988,7 +4988,7 @@
     </row>
     <row r="52" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="78">
-        <v>4.2900000000000001E-2</v>
+        <v>4.1099999999999998E-2</v>
       </c>
       <c r="B52" s="4" t="s">
         <v>51</v>
@@ -4997,10 +4997,10 @@
         <v>3</v>
       </c>
       <c r="D52" s="72">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="E52" s="72">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="F52" s="73">
         <v>3</v>
@@ -5013,10 +5013,10 @@
         <v>65</v>
       </c>
       <c r="J52" s="72">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="K52" s="72">
-        <v>69.8</v>
+        <v>72.900000000000006</v>
       </c>
       <c r="L52" s="74"/>
       <c r="M52" s="74"/>
@@ -5027,10 +5027,10 @@
         <v>20</v>
       </c>
       <c r="P52" s="73">
-        <v>3.49</v>
+        <v>3.65</v>
       </c>
       <c r="Q52" s="76">
-        <v>209.4</v>
+        <v>218.76</v>
       </c>
       <c r="R52" s="77" t="s">
         <v>10</v>
@@ -5050,7 +5050,7 @@
         <v>0</v>
       </c>
       <c r="E53" s="72">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="F53" s="81"/>
       <c r="G53" s="4"/>
@@ -5061,10 +5061,10 @@
         <v>45</v>
       </c>
       <c r="J53" s="72">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K53" s="72">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="L53" s="74"/>
       <c r="M53" s="74"/>
@@ -5075,10 +5075,10 @@
         <v>19</v>
       </c>
       <c r="P53" s="73">
-        <v>3.26</v>
+        <v>3.37</v>
       </c>
       <c r="Q53" s="76">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="R53" s="77" t="s">
         <v>10</v>
@@ -5134,7 +5134,7 @@
     </row>
     <row r="55" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" s="70">
-        <v>6.1899999999999997E-2</v>
+        <v>5.8799999999999998E-2</v>
       </c>
       <c r="B55" s="4" t="s">
         <v>91</v>
@@ -5143,10 +5143,10 @@
         <v>3</v>
       </c>
       <c r="D55" s="72">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="E55" s="72">
-        <v>3.88</v>
+        <v>4.08</v>
       </c>
       <c r="F55" s="73">
         <v>6</v>
@@ -5159,10 +5159,10 @@
         <v>79</v>
       </c>
       <c r="J55" s="72">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="K55" s="72">
-        <v>94.9</v>
+        <v>100.1</v>
       </c>
       <c r="L55" s="74"/>
       <c r="M55" s="74"/>
@@ -5173,10 +5173,10 @@
         <v>23</v>
       </c>
       <c r="P55" s="73">
-        <v>4.13</v>
+        <v>4.3499999999999996</v>
       </c>
       <c r="Q55" s="76">
-        <v>311.52</v>
+        <v>332.32</v>
       </c>
       <c r="R55" s="77" t="s">
         <v>10</v>
@@ -5184,7 +5184,7 @@
     </row>
     <row r="56" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="70">
-        <v>6.0600000000000001E-2</v>
+        <v>5.8000000000000003E-2</v>
       </c>
       <c r="B56" s="4" t="s">
         <v>127</v>
@@ -5193,10 +5193,10 @@
         <v>135</v>
       </c>
       <c r="D56" s="72">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="E56" s="72">
-        <v>2.64</v>
+        <v>2.76</v>
       </c>
       <c r="F56" s="73">
         <v>4</v>
@@ -5209,10 +5209,10 @@
         <v>53</v>
       </c>
       <c r="J56" s="72">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="K56" s="72">
-        <v>64.599999999999994</v>
+        <v>67.8</v>
       </c>
       <c r="L56" s="74"/>
       <c r="M56" s="74"/>
@@ -5223,7 +5223,7 @@
         <v>21</v>
       </c>
       <c r="P56" s="73">
-        <v>3.08</v>
+        <v>3.23</v>
       </c>
       <c r="Q56" s="76">
         <v>0</v>
@@ -5234,7 +5234,7 @@
     </row>
     <row r="57" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" s="78">
-        <v>3.7400000000000003E-2</v>
+        <v>3.5400000000000001E-2</v>
       </c>
       <c r="B57" s="4" t="s">
         <v>54</v>
@@ -5246,7 +5246,7 @@
         <v>0</v>
       </c>
       <c r="E57" s="72">
-        <v>4.28</v>
+        <v>4.5199999999999996</v>
       </c>
       <c r="F57" s="73">
         <v>4</v>
@@ -5259,10 +5259,10 @@
         <v>102</v>
       </c>
       <c r="J57" s="72">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="K57" s="72">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="L57" s="74"/>
       <c r="M57" s="74"/>
@@ -5270,21 +5270,21 @@
         <v>24</v>
       </c>
       <c r="O57" s="75">
-        <v>23</v>
+        <v>22.5</v>
       </c>
       <c r="P57" s="73">
-        <v>4.6500000000000004</v>
+        <v>5.0199999999999996</v>
       </c>
       <c r="Q57" s="76">
-        <v>0</v>
-      </c>
-      <c r="R57" s="79" t="s">
-        <v>12</v>
+        <v>302</v>
+      </c>
+      <c r="R57" s="77" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="58" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" s="78">
-        <v>4.82E-2</v>
+        <v>4.3999999999999997E-2</v>
       </c>
       <c r="B58" s="4" t="s">
         <v>128</v>
@@ -5293,10 +5293,10 @@
         <v>3</v>
       </c>
       <c r="D58" s="72">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="E58" s="72">
-        <v>3.32</v>
+        <v>3.64</v>
       </c>
       <c r="F58" s="73">
         <v>4</v>
@@ -5309,10 +5309,10 @@
         <v>67</v>
       </c>
       <c r="J58" s="72">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="K58" s="72">
-        <v>82.3</v>
+        <v>90.6</v>
       </c>
       <c r="L58" s="74"/>
       <c r="M58" s="74"/>
@@ -5323,10 +5323,10 @@
         <v>22</v>
       </c>
       <c r="P58" s="73">
-        <v>3.74</v>
+        <v>4.12</v>
       </c>
       <c r="Q58" s="76">
-        <v>246.96</v>
+        <v>310.56</v>
       </c>
       <c r="R58" s="77" t="s">
         <v>10</v>
@@ -5432,7 +5432,7 @@
     </row>
     <row r="61" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A61" s="84">
-        <v>0.1009</v>
+        <v>9.4799999999999995E-2</v>
       </c>
       <c r="B61" s="4" t="s">
         <v>57</v>
@@ -5441,10 +5441,10 @@
         <v>3</v>
       </c>
       <c r="D61" s="72">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="E61" s="72">
-        <v>4.3600000000000003</v>
+        <v>4.6399999999999997</v>
       </c>
       <c r="F61" s="73">
         <v>11</v>
@@ -5457,10 +5457,10 @@
         <v>97</v>
       </c>
       <c r="J61" s="72">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="K61" s="72">
-        <v>102.4</v>
+        <v>109.6</v>
       </c>
       <c r="L61" s="86"/>
       <c r="M61" s="86"/>
@@ -5471,10 +5471,10 @@
         <v>23</v>
       </c>
       <c r="P61" s="73">
-        <v>4.45</v>
+        <v>4.7699999999999996</v>
       </c>
       <c r="Q61" s="76">
-        <v>341.44</v>
+        <v>370.56</v>
       </c>
       <c r="R61" s="77" t="s">
         <v>10</v>
@@ -5482,7 +5482,7 @@
     </row>
     <row r="62" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A62" s="78">
-        <v>3.9600000000000003E-2</v>
+        <v>3.85E-2</v>
       </c>
       <c r="B62" s="4" t="s">
         <v>58</v>
@@ -5494,7 +5494,7 @@
         <v>0</v>
       </c>
       <c r="E62" s="72">
-        <v>4.04</v>
+        <v>4.16</v>
       </c>
       <c r="F62" s="73">
         <v>4</v>
@@ -5507,10 +5507,10 @@
         <v>75</v>
       </c>
       <c r="J62" s="72">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="K62" s="72">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="L62" s="86"/>
       <c r="M62" s="86"/>
@@ -5521,10 +5521,10 @@
         <v>22</v>
       </c>
       <c r="P62" s="73">
-        <v>4.59</v>
+        <v>4.7300000000000004</v>
       </c>
       <c r="Q62" s="76">
-        <v>352</v>
+        <v>364</v>
       </c>
       <c r="R62" s="77" t="s">
         <v>10</v>
@@ -5532,7 +5532,7 @@
     </row>
     <row r="63" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A63" s="85">
-        <v>2.7E-2</v>
+        <v>2.5999999999999999E-2</v>
       </c>
       <c r="B63" s="4" t="s">
         <v>92</v>
@@ -5544,7 +5544,7 @@
         <v>0</v>
       </c>
       <c r="E63" s="72">
-        <v>2.96</v>
+        <v>3.08</v>
       </c>
       <c r="F63" s="73">
         <v>2</v>
@@ -5557,10 +5557,10 @@
         <v>65</v>
       </c>
       <c r="J63" s="72">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="K63" s="72">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="L63" s="86"/>
       <c r="M63" s="86"/>
@@ -5571,7 +5571,7 @@
         <v>18</v>
       </c>
       <c r="P63" s="73">
-        <v>4.1100000000000003</v>
+        <v>4.28</v>
       </c>
       <c r="Q63" s="76">
         <v>0</v>
@@ -5582,7 +5582,7 @@
     </row>
     <row r="64" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A64" s="85">
-        <v>1.83E-2</v>
+        <v>1.7399999999999999E-2</v>
       </c>
       <c r="B64" s="4" t="s">
         <v>59</v>
@@ -5594,7 +5594,7 @@
         <v>0</v>
       </c>
       <c r="E64" s="72">
-        <v>4.3600000000000003</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="F64" s="73">
         <v>2</v>
@@ -5607,10 +5607,10 @@
         <v>103</v>
       </c>
       <c r="J64" s="72">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="K64" s="72">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="L64" s="86"/>
       <c r="M64" s="86"/>
@@ -5621,10 +5621,10 @@
         <v>22</v>
       </c>
       <c r="P64" s="73">
-        <v>4.95</v>
+        <v>5.23</v>
       </c>
       <c r="Q64" s="76">
-        <v>297</v>
+        <v>320</v>
       </c>
       <c r="R64" s="77" t="s">
         <v>10</v>
@@ -5632,7 +5632,7 @@
     </row>
     <row r="65" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="84">
-        <v>9.3799999999999994E-2</v>
+        <v>8.3299999999999999E-2</v>
       </c>
       <c r="B65" s="4" t="s">
         <v>60</v>
@@ -5641,10 +5641,10 @@
         <v>3</v>
       </c>
       <c r="D65" s="72">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="E65" s="72">
-        <v>2.56</v>
+        <v>2.88</v>
       </c>
       <c r="F65" s="73">
         <v>6</v>
@@ -5657,10 +5657,10 @@
         <v>42</v>
       </c>
       <c r="J65" s="72">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="K65" s="72">
-        <v>60.6</v>
+        <v>68.900000000000006</v>
       </c>
       <c r="L65" s="86"/>
       <c r="M65" s="86"/>
@@ -5671,10 +5671,10 @@
         <v>17</v>
       </c>
       <c r="P65" s="73">
-        <v>3.56</v>
+        <v>4.05</v>
       </c>
       <c r="Q65" s="76">
-        <v>181.68</v>
+        <v>303.52</v>
       </c>
       <c r="R65" s="77" t="s">
         <v>10</v>
@@ -5682,7 +5682,7 @@
     </row>
     <row r="66" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="70">
-        <v>6.0600000000000001E-2</v>
+        <v>5.6300000000000003E-2</v>
       </c>
       <c r="B66" s="4" t="s">
         <v>61</v>
@@ -5691,10 +5691,10 @@
         <v>135</v>
       </c>
       <c r="D66" s="72">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="E66" s="72">
-        <v>2.64</v>
+        <v>2.84</v>
       </c>
       <c r="F66" s="73">
         <v>4</v>
@@ -5707,10 +5707,10 @@
         <v>60</v>
       </c>
       <c r="J66" s="72">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="K66" s="72">
-        <v>64.599999999999994</v>
+        <v>69.8</v>
       </c>
       <c r="L66" s="86"/>
       <c r="M66" s="86"/>
@@ -5721,7 +5721,7 @@
         <v>21</v>
       </c>
       <c r="P66" s="73">
-        <v>3.08</v>
+        <v>3.33</v>
       </c>
       <c r="Q66" s="76">
         <v>0</v>
@@ -5744,7 +5744,7 @@
         <v>0</v>
       </c>
       <c r="E67" s="72">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="F67" s="81"/>
       <c r="G67" s="4"/>
@@ -5755,10 +5755,10 @@
         <v>55</v>
       </c>
       <c r="J67" s="72">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K67" s="72">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L67" s="86"/>
       <c r="M67" s="86"/>
@@ -5769,7 +5769,7 @@
         <v>19</v>
       </c>
       <c r="P67" s="73">
-        <v>3.37</v>
+        <v>3.42</v>
       </c>
       <c r="Q67" s="76">
         <v>0</v>
@@ -5780,7 +5780,7 @@
     </row>
     <row r="68" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A68" s="84">
-        <v>8.3299999999999999E-2</v>
+        <v>7.4800000000000005E-2</v>
       </c>
       <c r="B68" s="4" t="s">
         <v>64</v>
@@ -5789,10 +5789,10 @@
         <v>135</v>
       </c>
       <c r="D68" s="72">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="E68" s="72">
-        <v>3.84</v>
+        <v>4.28</v>
       </c>
       <c r="F68" s="73">
         <v>8</v>
@@ -5805,10 +5805,10 @@
         <v>93</v>
       </c>
       <c r="J68" s="72">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="K68" s="72">
-        <v>91.8</v>
+        <v>103.3</v>
       </c>
       <c r="L68" s="86"/>
       <c r="M68" s="86"/>
@@ -5819,13 +5819,13 @@
         <v>20</v>
       </c>
       <c r="P68" s="73">
-        <v>4.59</v>
+        <v>5.16</v>
       </c>
       <c r="Q68" s="76">
-        <v>0</v>
-      </c>
-      <c r="R68" s="79" t="s">
-        <v>12</v>
+        <v>313.12</v>
+      </c>
+      <c r="R68" s="77" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="69" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5926,7 +5926,7 @@
     </row>
     <row r="71" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A71" s="84">
-        <v>9.2600000000000002E-2</v>
+        <v>8.9300000000000004E-2</v>
       </c>
       <c r="B71" s="4" t="s">
         <v>69</v>
@@ -5938,7 +5938,7 @@
         <v>2.8</v>
       </c>
       <c r="E71" s="72">
-        <v>2.16</v>
+        <v>2.2400000000000002</v>
       </c>
       <c r="F71" s="73">
         <v>5</v>
@@ -5953,10 +5953,10 @@
         <v>41</v>
       </c>
       <c r="J71" s="72">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K71" s="72">
-        <v>51.2</v>
+        <v>53.2</v>
       </c>
       <c r="L71" s="86"/>
       <c r="M71" s="86"/>
@@ -5967,10 +5967,10 @@
         <v>9</v>
       </c>
       <c r="P71" s="73">
-        <v>5.68</v>
+        <v>5.92</v>
       </c>
       <c r="Q71" s="76">
-        <v>404.43</v>
+        <v>409.97</v>
       </c>
       <c r="R71" s="77" t="s">
         <v>10</v>
@@ -5978,7 +5978,7 @@
     </row>
     <row r="72" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A72" s="70">
-        <v>5.3800000000000001E-2</v>
+        <v>5.3199999999999997E-2</v>
       </c>
       <c r="B72" s="4" t="s">
         <v>70</v>
@@ -5987,10 +5987,10 @@
         <v>135</v>
       </c>
       <c r="D72" s="72">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="E72" s="72">
-        <v>3.72</v>
+        <v>3.76</v>
       </c>
       <c r="F72" s="73">
         <v>5</v>
@@ -6005,10 +6005,10 @@
         <v>75</v>
       </c>
       <c r="J72" s="72">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K72" s="72">
-        <v>91.7</v>
+        <v>92.8</v>
       </c>
       <c r="L72" s="86"/>
       <c r="M72" s="86"/>
@@ -6019,7 +6019,7 @@
         <v>22</v>
       </c>
       <c r="P72" s="73">
-        <v>4.17</v>
+        <v>4.22</v>
       </c>
       <c r="Q72" s="76">
         <v>0</v>
@@ -6172,7 +6172,7 @@
     </row>
     <row r="76" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A76" s="85">
-        <v>2.1600000000000001E-2</v>
+        <v>2.1100000000000001E-2</v>
       </c>
       <c r="B76" s="4" t="s">
         <v>74</v>
@@ -6184,7 +6184,7 @@
         <v>0</v>
       </c>
       <c r="E76" s="72">
-        <v>5.56</v>
+        <v>5.68</v>
       </c>
       <c r="F76" s="73">
         <v>3</v>
@@ -6197,10 +6197,10 @@
         <v>107</v>
       </c>
       <c r="J76" s="72">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="K76" s="72">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L76" s="86"/>
       <c r="M76" s="86"/>
@@ -6211,10 +6211,10 @@
         <v>22</v>
       </c>
       <c r="P76" s="73">
-        <v>6.32</v>
+        <v>6.45</v>
       </c>
       <c r="Q76" s="76">
-        <v>642</v>
+        <v>660</v>
       </c>
       <c r="R76" s="77" t="s">
         <v>10</v>
@@ -6234,7 +6234,7 @@
         <v>0</v>
       </c>
       <c r="E77" s="72">
-        <v>2.64</v>
+        <v>2.76</v>
       </c>
       <c r="F77" s="81"/>
       <c r="G77" s="4"/>
@@ -6245,10 +6245,10 @@
         <v>55</v>
       </c>
       <c r="J77" s="72">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="K77" s="72">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="L77" s="86"/>
       <c r="M77" s="86"/>
@@ -6257,7 +6257,7 @@
         <v>23</v>
       </c>
       <c r="P77" s="73">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="Q77" s="76">
         <v>159.38</v>
@@ -6267,8 +6267,8 @@
       </c>
     </row>
     <row r="78" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="84">
-        <v>7.2700000000000001E-2</v>
+      <c r="A78" s="70">
+        <v>6.9000000000000006E-2</v>
       </c>
       <c r="B78" s="4" t="s">
         <v>76</v>
@@ -6277,10 +6277,10 @@
         <v>3</v>
       </c>
       <c r="D78" s="72">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="E78" s="72">
-        <v>2.2000000000000002</v>
+        <v>2.3199999999999998</v>
       </c>
       <c r="F78" s="73">
         <v>4</v>
@@ -6293,10 +6293,10 @@
         <v>47</v>
       </c>
       <c r="J78" s="72">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K78" s="72">
-        <v>53.2</v>
+        <v>56.3</v>
       </c>
       <c r="L78" s="86"/>
       <c r="M78" s="86"/>
@@ -6307,10 +6307,10 @@
         <v>23</v>
       </c>
       <c r="P78" s="73">
-        <v>2.31</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="Q78" s="76">
-        <v>159.6</v>
+        <v>168.96</v>
       </c>
       <c r="R78" s="77" t="s">
         <v>10</v>
@@ -6318,7 +6318,7 @@
     </row>
     <row r="79" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A79" s="85">
-        <v>1.3899999999999999E-2</v>
+        <v>1.34E-2</v>
       </c>
       <c r="B79" s="4" t="s">
         <v>77</v>
@@ -6330,7 +6330,7 @@
         <v>0</v>
       </c>
       <c r="E79" s="72">
-        <v>5.76</v>
+        <v>5.96</v>
       </c>
       <c r="F79" s="73">
         <v>2</v>
@@ -6345,10 +6345,10 @@
         <v>110</v>
       </c>
       <c r="J79" s="72">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="K79" s="72">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L79" s="86"/>
       <c r="M79" s="86"/>
@@ -6359,10 +6359,10 @@
         <v>23</v>
       </c>
       <c r="P79" s="73">
-        <v>6.26</v>
+        <v>6.48</v>
       </c>
       <c r="Q79" s="76">
-        <v>1340</v>
+        <v>1380</v>
       </c>
       <c r="R79" s="77" t="s">
         <v>10</v>
@@ -6370,7 +6370,7 @@
     </row>
     <row r="80" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A80" s="85">
-        <v>1.1599999999999999E-2</v>
+        <v>1.15E-2</v>
       </c>
       <c r="B80" s="4" t="s">
         <v>130</v>
@@ -6382,7 +6382,7 @@
         <v>0</v>
       </c>
       <c r="E80" s="72">
-        <v>3.44</v>
+        <v>3.48</v>
       </c>
       <c r="F80" s="73">
         <v>1</v>
@@ -6395,10 +6395,10 @@
         <v>74</v>
       </c>
       <c r="J80" s="72">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K80" s="72">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L80" s="86"/>
       <c r="M80" s="86"/>
@@ -6409,10 +6409,10 @@
         <v>22</v>
       </c>
       <c r="P80" s="73">
-        <v>3.91</v>
+        <v>3.95</v>
       </c>
       <c r="Q80" s="76">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="R80" s="77" t="s">
         <v>10</v>
@@ -6420,7 +6420,7 @@
     </row>
     <row r="81" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A81" s="70">
-        <v>6.6699999999999995E-2</v>
+        <v>6.0999999999999999E-2</v>
       </c>
       <c r="B81" s="4" t="s">
         <v>93</v>
@@ -6429,10 +6429,10 @@
         <v>135</v>
       </c>
       <c r="D81" s="72">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="E81" s="72">
-        <v>3</v>
+        <v>3.28</v>
       </c>
       <c r="F81" s="73">
         <v>5</v>
@@ -6447,10 +6447,10 @@
         <v>57</v>
       </c>
       <c r="J81" s="72">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="K81" s="72">
-        <v>73</v>
+        <v>80.3</v>
       </c>
       <c r="L81" s="86"/>
       <c r="M81" s="86"/>
@@ -6461,7 +6461,7 @@
         <v>18</v>
       </c>
       <c r="P81" s="73">
-        <v>4.0599999999999996</v>
+        <v>4.46</v>
       </c>
       <c r="Q81" s="76">
         <v>0</v>
@@ -6484,7 +6484,7 @@
         <v>0</v>
       </c>
       <c r="E82" s="72">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="F82" s="81"/>
       <c r="G82" s="4"/>
@@ -6495,10 +6495,10 @@
         <v>23</v>
       </c>
       <c r="J82" s="72">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K82" s="72">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L82" s="86"/>
       <c r="M82" s="86"/>
@@ -6509,7 +6509,7 @@
         <v>16</v>
       </c>
       <c r="P82" s="73">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="Q82" s="76">
         <v>0</v>
@@ -6614,7 +6614,7 @@
         <v>22</v>
       </c>
       <c r="I86" s="76">
-        <v>190.73</v>
+        <v>195.72</v>
       </c>
       <c r="J86" s="57"/>
       <c r="K86" s="57"/>
@@ -6674,7 +6674,7 @@
         <v>22</v>
       </c>
       <c r="I88" s="76">
-        <v>200.9</v>
+        <v>207</v>
       </c>
       <c r="J88" s="57"/>
       <c r="K88" s="57"/>
@@ -6704,7 +6704,7 @@
         <v>22</v>
       </c>
       <c r="I89" s="76">
-        <v>402</v>
+        <v>414</v>
       </c>
       <c r="J89" s="57"/>
       <c r="K89" s="57"/>
@@ -6734,7 +6734,7 @@
         <v>22</v>
       </c>
       <c r="I90" s="76">
-        <v>308.7</v>
+        <v>366</v>
       </c>
       <c r="J90" s="57"/>
       <c r="K90" s="57"/>
@@ -6764,7 +6764,7 @@
         <v>22</v>
       </c>
       <c r="I91" s="76">
-        <v>367.2</v>
+        <v>369.6</v>
       </c>
       <c r="J91" s="57"/>
       <c r="K91" s="57"/>
@@ -6794,7 +6794,7 @@
         <v>22</v>
       </c>
       <c r="I92" s="76">
-        <v>202.8</v>
+        <v>204</v>
       </c>
       <c r="J92" s="57"/>
       <c r="K92" s="57"/>
@@ -6824,7 +6824,7 @@
         <v>22</v>
       </c>
       <c r="I93" s="76">
-        <v>194.21</v>
+        <v>195.46</v>
       </c>
       <c r="J93" s="13"/>
       <c r="K93" s="13"/>
@@ -9896,9 +9896,9 @@
         <f t="shared" si="0"/>
         <v>ALAN SOUTO</v>
       </c>
-      <c r="H4">
+      <c r="H4" t="str">
         <f>IFERROR(VLOOKUP(D4,CPF!A:D,4,0),"NAO ENCONTRADO")</f>
-        <v>0</v>
+        <v>646.525.643-68</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
@@ -45841,7 +45841,9 @@
       <c r="C3" s="56" t="s">
         <v>194</v>
       </c>
-      <c r="D3" s="56"/>
+      <c r="D3" s="56" t="s">
+        <v>195</v>
+      </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="56" t="s">
@@ -47037,13 +47039,9 @@
         <v>310</v>
       </c>
     </row>
-    <row r="91" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A91" s="91" t="s">
-        <v>95</v>
-      </c>
-      <c r="D91" s="56" t="s">
-        <v>195</v>
-      </c>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A91" s="56"/>
+      <c r="D91" s="56"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/PREMIO.xlsx
+++ b/PREMIO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alan Souto\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4065F84C-58D8-4FDA-BF12-78AE1B9B3276}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9457629E-4FCC-47DF-ABC9-FF4980A3D163}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EBBE1F25-C943-4A3A-8B11-92CFB5DB310C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{EBBE1F25-C943-4A3A-8B11-92CFB5DB310C}"/>
   </bookViews>
   <sheets>
     <sheet name="RELATORIO CONTROLADORIA" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1180" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1182" uniqueCount="322">
   <si>
     <t>COLABORADOR :</t>
   </si>
@@ -1010,6 +1010,9 @@
   </si>
   <si>
     <t>Dnet</t>
+  </si>
+  <si>
+    <t>047.553.713-09</t>
   </si>
 </sst>
 </file>
@@ -11933,7 +11936,7 @@
       </c>
       <c r="H83" t="str">
         <f>IFERROR(VLOOKUP(D83,CPF!A:D,4,0),"NAO ENCONTRADO")</f>
-        <v>NAO ENCONTRADO</v>
+        <v>047.553.713-09</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
@@ -46336,10 +46339,14 @@
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A39" s="56"/>
+      <c r="A39" s="56" t="s">
+        <v>86</v>
+      </c>
       <c r="B39" s="56"/>
       <c r="C39" s="56"/>
-      <c r="D39" s="56"/>
+      <c r="D39" s="56" t="s">
+        <v>321</v>
+      </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="56" t="s">

--- a/PREMIO.xlsx
+++ b/PREMIO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alan Souto\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9457629E-4FCC-47DF-ABC9-FF4980A3D163}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0B596CDD-F0EF-4120-AB92-05654F56EA34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{EBBE1F25-C943-4A3A-8B11-92CFB5DB310C}"/>
   </bookViews>

--- a/PREMIO.xlsx
+++ b/PREMIO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alan Souto\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0B596CDD-F0EF-4120-AB92-05654F56EA34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2A0DB97-33D8-4E5D-AE92-0C214D7CD147}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{EBBE1F25-C943-4A3A-8B11-92CFB5DB310C}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1182" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="323">
   <si>
     <t>COLABORADOR :</t>
   </si>
@@ -1013,6 +1013,9 @@
   </si>
   <si>
     <t>047.553.713-09</t>
+  </si>
+  <si>
+    <t>614.694.923-00</t>
   </si>
 </sst>
 </file>
@@ -12092,7 +12095,7 @@
       </c>
       <c r="H89" t="str">
         <f>IFERROR(VLOOKUP(D89,CPF!A:D,4,0),"NAO ENCONTRADO")</f>
-        <v>NAO ENCONTRADO</v>
+        <v>614.694.923-00</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.3">
@@ -46587,10 +46590,14 @@
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A57" s="56"/>
+      <c r="A57" s="56" t="s">
+        <v>122</v>
+      </c>
       <c r="B57" s="56"/>
       <c r="C57" s="56"/>
-      <c r="D57" s="56"/>
+      <c r="D57" s="56" t="s">
+        <v>322</v>
+      </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="56" t="s">
